--- a/VerveStacks_POL_grids_kan50/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_POL_grids_kan50/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr updateLinks="never"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\SubRES_Tmpl\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan51\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06207D76-FEBF-44F4-BE86-8127EF830D95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC5F1B94-8D46-464F-BCD1-844899099654}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="368" yWindow="368" windowWidth="21599" windowHeight="12772" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AVA" sheetId="6" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="928" uniqueCount="188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1068" uniqueCount="212">
   <si>
     <t>PSET_PN</t>
   </si>
@@ -307,13 +307,13 @@
     <t>at grid node - Gdynia_POL</t>
   </si>
   <si>
-    <t>en_gas_ccgt,en_gas_turbine,en_chp_gas_cc_ext,en_gas_ccs,en_coal_subcritical,en_coal_supercritical,en_coal_ultrasupercritical,en_coal_igcc,en_nuclear,en_nuclear_smr,en_biomass,en_chp_biomass_chips_ext,en_hop_gas_boiler,en_hop_biomass_chips,en_hop_electric_boiler,en_hp_air_10mw,en_chp_gas_cc_ext_ccs</t>
-  </si>
-  <si>
-    <t>Katowice_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Katowice_POL</t>
+    <t>en_gas_ccgt,en_gas_turbine,en_chp_gas_cc_ext,en_gas_ccs,en_coal_subcritical,en_coal_supercritical,en_coal_ultrasupercritical,en_coal_igcc,en_nuclear,en_nuclear_smr,en_biomass,en_chp_biomass_chips_ext,en_biomass_ccs,en_chp_biomass_pellets_ext_ccs,en_hop_gas_boiler,en_hop_biomass_chips,en_hop_electric_boiler,en_hp_air_10mw,en_chp_gas_cc_ext_ccs</t>
+  </si>
+  <si>
+    <t>Giszowiec_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Giszowiec_POL</t>
   </si>
   <si>
     <t>Radomsko_POL</t>
@@ -322,10 +322,16 @@
     <t>at grid node - Radomsko_POL</t>
   </si>
   <si>
-    <t>Poznan_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Poznan_POL</t>
+    <t>Swarzedz_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Swarzedz_POL</t>
+  </si>
+  <si>
+    <t>SiemianowiceSlaski_POL</t>
+  </si>
+  <si>
+    <t>at grid node - SiemianowiceSlaski_POL</t>
   </si>
   <si>
     <t>Krakow_POL</t>
@@ -334,16 +340,22 @@
     <t>at grid node - Krakow_POL</t>
   </si>
   <si>
-    <t>Mielec_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Mielec_POL</t>
-  </si>
-  <si>
-    <t>Lomza_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Lomza_POL</t>
+    <t>Staszow_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Staszow_POL</t>
+  </si>
+  <si>
+    <t>Sosnowiec_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Sosnowiec_POL</t>
+  </si>
+  <si>
+    <t>Kolno_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Kolno_POL</t>
   </si>
   <si>
     <t>Wloclawek_POL</t>
@@ -358,28 +370,28 @@
     <t>at grid node - Konin_POL</t>
   </si>
   <si>
-    <t>Sosnowiec_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Sosnowiec_POL</t>
-  </si>
-  <si>
-    <t>Bydgoszcz_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Bydgoszcz_POL</t>
-  </si>
-  <si>
-    <t>Szczecin_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Szczecin_POL</t>
-  </si>
-  <si>
-    <t>Gdansk_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Gdansk_POL</t>
+    <t>KedzierzynKozle_POL</t>
+  </si>
+  <si>
+    <t>at grid node - KedzierzynKozle_POL</t>
+  </si>
+  <si>
+    <t>Torun_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Torun_POL</t>
+  </si>
+  <si>
+    <t>Police_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Police_POL</t>
+  </si>
+  <si>
+    <t>Rumia_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Rumia_POL</t>
   </si>
   <si>
     <t>GorzowWielkopolski_POL</t>
@@ -394,16 +406,130 @@
     <t>at grid node - Grudziadz_POL</t>
   </si>
   <si>
-    <t>Lubin_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Lubin_POL</t>
-  </si>
-  <si>
-    <t>Olesnica_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Olesnica_POL</t>
+    <t>NowaSol_POL</t>
+  </si>
+  <si>
+    <t>at grid node - NowaSol_POL</t>
+  </si>
+  <si>
+    <t>Kalisz_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Kalisz_POL</t>
+  </si>
+  <si>
+    <t>Radom_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Radom_POL</t>
+  </si>
+  <si>
+    <t>PiotrkowTrybunalsk_POL</t>
+  </si>
+  <si>
+    <t>at grid node - PiotrkowTrybunalsk_POL</t>
+  </si>
+  <si>
+    <t>OstrowMazowiecka_POL</t>
+  </si>
+  <si>
+    <t>at grid node - OstrowMazowiecka_POL</t>
+  </si>
+  <si>
+    <t>Tczew_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Tczew_POL</t>
+  </si>
+  <si>
+    <t>Plock_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Plock_POL</t>
+  </si>
+  <si>
+    <t>KamienPomorski_POL</t>
+  </si>
+  <si>
+    <t>at grid node - KamienPomorski_POL</t>
+  </si>
+  <si>
+    <t>Zory_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Zory_POL</t>
+  </si>
+  <si>
+    <t>Rzeszow_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Rzeszow_POL</t>
+  </si>
+  <si>
+    <t>Wroclaw_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Wroclaw_POL</t>
+  </si>
+  <si>
+    <t>Lukow_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Lukow_POL</t>
+  </si>
+  <si>
+    <t>Zabki_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Zabki_POL</t>
+  </si>
+  <si>
+    <t>Kwidzyn_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Kwidzyn_POL</t>
+  </si>
+  <si>
+    <t>Swidnik_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Swidnik_POL</t>
+  </si>
+  <si>
+    <t>ZielonaGora_POL</t>
+  </si>
+  <si>
+    <t>at grid node - ZielonaGora_POL</t>
+  </si>
+  <si>
+    <t>Bialystok_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Bialystok_POL</t>
+  </si>
+  <si>
+    <t>BielskoBiala_POL</t>
+  </si>
+  <si>
+    <t>at grid node - BielskoBiala_POL</t>
+  </si>
+  <si>
+    <t>Wloszczowa_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Wloszczowa_POL</t>
+  </si>
+  <si>
+    <t>Mikolow_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Mikolow_POL</t>
+  </si>
+  <si>
+    <t>Opole_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Opole_POL</t>
   </si>
   <si>
     <t>Pulawy_POL</t>
@@ -412,28 +538,37 @@
     <t>at grid node - Pulawy_POL</t>
   </si>
   <si>
-    <t>PiotrkowTrybunalsk_POL</t>
-  </si>
-  <si>
-    <t>at grid node - PiotrkowTrybunalsk_POL</t>
-  </si>
-  <si>
-    <t>Rzeszow_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Rzeszow_POL</t>
-  </si>
-  <si>
-    <t>Plock_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Plock_POL</t>
-  </si>
-  <si>
-    <t>Police_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Police_POL</t>
+    <t>Boleslawiec_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Boleslawiec_POL</t>
+  </si>
+  <si>
+    <t>en_battery_4h,en_battery_8h</t>
+  </si>
+  <si>
+    <t>Ustka_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Ustka_POL</t>
+  </si>
+  <si>
+    <t>Koszalin_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Koszalin_POL</t>
+  </si>
+  <si>
+    <t>Krapkowice_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Krapkowice_POL</t>
+  </si>
+  <si>
+    <t>Walbrzych_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Walbrzych_POL</t>
   </si>
   <si>
     <t>Debica_POL</t>
@@ -442,103 +577,37 @@
     <t>at grid node - Debica_POL</t>
   </si>
   <si>
-    <t>Wroclaw_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Wroclaw_POL</t>
-  </si>
-  <si>
-    <t>Warsaw_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Warsaw_POL</t>
-  </si>
-  <si>
-    <t>Kwidzyn_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Kwidzyn_POL</t>
-  </si>
-  <si>
-    <t>ZielonaGora_POL</t>
-  </si>
-  <si>
-    <t>at grid node - ZielonaGora_POL</t>
-  </si>
-  <si>
-    <t>Bialystok_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Bialystok_POL</t>
-  </si>
-  <si>
-    <t>BielskoBiala_POL</t>
-  </si>
-  <si>
-    <t>at grid node - BielskoBiala_POL</t>
-  </si>
-  <si>
-    <t>Czestochowa_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Czestochowa_POL</t>
-  </si>
-  <si>
-    <t>Gliwice_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Gliwice_POL</t>
-  </si>
-  <si>
-    <t>Opole_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Opole_POL</t>
-  </si>
-  <si>
-    <t>Boleslawiec_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Boleslawiec_POL</t>
-  </si>
-  <si>
-    <t>en_battery_4h,en_battery_8h</t>
-  </si>
-  <si>
-    <t>Ustka_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Ustka_POL</t>
-  </si>
-  <si>
-    <t>Koszalin_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Koszalin_POL</t>
-  </si>
-  <si>
-    <t>KedzierzynKozle_POL</t>
-  </si>
-  <si>
-    <t>at grid node - KedzierzynKozle_POL</t>
-  </si>
-  <si>
-    <t>Swidnica_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Swidnica_POL</t>
-  </si>
-  <si>
-    <t>Tarnow_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Tarnow_POL</t>
-  </si>
-  <si>
-    <t>Krosno_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Krosno_POL</t>
+    <t>Sanok_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Sanok_POL</t>
+  </si>
+  <si>
+    <t>Miastko_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Miastko_POL</t>
+  </si>
+  <si>
+    <t>OstrowiecSwietokrz_POL</t>
+  </si>
+  <si>
+    <t>at grid node - OstrowiecSwietokrz_POL</t>
+  </si>
+  <si>
+    <t>e_demand,ev_battery,H2prd_Elc_PEM,H2prd_Elc_ALK</t>
+  </si>
+  <si>
+    <t>Chelm_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Chelm_POL</t>
+  </si>
+  <si>
+    <t>Otwock_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Otwock_POL</t>
   </si>
   <si>
     <t>Legnica_POL</t>
@@ -547,7 +616,34 @@
     <t>at grid node - Legnica_POL</t>
   </si>
   <si>
-    <t>e_demand,ev_battery,H2prd_Elc_PEM,H2prd_Elc_ALK</t>
+    <t>Nowogard_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Nowogard_POL</t>
+  </si>
+  <si>
+    <t>Rybnik_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Rybnik_POL</t>
+  </si>
+  <si>
+    <t>Slupsk_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Slupsk_POL</t>
+  </si>
+  <si>
+    <t>Elk_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Elk_POL</t>
+  </si>
+  <si>
+    <t>Olsztyn_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Olsztyn_POL</t>
   </si>
   <si>
     <t>Grajewo_POL</t>
@@ -562,40 +658,16 @@
     <t>at grid node - Kielce_POL</t>
   </si>
   <si>
-    <t>Slupsk_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Slupsk_POL</t>
-  </si>
-  <si>
-    <t>OstrowiecSwietokrz_POL</t>
-  </si>
-  <si>
-    <t>at grid node - OstrowiecSwietokrz_POL</t>
-  </si>
-  <si>
-    <t>Olsztyn_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Olsztyn_POL</t>
-  </si>
-  <si>
-    <t>Elk_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Elk_POL</t>
-  </si>
-  <si>
-    <t>Zamosc_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Zamosc_POL</t>
-  </si>
-  <si>
-    <t>Chelm_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Chelm_POL</t>
+    <t>TomaszowLubelski_POL</t>
+  </si>
+  <si>
+    <t>at grid node - TomaszowLubelski_POL</t>
+  </si>
+  <si>
+    <t>Wagrowiec_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Wagrowiec_POL</t>
   </si>
   <si>
     <t>h_demand</t>
@@ -970,15 +1042,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{268E9BAB-B98F-4B82-9042-51EABC9ED525}">
-  <dimension ref="B3:Y58"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <dimension ref="B3:Y70"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="3" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="3" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="4" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="4" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>20</v>
       </c>
@@ -986,7 +1058,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="5" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="5" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>43</v>
       </c>
@@ -994,7 +1066,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="9" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>69</v>
       </c>
@@ -1011,7 +1083,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="10" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="10" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
         <v>31</v>
       </c>
@@ -1073,7 +1145,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="11" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
         <v>86</v>
       </c>
@@ -1090,52 +1162,52 @@
         <v>86</v>
       </c>
       <c r="H11" t="s">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="I11" t="s">
-        <v>139</v>
+        <v>149</v>
       </c>
       <c r="J11" t="s">
-        <v>154</v>
+        <v>168</v>
       </c>
       <c r="L11" t="s">
         <v>86</v>
       </c>
       <c r="M11" t="s">
-        <v>167</v>
+        <v>183</v>
       </c>
       <c r="N11" t="s">
-        <v>168</v>
+        <v>184</v>
       </c>
       <c r="O11" t="s">
-        <v>169</v>
+        <v>185</v>
       </c>
       <c r="Q11" t="s">
         <v>86</v>
       </c>
       <c r="R11" t="s">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="S11" t="s">
-        <v>101</v>
+        <v>131</v>
       </c>
       <c r="T11" t="s">
-        <v>186</v>
+        <v>210</v>
       </c>
       <c r="V11" t="s">
         <v>86</v>
       </c>
       <c r="W11" t="s">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="X11" t="s">
-        <v>101</v>
+        <v>131</v>
       </c>
       <c r="Y11" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="12" spans="2:25" x14ac:dyDescent="0.45">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="12" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
         <v>86</v>
       </c>
@@ -1152,52 +1224,52 @@
         <v>86</v>
       </c>
       <c r="H12" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="I12" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="J12" t="s">
-        <v>154</v>
+        <v>168</v>
       </c>
       <c r="L12" t="s">
         <v>86</v>
       </c>
       <c r="M12" t="s">
-        <v>106</v>
+        <v>142</v>
       </c>
       <c r="N12" t="s">
-        <v>107</v>
+        <v>143</v>
       </c>
       <c r="O12" t="s">
-        <v>169</v>
+        <v>185</v>
       </c>
       <c r="Q12" t="s">
         <v>86</v>
       </c>
       <c r="R12" t="s">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="S12" t="s">
-        <v>139</v>
+        <v>149</v>
       </c>
       <c r="T12" t="s">
-        <v>186</v>
+        <v>210</v>
       </c>
       <c r="V12" t="s">
         <v>86</v>
       </c>
       <c r="W12" t="s">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="X12" t="s">
-        <v>139</v>
+        <v>149</v>
       </c>
       <c r="Y12" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="13" spans="2:25" x14ac:dyDescent="0.45">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="13" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>86</v>
       </c>
@@ -1214,52 +1286,52 @@
         <v>86</v>
       </c>
       <c r="H13" t="s">
-        <v>142</v>
+        <v>154</v>
       </c>
       <c r="I13" t="s">
-        <v>143</v>
+        <v>155</v>
       </c>
       <c r="J13" t="s">
-        <v>154</v>
+        <v>168</v>
       </c>
       <c r="L13" t="s">
         <v>86</v>
       </c>
       <c r="M13" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="N13" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="O13" t="s">
-        <v>169</v>
+        <v>185</v>
       </c>
       <c r="Q13" t="s">
         <v>86</v>
       </c>
       <c r="R13" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="S13" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="T13" t="s">
-        <v>186</v>
+        <v>210</v>
       </c>
       <c r="V13" t="s">
         <v>86</v>
       </c>
       <c r="W13" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="X13" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="Y13" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="14" spans="2:25" x14ac:dyDescent="0.45">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="14" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
         <v>86</v>
       </c>
@@ -1276,52 +1348,52 @@
         <v>86</v>
       </c>
       <c r="H14" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="I14" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="J14" t="s">
+        <v>168</v>
+      </c>
+      <c r="L14" t="s">
+        <v>86</v>
+      </c>
+      <c r="M14" t="s">
+        <v>186</v>
+      </c>
+      <c r="N14" t="s">
+        <v>187</v>
+      </c>
+      <c r="O14" t="s">
+        <v>185</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>86</v>
+      </c>
+      <c r="R14" t="s">
         <v>154</v>
       </c>
-      <c r="L14" t="s">
-        <v>86</v>
-      </c>
-      <c r="M14" t="s">
-        <v>172</v>
-      </c>
-      <c r="N14" t="s">
-        <v>173</v>
-      </c>
-      <c r="O14" t="s">
-        <v>169</v>
-      </c>
-      <c r="Q14" t="s">
-        <v>86</v>
-      </c>
-      <c r="R14" t="s">
-        <v>142</v>
-      </c>
       <c r="S14" t="s">
-        <v>143</v>
+        <v>155</v>
       </c>
       <c r="T14" t="s">
-        <v>186</v>
+        <v>210</v>
       </c>
       <c r="V14" t="s">
         <v>86</v>
       </c>
       <c r="W14" t="s">
-        <v>142</v>
+        <v>154</v>
       </c>
       <c r="X14" t="s">
-        <v>143</v>
+        <v>155</v>
       </c>
       <c r="Y14" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="15" spans="2:25" x14ac:dyDescent="0.45">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="15" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
         <v>86</v>
       </c>
@@ -1344,46 +1416,46 @@
         <v>88</v>
       </c>
       <c r="J15" t="s">
-        <v>154</v>
+        <v>168</v>
       </c>
       <c r="L15" t="s">
         <v>86</v>
       </c>
       <c r="M15" t="s">
-        <v>94</v>
+        <v>138</v>
       </c>
       <c r="N15" t="s">
-        <v>95</v>
+        <v>139</v>
       </c>
       <c r="O15" t="s">
-        <v>169</v>
+        <v>185</v>
       </c>
       <c r="Q15" t="s">
         <v>86</v>
       </c>
       <c r="R15" t="s">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="S15" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="T15" t="s">
-        <v>186</v>
+        <v>210</v>
       </c>
       <c r="V15" t="s">
         <v>86</v>
       </c>
       <c r="W15" t="s">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="X15" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="Y15" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="16" spans="2:25" x14ac:dyDescent="0.45">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="16" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
         <v>86</v>
       </c>
@@ -1406,46 +1478,46 @@
         <v>91</v>
       </c>
       <c r="J16" t="s">
-        <v>154</v>
+        <v>168</v>
       </c>
       <c r="L16" t="s">
         <v>86</v>
       </c>
       <c r="M16" t="s">
-        <v>116</v>
+        <v>98</v>
       </c>
       <c r="N16" t="s">
-        <v>117</v>
+        <v>99</v>
       </c>
       <c r="O16" t="s">
-        <v>169</v>
+        <v>185</v>
       </c>
       <c r="Q16" t="s">
         <v>86</v>
       </c>
       <c r="R16" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="S16" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="T16" t="s">
-        <v>186</v>
+        <v>210</v>
       </c>
       <c r="V16" t="s">
         <v>86</v>
       </c>
       <c r="W16" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="X16" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="Y16" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="17" spans="2:25" x14ac:dyDescent="0.45">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="17" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
         <v>86</v>
       </c>
@@ -1468,46 +1540,46 @@
         <v>93</v>
       </c>
       <c r="J17" t="s">
-        <v>154</v>
+        <v>168</v>
       </c>
       <c r="L17" t="s">
         <v>86</v>
       </c>
       <c r="M17" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="N17" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="O17" t="s">
-        <v>169</v>
+        <v>185</v>
       </c>
       <c r="Q17" t="s">
         <v>86</v>
       </c>
       <c r="R17" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="S17" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="T17" t="s">
-        <v>186</v>
+        <v>210</v>
       </c>
       <c r="V17" t="s">
         <v>86</v>
       </c>
       <c r="W17" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="X17" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="Y17" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="18" spans="2:25" x14ac:dyDescent="0.45">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="18" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
         <v>86</v>
       </c>
@@ -1530,46 +1602,46 @@
         <v>95</v>
       </c>
       <c r="J18" t="s">
-        <v>154</v>
+        <v>168</v>
       </c>
       <c r="L18" t="s">
         <v>86</v>
       </c>
       <c r="M18" t="s">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="N18" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="O18" t="s">
-        <v>169</v>
+        <v>185</v>
       </c>
       <c r="Q18" t="s">
         <v>86</v>
       </c>
       <c r="R18" t="s">
-        <v>146</v>
+        <v>158</v>
       </c>
       <c r="S18" t="s">
-        <v>147</v>
+        <v>159</v>
       </c>
       <c r="T18" t="s">
-        <v>186</v>
+        <v>210</v>
       </c>
       <c r="V18" t="s">
         <v>86</v>
       </c>
       <c r="W18" t="s">
-        <v>146</v>
+        <v>158</v>
       </c>
       <c r="X18" t="s">
-        <v>147</v>
+        <v>159</v>
       </c>
       <c r="Y18" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="19" spans="2:25" x14ac:dyDescent="0.45">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="19" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
         <v>86</v>
       </c>
@@ -1592,46 +1664,46 @@
         <v>97</v>
       </c>
       <c r="J19" t="s">
-        <v>154</v>
+        <v>168</v>
       </c>
       <c r="L19" t="s">
         <v>86</v>
       </c>
       <c r="M19" t="s">
-        <v>140</v>
+        <v>106</v>
       </c>
       <c r="N19" t="s">
-        <v>141</v>
+        <v>107</v>
       </c>
       <c r="O19" t="s">
-        <v>169</v>
+        <v>185</v>
       </c>
       <c r="Q19" t="s">
         <v>86</v>
       </c>
       <c r="R19" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="S19" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="T19" t="s">
-        <v>186</v>
+        <v>210</v>
       </c>
       <c r="V19" t="s">
         <v>86</v>
       </c>
       <c r="W19" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="X19" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="Y19" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="20" spans="2:25" x14ac:dyDescent="0.45">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="20" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B20" t="s">
         <v>86</v>
       </c>
@@ -1648,52 +1720,52 @@
         <v>86</v>
       </c>
       <c r="H20" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="I20" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="J20" t="s">
-        <v>154</v>
+        <v>168</v>
       </c>
       <c r="L20" t="s">
         <v>86</v>
       </c>
       <c r="M20" t="s">
-        <v>144</v>
+        <v>166</v>
       </c>
       <c r="N20" t="s">
-        <v>145</v>
+        <v>167</v>
       </c>
       <c r="O20" t="s">
-        <v>169</v>
+        <v>185</v>
       </c>
       <c r="Q20" t="s">
         <v>86</v>
       </c>
       <c r="R20" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="S20" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="T20" t="s">
-        <v>186</v>
+        <v>210</v>
       </c>
       <c r="V20" t="s">
         <v>86</v>
       </c>
       <c r="W20" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="X20" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="Y20" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="21" spans="2:25" x14ac:dyDescent="0.45">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="21" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
         <v>86</v>
       </c>
@@ -1716,46 +1788,46 @@
         <v>103</v>
       </c>
       <c r="J21" t="s">
-        <v>154</v>
+        <v>168</v>
       </c>
       <c r="L21" t="s">
         <v>86</v>
       </c>
       <c r="M21" t="s">
-        <v>96</v>
+        <v>124</v>
       </c>
       <c r="N21" t="s">
-        <v>97</v>
+        <v>125</v>
       </c>
       <c r="O21" t="s">
-        <v>169</v>
+        <v>185</v>
       </c>
       <c r="Q21" t="s">
         <v>86</v>
       </c>
       <c r="R21" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="S21" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="T21" t="s">
-        <v>186</v>
+        <v>210</v>
       </c>
       <c r="V21" t="s">
         <v>86</v>
       </c>
       <c r="W21" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="X21" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="Y21" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="22" spans="2:25" x14ac:dyDescent="0.45">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="22" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
         <v>86</v>
       </c>
@@ -1772,52 +1844,52 @@
         <v>86</v>
       </c>
       <c r="H22" t="s">
-        <v>146</v>
+        <v>104</v>
       </c>
       <c r="I22" t="s">
-        <v>147</v>
+        <v>105</v>
       </c>
       <c r="J22" t="s">
-        <v>154</v>
+        <v>168</v>
       </c>
       <c r="L22" t="s">
         <v>86</v>
       </c>
       <c r="M22" t="s">
-        <v>124</v>
+        <v>188</v>
       </c>
       <c r="N22" t="s">
-        <v>125</v>
+        <v>189</v>
       </c>
       <c r="O22" t="s">
-        <v>169</v>
+        <v>185</v>
       </c>
       <c r="Q22" t="s">
         <v>86</v>
       </c>
       <c r="R22" t="s">
-        <v>110</v>
+        <v>96</v>
       </c>
       <c r="S22" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="T22" t="s">
-        <v>186</v>
+        <v>210</v>
       </c>
       <c r="V22" t="s">
         <v>86</v>
       </c>
       <c r="W22" t="s">
-        <v>110</v>
+        <v>96</v>
       </c>
       <c r="X22" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="Y22" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="23" spans="2:25" x14ac:dyDescent="0.45">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="23" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
         <v>86</v>
       </c>
@@ -1834,25 +1906,25 @@
         <v>86</v>
       </c>
       <c r="H23" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="I23" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="J23" t="s">
-        <v>154</v>
+        <v>168</v>
       </c>
       <c r="L23" t="s">
         <v>86</v>
       </c>
       <c r="M23" t="s">
-        <v>150</v>
+        <v>134</v>
       </c>
       <c r="N23" t="s">
-        <v>151</v>
+        <v>135</v>
       </c>
       <c r="O23" t="s">
-        <v>169</v>
+        <v>185</v>
       </c>
       <c r="Q23" t="s">
         <v>86</v>
@@ -1864,7 +1936,7 @@
         <v>115</v>
       </c>
       <c r="T23" t="s">
-        <v>186</v>
+        <v>210</v>
       </c>
       <c r="V23" t="s">
         <v>86</v>
@@ -1876,10 +1948,10 @@
         <v>115</v>
       </c>
       <c r="Y23" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="24" spans="2:25" x14ac:dyDescent="0.45">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="24" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B24" t="s">
         <v>86</v>
       </c>
@@ -1896,25 +1968,25 @@
         <v>86</v>
       </c>
       <c r="H24" t="s">
-        <v>106</v>
+        <v>158</v>
       </c>
       <c r="I24" t="s">
-        <v>107</v>
+        <v>159</v>
       </c>
       <c r="J24" t="s">
-        <v>154</v>
+        <v>168</v>
       </c>
       <c r="L24" t="s">
         <v>86</v>
       </c>
       <c r="M24" t="s">
-        <v>92</v>
+        <v>175</v>
       </c>
       <c r="N24" t="s">
-        <v>93</v>
+        <v>176</v>
       </c>
       <c r="O24" t="s">
-        <v>169</v>
+        <v>185</v>
       </c>
       <c r="Q24" t="s">
         <v>86</v>
@@ -1926,7 +1998,7 @@
         <v>119</v>
       </c>
       <c r="T24" t="s">
-        <v>186</v>
+        <v>210</v>
       </c>
       <c r="V24" t="s">
         <v>86</v>
@@ -1938,10 +2010,10 @@
         <v>119</v>
       </c>
       <c r="Y24" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="25" spans="2:25" x14ac:dyDescent="0.45">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="25" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B25" t="s">
         <v>86</v>
       </c>
@@ -1964,46 +2036,46 @@
         <v>109</v>
       </c>
       <c r="J25" t="s">
-        <v>154</v>
+        <v>168</v>
       </c>
       <c r="L25" t="s">
         <v>86</v>
       </c>
       <c r="M25" t="s">
-        <v>176</v>
+        <v>150</v>
       </c>
       <c r="N25" t="s">
-        <v>177</v>
+        <v>151</v>
       </c>
       <c r="O25" t="s">
-        <v>169</v>
+        <v>185</v>
       </c>
       <c r="Q25" t="s">
         <v>86</v>
       </c>
       <c r="R25" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="S25" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="T25" t="s">
-        <v>186</v>
+        <v>210</v>
       </c>
       <c r="V25" t="s">
         <v>86</v>
       </c>
       <c r="W25" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="X25" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="Y25" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="26" spans="2:25" x14ac:dyDescent="0.45">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="26" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B26" t="s">
         <v>86</v>
       </c>
@@ -2026,46 +2098,46 @@
         <v>111</v>
       </c>
       <c r="J26" t="s">
-        <v>154</v>
+        <v>168</v>
       </c>
       <c r="L26" t="s">
         <v>86</v>
       </c>
       <c r="M26" t="s">
-        <v>157</v>
+        <v>146</v>
       </c>
       <c r="N26" t="s">
-        <v>158</v>
+        <v>147</v>
       </c>
       <c r="O26" t="s">
-        <v>169</v>
+        <v>185</v>
       </c>
       <c r="Q26" t="s">
         <v>86</v>
       </c>
       <c r="R26" t="s">
-        <v>96</v>
+        <v>124</v>
       </c>
       <c r="S26" t="s">
-        <v>97</v>
+        <v>125</v>
       </c>
       <c r="T26" t="s">
-        <v>186</v>
+        <v>210</v>
       </c>
       <c r="V26" t="s">
         <v>86</v>
       </c>
       <c r="W26" t="s">
-        <v>96</v>
+        <v>124</v>
       </c>
       <c r="X26" t="s">
-        <v>97</v>
+        <v>125</v>
       </c>
       <c r="Y26" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="27" spans="2:25" x14ac:dyDescent="0.45">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="27" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B27" t="s">
         <v>86</v>
       </c>
@@ -2088,46 +2160,46 @@
         <v>113</v>
       </c>
       <c r="J27" t="s">
-        <v>154</v>
+        <v>168</v>
       </c>
       <c r="L27" t="s">
         <v>86</v>
       </c>
       <c r="M27" t="s">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="N27" t="s">
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="O27" t="s">
-        <v>169</v>
+        <v>185</v>
       </c>
       <c r="Q27" t="s">
         <v>86</v>
       </c>
       <c r="R27" t="s">
-        <v>124</v>
+        <v>98</v>
       </c>
       <c r="S27" t="s">
-        <v>125</v>
+        <v>99</v>
       </c>
       <c r="T27" t="s">
-        <v>186</v>
+        <v>210</v>
       </c>
       <c r="V27" t="s">
         <v>86</v>
       </c>
       <c r="W27" t="s">
-        <v>124</v>
+        <v>98</v>
       </c>
       <c r="X27" t="s">
-        <v>125</v>
+        <v>99</v>
       </c>
       <c r="Y27" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="28" spans="2:25" x14ac:dyDescent="0.45">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="28" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B28" t="s">
         <v>86</v>
       </c>
@@ -2150,46 +2222,46 @@
         <v>115</v>
       </c>
       <c r="J28" t="s">
-        <v>154</v>
+        <v>168</v>
       </c>
       <c r="L28" t="s">
         <v>86</v>
       </c>
       <c r="M28" t="s">
-        <v>114</v>
+        <v>190</v>
       </c>
       <c r="N28" t="s">
-        <v>115</v>
+        <v>191</v>
       </c>
       <c r="O28" t="s">
-        <v>169</v>
+        <v>185</v>
       </c>
       <c r="Q28" t="s">
         <v>86</v>
       </c>
       <c r="R28" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="S28" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="T28" t="s">
-        <v>186</v>
+        <v>210</v>
       </c>
       <c r="V28" t="s">
         <v>86</v>
       </c>
       <c r="W28" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="X28" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="Y28" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="29" spans="2:25" x14ac:dyDescent="0.45">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="29" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B29" t="s">
         <v>86</v>
       </c>
@@ -2212,46 +2284,46 @@
         <v>117</v>
       </c>
       <c r="J29" t="s">
-        <v>154</v>
+        <v>168</v>
       </c>
       <c r="L29" t="s">
         <v>86</v>
       </c>
       <c r="M29" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="N29" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="O29" t="s">
-        <v>169</v>
+        <v>185</v>
       </c>
       <c r="Q29" t="s">
         <v>86</v>
       </c>
       <c r="R29" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="S29" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="T29" t="s">
-        <v>186</v>
+        <v>210</v>
       </c>
       <c r="V29" t="s">
         <v>86</v>
       </c>
       <c r="W29" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="X29" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="Y29" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="30" spans="2:25" x14ac:dyDescent="0.45">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="30" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B30" t="s">
         <v>86</v>
       </c>
@@ -2274,19 +2346,19 @@
         <v>119</v>
       </c>
       <c r="J30" t="s">
-        <v>154</v>
+        <v>168</v>
       </c>
       <c r="L30" t="s">
         <v>86</v>
       </c>
       <c r="M30" t="s">
-        <v>178</v>
+        <v>118</v>
       </c>
       <c r="N30" t="s">
-        <v>179</v>
+        <v>119</v>
       </c>
       <c r="O30" t="s">
-        <v>169</v>
+        <v>185</v>
       </c>
       <c r="Q30" t="s">
         <v>86</v>
@@ -2298,7 +2370,7 @@
         <v>95</v>
       </c>
       <c r="T30" t="s">
-        <v>186</v>
+        <v>210</v>
       </c>
       <c r="V30" t="s">
         <v>86</v>
@@ -2310,10 +2382,10 @@
         <v>95</v>
       </c>
       <c r="Y30" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="31" spans="2:25" x14ac:dyDescent="0.45">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="31" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B31" t="s">
         <v>86</v>
       </c>
@@ -2336,46 +2408,46 @@
         <v>121</v>
       </c>
       <c r="J31" t="s">
-        <v>154</v>
+        <v>168</v>
       </c>
       <c r="L31" t="s">
         <v>86</v>
       </c>
       <c r="M31" t="s">
-        <v>108</v>
+        <v>130</v>
       </c>
       <c r="N31" t="s">
-        <v>109</v>
+        <v>131</v>
       </c>
       <c r="O31" t="s">
-        <v>169</v>
+        <v>185</v>
       </c>
       <c r="Q31" t="s">
         <v>86</v>
       </c>
       <c r="R31" t="s">
-        <v>132</v>
+        <v>140</v>
       </c>
       <c r="S31" t="s">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="T31" t="s">
-        <v>186</v>
+        <v>210</v>
       </c>
       <c r="V31" t="s">
         <v>86</v>
       </c>
       <c r="W31" t="s">
-        <v>132</v>
+        <v>140</v>
       </c>
       <c r="X31" t="s">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="Y31" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="32" spans="2:25" x14ac:dyDescent="0.45">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="32" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B32" t="s">
         <v>86</v>
       </c>
@@ -2398,46 +2470,46 @@
         <v>123</v>
       </c>
       <c r="J32" t="s">
-        <v>154</v>
+        <v>168</v>
       </c>
       <c r="L32" t="s">
         <v>86</v>
       </c>
       <c r="M32" t="s">
-        <v>130</v>
+        <v>152</v>
       </c>
       <c r="N32" t="s">
-        <v>131</v>
+        <v>153</v>
       </c>
       <c r="O32" t="s">
-        <v>169</v>
+        <v>185</v>
       </c>
       <c r="Q32" t="s">
         <v>86</v>
       </c>
       <c r="R32" t="s">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="S32" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="T32" t="s">
-        <v>186</v>
+        <v>210</v>
       </c>
       <c r="V32" t="s">
         <v>86</v>
       </c>
       <c r="W32" t="s">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="X32" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="Y32" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="33" spans="2:25" x14ac:dyDescent="0.45">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="33" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B33" t="s">
         <v>86</v>
       </c>
@@ -2460,46 +2532,46 @@
         <v>125</v>
       </c>
       <c r="J33" t="s">
-        <v>154</v>
+        <v>168</v>
       </c>
       <c r="L33" t="s">
         <v>86</v>
       </c>
       <c r="M33" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="N33" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="O33" t="s">
-        <v>169</v>
+        <v>185</v>
       </c>
       <c r="Q33" t="s">
         <v>86</v>
       </c>
       <c r="R33" t="s">
-        <v>122</v>
+        <v>144</v>
       </c>
       <c r="S33" t="s">
-        <v>123</v>
+        <v>145</v>
       </c>
       <c r="T33" t="s">
-        <v>186</v>
+        <v>210</v>
       </c>
       <c r="V33" t="s">
         <v>86</v>
       </c>
       <c r="W33" t="s">
-        <v>122</v>
+        <v>144</v>
       </c>
       <c r="X33" t="s">
-        <v>123</v>
+        <v>145</v>
       </c>
       <c r="Y33" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="34" spans="2:25" x14ac:dyDescent="0.45">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="34" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B34" t="s">
         <v>86</v>
       </c>
@@ -2522,46 +2594,46 @@
         <v>127</v>
       </c>
       <c r="J34" t="s">
-        <v>154</v>
+        <v>168</v>
       </c>
       <c r="L34" t="s">
         <v>86</v>
       </c>
       <c r="M34" t="s">
-        <v>142</v>
+        <v>100</v>
       </c>
       <c r="N34" t="s">
-        <v>143</v>
+        <v>101</v>
       </c>
       <c r="O34" t="s">
-        <v>169</v>
+        <v>185</v>
       </c>
       <c r="Q34" t="s">
         <v>86</v>
       </c>
       <c r="R34" t="s">
-        <v>136</v>
+        <v>146</v>
       </c>
       <c r="S34" t="s">
-        <v>137</v>
+        <v>147</v>
       </c>
       <c r="T34" t="s">
-        <v>186</v>
+        <v>210</v>
       </c>
       <c r="V34" t="s">
         <v>86</v>
       </c>
       <c r="W34" t="s">
-        <v>136</v>
+        <v>146</v>
       </c>
       <c r="X34" t="s">
-        <v>137</v>
+        <v>147</v>
       </c>
       <c r="Y34" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="35" spans="2:25" x14ac:dyDescent="0.45">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="35" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B35" t="s">
         <v>86</v>
       </c>
@@ -2584,46 +2656,46 @@
         <v>129</v>
       </c>
       <c r="J35" t="s">
-        <v>154</v>
+        <v>168</v>
       </c>
       <c r="L35" t="s">
         <v>86</v>
       </c>
       <c r="M35" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="N35" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="O35" t="s">
-        <v>169</v>
+        <v>185</v>
       </c>
       <c r="Q35" t="s">
         <v>86</v>
       </c>
       <c r="R35" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="S35" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="T35" t="s">
-        <v>186</v>
+        <v>210</v>
       </c>
       <c r="V35" t="s">
         <v>86</v>
       </c>
       <c r="W35" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="X35" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="Y35" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="36" spans="2:25" x14ac:dyDescent="0.45">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="36" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B36" t="s">
         <v>86</v>
       </c>
@@ -2640,52 +2712,52 @@
         <v>86</v>
       </c>
       <c r="H36" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="I36" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="J36" t="s">
-        <v>154</v>
+        <v>168</v>
       </c>
       <c r="L36" t="s">
         <v>86</v>
       </c>
       <c r="M36" t="s">
-        <v>98</v>
+        <v>192</v>
       </c>
       <c r="N36" t="s">
-        <v>99</v>
+        <v>193</v>
       </c>
       <c r="O36" t="s">
-        <v>169</v>
+        <v>185</v>
       </c>
       <c r="Q36" t="s">
         <v>86</v>
       </c>
       <c r="R36" t="s">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="S36" t="s">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="T36" t="s">
-        <v>186</v>
+        <v>210</v>
       </c>
       <c r="V36" t="s">
         <v>86</v>
       </c>
       <c r="W36" t="s">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="X36" t="s">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="Y36" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="37" spans="2:25" x14ac:dyDescent="0.45">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="37" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B37" t="s">
         <v>86</v>
       </c>
@@ -2702,52 +2774,52 @@
         <v>86</v>
       </c>
       <c r="H37" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="I37" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="J37" t="s">
-        <v>154</v>
+        <v>168</v>
       </c>
       <c r="L37" t="s">
         <v>86</v>
       </c>
       <c r="M37" t="s">
-        <v>128</v>
+        <v>96</v>
       </c>
       <c r="N37" t="s">
-        <v>129</v>
+        <v>97</v>
       </c>
       <c r="O37" t="s">
-        <v>169</v>
+        <v>185</v>
       </c>
       <c r="Q37" t="s">
         <v>86</v>
       </c>
       <c r="R37" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="S37" t="s">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="T37" t="s">
-        <v>186</v>
+        <v>210</v>
       </c>
       <c r="V37" t="s">
         <v>86</v>
       </c>
       <c r="W37" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="X37" t="s">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="Y37" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="38" spans="2:25" x14ac:dyDescent="0.45">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="38" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B38" t="s">
         <v>86</v>
       </c>
@@ -2764,52 +2836,52 @@
         <v>86</v>
       </c>
       <c r="H38" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="I38" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="J38" t="s">
-        <v>154</v>
+        <v>168</v>
       </c>
       <c r="L38" t="s">
         <v>86</v>
       </c>
       <c r="M38" t="s">
-        <v>136</v>
+        <v>169</v>
       </c>
       <c r="N38" t="s">
-        <v>137</v>
+        <v>170</v>
       </c>
       <c r="O38" t="s">
-        <v>169</v>
+        <v>185</v>
       </c>
       <c r="Q38" t="s">
         <v>86</v>
       </c>
       <c r="R38" t="s">
-        <v>148</v>
+        <v>156</v>
       </c>
       <c r="S38" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="T38" t="s">
-        <v>186</v>
+        <v>210</v>
       </c>
       <c r="V38" t="s">
         <v>86</v>
       </c>
       <c r="W38" t="s">
-        <v>148</v>
+        <v>156</v>
       </c>
       <c r="X38" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="Y38" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="39" spans="2:25" x14ac:dyDescent="0.45">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="39" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B39" t="s">
         <v>86</v>
       </c>
@@ -2826,52 +2898,52 @@
         <v>86</v>
       </c>
       <c r="H39" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="I39" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="J39" t="s">
-        <v>154</v>
+        <v>168</v>
       </c>
       <c r="L39" t="s">
         <v>86</v>
       </c>
       <c r="M39" t="s">
-        <v>132</v>
+        <v>194</v>
       </c>
       <c r="N39" t="s">
-        <v>133</v>
+        <v>195</v>
       </c>
       <c r="O39" t="s">
-        <v>169</v>
+        <v>185</v>
       </c>
       <c r="Q39" t="s">
         <v>86</v>
       </c>
       <c r="R39" t="s">
-        <v>152</v>
+        <v>90</v>
       </c>
       <c r="S39" t="s">
-        <v>153</v>
+        <v>91</v>
       </c>
       <c r="T39" t="s">
-        <v>186</v>
+        <v>210</v>
       </c>
       <c r="V39" t="s">
         <v>86</v>
       </c>
       <c r="W39" t="s">
-        <v>152</v>
+        <v>90</v>
       </c>
       <c r="X39" t="s">
-        <v>153</v>
+        <v>91</v>
       </c>
       <c r="Y39" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="40" spans="2:25" x14ac:dyDescent="0.45">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="40" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B40" t="s">
         <v>86</v>
       </c>
@@ -2888,28 +2960,52 @@
         <v>86</v>
       </c>
       <c r="H40" t="s">
-        <v>155</v>
+        <v>140</v>
       </c>
       <c r="I40" t="s">
-        <v>156</v>
+        <v>141</v>
       </c>
       <c r="J40" t="s">
-        <v>154</v>
+        <v>168</v>
       </c>
       <c r="L40" t="s">
         <v>86</v>
       </c>
       <c r="M40" t="s">
-        <v>120</v>
+        <v>179</v>
       </c>
       <c r="N40" t="s">
-        <v>121</v>
+        <v>180</v>
       </c>
       <c r="O40" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="41" spans="2:25" x14ac:dyDescent="0.45">
+        <v>185</v>
+      </c>
+      <c r="Q40" t="s">
+        <v>86</v>
+      </c>
+      <c r="R40" t="s">
+        <v>160</v>
+      </c>
+      <c r="S40" t="s">
+        <v>161</v>
+      </c>
+      <c r="T40" t="s">
+        <v>210</v>
+      </c>
+      <c r="V40" t="s">
+        <v>86</v>
+      </c>
+      <c r="W40" t="s">
+        <v>160</v>
+      </c>
+      <c r="X40" t="s">
+        <v>161</v>
+      </c>
+      <c r="Y40" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="41" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B41" t="s">
         <v>86</v>
       </c>
@@ -2926,28 +3022,52 @@
         <v>86</v>
       </c>
       <c r="H41" t="s">
-        <v>157</v>
+        <v>142</v>
       </c>
       <c r="I41" t="s">
-        <v>158</v>
+        <v>143</v>
       </c>
       <c r="J41" t="s">
+        <v>168</v>
+      </c>
+      <c r="L41" t="s">
+        <v>86</v>
+      </c>
+      <c r="M41" t="s">
         <v>154</v>
       </c>
-      <c r="L41" t="s">
-        <v>86</v>
-      </c>
-      <c r="M41" t="s">
-        <v>152</v>
-      </c>
       <c r="N41" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="O41" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="42" spans="2:25" x14ac:dyDescent="0.45">
+        <v>185</v>
+      </c>
+      <c r="Q41" t="s">
+        <v>86</v>
+      </c>
+      <c r="R41" t="s">
+        <v>164</v>
+      </c>
+      <c r="S41" t="s">
+        <v>165</v>
+      </c>
+      <c r="T41" t="s">
+        <v>210</v>
+      </c>
+      <c r="V41" t="s">
+        <v>86</v>
+      </c>
+      <c r="W41" t="s">
+        <v>164</v>
+      </c>
+      <c r="X41" t="s">
+        <v>165</v>
+      </c>
+      <c r="Y41" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="42" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B42" t="s">
         <v>86</v>
       </c>
@@ -2964,28 +3084,52 @@
         <v>86</v>
       </c>
       <c r="H42" t="s">
-        <v>159</v>
+        <v>144</v>
       </c>
       <c r="I42" t="s">
-        <v>160</v>
+        <v>145</v>
       </c>
       <c r="J42" t="s">
-        <v>154</v>
+        <v>168</v>
       </c>
       <c r="L42" t="s">
         <v>86</v>
       </c>
       <c r="M42" t="s">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="N42" t="s">
-        <v>105</v>
+        <v>117</v>
       </c>
       <c r="O42" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="43" spans="2:25" x14ac:dyDescent="0.45">
+        <v>185</v>
+      </c>
+      <c r="Q42" t="s">
+        <v>86</v>
+      </c>
+      <c r="R42" t="s">
+        <v>138</v>
+      </c>
+      <c r="S42" t="s">
+        <v>139</v>
+      </c>
+      <c r="T42" t="s">
+        <v>210</v>
+      </c>
+      <c r="V42" t="s">
+        <v>86</v>
+      </c>
+      <c r="W42" t="s">
+        <v>138</v>
+      </c>
+      <c r="X42" t="s">
+        <v>139</v>
+      </c>
+      <c r="Y42" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="43" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B43" t="s">
         <v>86</v>
       </c>
@@ -3002,307 +3146,679 @@
         <v>86</v>
       </c>
       <c r="H43" t="s">
+        <v>146</v>
+      </c>
+      <c r="I43" t="s">
+        <v>147</v>
+      </c>
+      <c r="J43" t="s">
+        <v>168</v>
+      </c>
+      <c r="L43" t="s">
+        <v>86</v>
+      </c>
+      <c r="M43" t="s">
+        <v>196</v>
+      </c>
+      <c r="N43" t="s">
+        <v>197</v>
+      </c>
+      <c r="O43" t="s">
+        <v>185</v>
+      </c>
+      <c r="Q43" t="s">
+        <v>86</v>
+      </c>
+      <c r="R43" t="s">
+        <v>166</v>
+      </c>
+      <c r="S43" t="s">
+        <v>167</v>
+      </c>
+      <c r="T43" t="s">
+        <v>210</v>
+      </c>
+      <c r="V43" t="s">
+        <v>86</v>
+      </c>
+      <c r="W43" t="s">
+        <v>166</v>
+      </c>
+      <c r="X43" t="s">
+        <v>167</v>
+      </c>
+      <c r="Y43" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="44" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="B44" t="s">
+        <v>86</v>
+      </c>
+      <c r="C44" t="s">
+        <v>154</v>
+      </c>
+      <c r="D44" t="s">
+        <v>155</v>
+      </c>
+      <c r="E44" t="s">
+        <v>89</v>
+      </c>
+      <c r="G44" t="s">
+        <v>86</v>
+      </c>
+      <c r="H44" t="s">
+        <v>150</v>
+      </c>
+      <c r="I44" t="s">
+        <v>151</v>
+      </c>
+      <c r="J44" t="s">
+        <v>168</v>
+      </c>
+      <c r="L44" t="s">
+        <v>86</v>
+      </c>
+      <c r="M44" t="s">
+        <v>126</v>
+      </c>
+      <c r="N44" t="s">
+        <v>127</v>
+      </c>
+      <c r="O44" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="45" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="B45" t="s">
+        <v>86</v>
+      </c>
+      <c r="C45" t="s">
+        <v>156</v>
+      </c>
+      <c r="D45" t="s">
+        <v>157</v>
+      </c>
+      <c r="E45" t="s">
+        <v>89</v>
+      </c>
+      <c r="G45" t="s">
+        <v>86</v>
+      </c>
+      <c r="H45" t="s">
+        <v>152</v>
+      </c>
+      <c r="I45" t="s">
+        <v>153</v>
+      </c>
+      <c r="J45" t="s">
+        <v>168</v>
+      </c>
+      <c r="L45" t="s">
+        <v>86</v>
+      </c>
+      <c r="M45" t="s">
+        <v>198</v>
+      </c>
+      <c r="N45" t="s">
+        <v>199</v>
+      </c>
+      <c r="O45" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="46" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="B46" t="s">
+        <v>86</v>
+      </c>
+      <c r="C46" t="s">
+        <v>158</v>
+      </c>
+      <c r="D46" t="s">
+        <v>159</v>
+      </c>
+      <c r="E46" t="s">
+        <v>89</v>
+      </c>
+      <c r="G46" t="s">
+        <v>86</v>
+      </c>
+      <c r="H46" t="s">
+        <v>169</v>
+      </c>
+      <c r="I46" t="s">
+        <v>170</v>
+      </c>
+      <c r="J46" t="s">
+        <v>168</v>
+      </c>
+      <c r="L46" t="s">
+        <v>86</v>
+      </c>
+      <c r="M46" t="s">
+        <v>200</v>
+      </c>
+      <c r="N46" t="s">
+        <v>201</v>
+      </c>
+      <c r="O46" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="47" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="B47" t="s">
+        <v>86</v>
+      </c>
+      <c r="C47" t="s">
+        <v>160</v>
+      </c>
+      <c r="D47" t="s">
+        <v>161</v>
+      </c>
+      <c r="E47" t="s">
+        <v>89</v>
+      </c>
+      <c r="G47" t="s">
+        <v>86</v>
+      </c>
+      <c r="H47" t="s">
+        <v>171</v>
+      </c>
+      <c r="I47" t="s">
+        <v>172</v>
+      </c>
+      <c r="J47" t="s">
+        <v>168</v>
+      </c>
+      <c r="L47" t="s">
+        <v>86</v>
+      </c>
+      <c r="M47" t="s">
+        <v>92</v>
+      </c>
+      <c r="N47" t="s">
+        <v>93</v>
+      </c>
+      <c r="O47" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="48" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="B48" t="s">
+        <v>86</v>
+      </c>
+      <c r="C48" t="s">
+        <v>162</v>
+      </c>
+      <c r="D48" t="s">
+        <v>163</v>
+      </c>
+      <c r="E48" t="s">
+        <v>89</v>
+      </c>
+      <c r="G48" t="s">
+        <v>86</v>
+      </c>
+      <c r="H48" t="s">
+        <v>173</v>
+      </c>
+      <c r="I48" t="s">
+        <v>174</v>
+      </c>
+      <c r="J48" t="s">
+        <v>168</v>
+      </c>
+      <c r="L48" t="s">
+        <v>86</v>
+      </c>
+      <c r="M48" t="s">
+        <v>148</v>
+      </c>
+      <c r="N48" t="s">
+        <v>149</v>
+      </c>
+      <c r="O48" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="49" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B49" t="s">
+        <v>86</v>
+      </c>
+      <c r="C49" t="s">
+        <v>164</v>
+      </c>
+      <c r="D49" t="s">
+        <v>165</v>
+      </c>
+      <c r="E49" t="s">
+        <v>89</v>
+      </c>
+      <c r="G49" t="s">
+        <v>86</v>
+      </c>
+      <c r="H49" t="s">
+        <v>156</v>
+      </c>
+      <c r="I49" t="s">
+        <v>157</v>
+      </c>
+      <c r="J49" t="s">
+        <v>168</v>
+      </c>
+      <c r="L49" t="s">
+        <v>86</v>
+      </c>
+      <c r="M49" t="s">
+        <v>94</v>
+      </c>
+      <c r="N49" t="s">
+        <v>95</v>
+      </c>
+      <c r="O49" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="50" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B50" t="s">
+        <v>86</v>
+      </c>
+      <c r="C50" t="s">
+        <v>166</v>
+      </c>
+      <c r="D50" t="s">
+        <v>167</v>
+      </c>
+      <c r="E50" t="s">
+        <v>89</v>
+      </c>
+      <c r="G50" t="s">
+        <v>86</v>
+      </c>
+      <c r="H50" t="s">
+        <v>160</v>
+      </c>
+      <c r="I50" t="s">
+        <v>161</v>
+      </c>
+      <c r="J50" t="s">
+        <v>168</v>
+      </c>
+      <c r="L50" t="s">
+        <v>86</v>
+      </c>
+      <c r="M50" t="s">
+        <v>202</v>
+      </c>
+      <c r="N50" t="s">
+        <v>203</v>
+      </c>
+      <c r="O50" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="51" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="G51" t="s">
+        <v>86</v>
+      </c>
+      <c r="H51" t="s">
+        <v>162</v>
+      </c>
+      <c r="I51" t="s">
+        <v>163</v>
+      </c>
+      <c r="J51" t="s">
+        <v>168</v>
+      </c>
+      <c r="L51" t="s">
+        <v>86</v>
+      </c>
+      <c r="M51" t="s">
+        <v>171</v>
+      </c>
+      <c r="N51" t="s">
+        <v>172</v>
+      </c>
+      <c r="O51" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="52" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="G52" t="s">
+        <v>86</v>
+      </c>
+      <c r="H52" t="s">
+        <v>164</v>
+      </c>
+      <c r="I52" t="s">
+        <v>165</v>
+      </c>
+      <c r="J52" t="s">
+        <v>168</v>
+      </c>
+      <c r="L52" t="s">
+        <v>86</v>
+      </c>
+      <c r="M52" t="s">
+        <v>140</v>
+      </c>
+      <c r="N52" t="s">
+        <v>141</v>
+      </c>
+      <c r="O52" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="53" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="G53" t="s">
+        <v>86</v>
+      </c>
+      <c r="H53" t="s">
+        <v>166</v>
+      </c>
+      <c r="I53" t="s">
+        <v>167</v>
+      </c>
+      <c r="J53" t="s">
+        <v>168</v>
+      </c>
+      <c r="L53" t="s">
+        <v>86</v>
+      </c>
+      <c r="M53" t="s">
+        <v>90</v>
+      </c>
+      <c r="N53" t="s">
+        <v>91</v>
+      </c>
+      <c r="O53" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="54" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="G54" t="s">
+        <v>86</v>
+      </c>
+      <c r="H54" t="s">
+        <v>175</v>
+      </c>
+      <c r="I54" t="s">
+        <v>176</v>
+      </c>
+      <c r="J54" t="s">
+        <v>168</v>
+      </c>
+      <c r="L54" t="s">
+        <v>86</v>
+      </c>
+      <c r="M54" t="s">
+        <v>128</v>
+      </c>
+      <c r="N54" t="s">
+        <v>129</v>
+      </c>
+      <c r="O54" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="55" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="G55" t="s">
+        <v>86</v>
+      </c>
+      <c r="H55" t="s">
+        <v>177</v>
+      </c>
+      <c r="I55" t="s">
+        <v>178</v>
+      </c>
+      <c r="J55" t="s">
+        <v>168</v>
+      </c>
+      <c r="L55" t="s">
+        <v>86</v>
+      </c>
+      <c r="M55" t="s">
+        <v>132</v>
+      </c>
+      <c r="N55" t="s">
+        <v>133</v>
+      </c>
+      <c r="O55" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="56" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="G56" t="s">
+        <v>86</v>
+      </c>
+      <c r="H56" t="s">
+        <v>179</v>
+      </c>
+      <c r="I56" t="s">
+        <v>180</v>
+      </c>
+      <c r="J56" t="s">
+        <v>168</v>
+      </c>
+      <c r="L56" t="s">
+        <v>86</v>
+      </c>
+      <c r="M56" t="s">
+        <v>204</v>
+      </c>
+      <c r="N56" t="s">
+        <v>205</v>
+      </c>
+      <c r="O56" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="57" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="G57" t="s">
+        <v>86</v>
+      </c>
+      <c r="H57" t="s">
+        <v>181</v>
+      </c>
+      <c r="I57" t="s">
+        <v>182</v>
+      </c>
+      <c r="J57" t="s">
+        <v>168</v>
+      </c>
+      <c r="L57" t="s">
+        <v>86</v>
+      </c>
+      <c r="M57" t="s">
+        <v>181</v>
+      </c>
+      <c r="N57" t="s">
+        <v>182</v>
+      </c>
+      <c r="O57" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="58" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="L58" t="s">
+        <v>86</v>
+      </c>
+      <c r="M58" t="s">
+        <v>104</v>
+      </c>
+      <c r="N58" t="s">
+        <v>105</v>
+      </c>
+      <c r="O58" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="59" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="L59" t="s">
+        <v>86</v>
+      </c>
+      <c r="M59" t="s">
+        <v>87</v>
+      </c>
+      <c r="N59" t="s">
+        <v>88</v>
+      </c>
+      <c r="O59" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="60" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="L60" t="s">
+        <v>86</v>
+      </c>
+      <c r="M60" t="s">
+        <v>156</v>
+      </c>
+      <c r="N60" t="s">
+        <v>157</v>
+      </c>
+      <c r="O60" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="61" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="L61" t="s">
+        <v>86</v>
+      </c>
+      <c r="M61" t="s">
+        <v>120</v>
+      </c>
+      <c r="N61" t="s">
+        <v>121</v>
+      </c>
+      <c r="O61" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="62" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="L62" t="s">
+        <v>86</v>
+      </c>
+      <c r="M62" t="s">
+        <v>114</v>
+      </c>
+      <c r="N62" t="s">
+        <v>115</v>
+      </c>
+      <c r="O62" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="63" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="L63" t="s">
+        <v>86</v>
+      </c>
+      <c r="M63" t="s">
         <v>144</v>
       </c>
-      <c r="I43" t="s">
+      <c r="N63" t="s">
         <v>145</v>
       </c>
-      <c r="J43" t="s">
-        <v>154</v>
-      </c>
-      <c r="L43" t="s">
-        <v>86</v>
-      </c>
-      <c r="M43" t="s">
-        <v>100</v>
-      </c>
-      <c r="N43" t="s">
-        <v>101</v>
-      </c>
-      <c r="O43" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="44" spans="2:25" x14ac:dyDescent="0.45">
-      <c r="G44" t="s">
-        <v>86</v>
-      </c>
-      <c r="H44" t="s">
-        <v>148</v>
-      </c>
-      <c r="I44" t="s">
-        <v>149</v>
-      </c>
-      <c r="J44" t="s">
-        <v>154</v>
-      </c>
-      <c r="L44" t="s">
-        <v>86</v>
-      </c>
-      <c r="M44" t="s">
+      <c r="O63" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="64" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="L64" t="s">
+        <v>86</v>
+      </c>
+      <c r="M64" t="s">
         <v>122</v>
       </c>
-      <c r="N44" t="s">
+      <c r="N64" t="s">
         <v>123</v>
       </c>
-      <c r="O44" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="45" spans="2:25" x14ac:dyDescent="0.45">
-      <c r="G45" t="s">
-        <v>86</v>
-      </c>
-      <c r="H45" t="s">
-        <v>150</v>
-      </c>
-      <c r="I45" t="s">
-        <v>151</v>
-      </c>
-      <c r="J45" t="s">
-        <v>154</v>
-      </c>
-      <c r="L45" t="s">
-        <v>86</v>
-      </c>
-      <c r="M45" t="s">
-        <v>146</v>
-      </c>
-      <c r="N45" t="s">
-        <v>147</v>
-      </c>
-      <c r="O45" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="46" spans="2:25" x14ac:dyDescent="0.45">
-      <c r="G46" t="s">
-        <v>86</v>
-      </c>
-      <c r="H46" t="s">
-        <v>152</v>
-      </c>
-      <c r="I46" t="s">
-        <v>153</v>
-      </c>
-      <c r="J46" t="s">
-        <v>154</v>
-      </c>
-      <c r="L46" t="s">
-        <v>86</v>
-      </c>
-      <c r="M46" t="s">
+      <c r="O64" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="65" spans="12:15" x14ac:dyDescent="0.25">
+      <c r="L65" t="s">
+        <v>86</v>
+      </c>
+      <c r="M65" t="s">
         <v>112</v>
       </c>
-      <c r="N46" t="s">
+      <c r="N65" t="s">
         <v>113</v>
       </c>
-      <c r="O46" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="47" spans="2:25" x14ac:dyDescent="0.45">
-      <c r="G47" t="s">
-        <v>86</v>
-      </c>
-      <c r="H47" t="s">
-        <v>161</v>
-      </c>
-      <c r="I47" t="s">
-        <v>162</v>
-      </c>
-      <c r="J47" t="s">
-        <v>154</v>
-      </c>
-      <c r="L47" t="s">
-        <v>86</v>
-      </c>
-      <c r="M47" t="s">
+      <c r="O65" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="66" spans="12:15" x14ac:dyDescent="0.25">
+      <c r="L66" t="s">
+        <v>86</v>
+      </c>
+      <c r="M66" t="s">
         <v>110</v>
       </c>
-      <c r="N47" t="s">
+      <c r="N66" t="s">
         <v>111</v>
       </c>
-      <c r="O47" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="48" spans="2:25" x14ac:dyDescent="0.45">
-      <c r="G48" t="s">
-        <v>86</v>
-      </c>
-      <c r="H48" t="s">
-        <v>163</v>
-      </c>
-      <c r="I48" t="s">
+      <c r="O66" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="67" spans="12:15" x14ac:dyDescent="0.25">
+      <c r="L67" t="s">
+        <v>86</v>
+      </c>
+      <c r="M67" t="s">
+        <v>158</v>
+      </c>
+      <c r="N67" t="s">
+        <v>159</v>
+      </c>
+      <c r="O67" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="68" spans="12:15" x14ac:dyDescent="0.25">
+      <c r="L68" t="s">
+        <v>86</v>
+      </c>
+      <c r="M68" t="s">
+        <v>206</v>
+      </c>
+      <c r="N68" t="s">
+        <v>207</v>
+      </c>
+      <c r="O68" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="69" spans="12:15" x14ac:dyDescent="0.25">
+      <c r="L69" t="s">
+        <v>86</v>
+      </c>
+      <c r="M69" t="s">
         <v>164</v>
       </c>
-      <c r="J48" t="s">
-        <v>154</v>
-      </c>
-      <c r="L48" t="s">
-        <v>86</v>
-      </c>
-      <c r="M48" t="s">
-        <v>180</v>
-      </c>
-      <c r="N48" t="s">
-        <v>181</v>
-      </c>
-      <c r="O48" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="49" spans="7:15" x14ac:dyDescent="0.45">
-      <c r="G49" t="s">
-        <v>86</v>
-      </c>
-      <c r="H49" t="s">
+      <c r="N69" t="s">
         <v>165</v>
       </c>
-      <c r="I49" t="s">
-        <v>166</v>
-      </c>
-      <c r="J49" t="s">
-        <v>154</v>
-      </c>
-      <c r="L49" t="s">
-        <v>86</v>
-      </c>
-      <c r="M49" t="s">
-        <v>148</v>
-      </c>
-      <c r="N49" t="s">
-        <v>149</v>
-      </c>
-      <c r="O49" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="50" spans="7:15" x14ac:dyDescent="0.45">
-      <c r="L50" t="s">
-        <v>86</v>
-      </c>
-      <c r="M50" t="s">
-        <v>159</v>
-      </c>
-      <c r="N50" t="s">
-        <v>160</v>
-      </c>
-      <c r="O50" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="51" spans="7:15" x14ac:dyDescent="0.45">
-      <c r="L51" t="s">
-        <v>86</v>
-      </c>
-      <c r="M51" t="s">
-        <v>182</v>
-      </c>
-      <c r="N51" t="s">
-        <v>183</v>
-      </c>
-      <c r="O51" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="52" spans="7:15" x14ac:dyDescent="0.45">
-      <c r="L52" t="s">
-        <v>86</v>
-      </c>
-      <c r="M52" t="s">
-        <v>134</v>
-      </c>
-      <c r="N52" t="s">
-        <v>135</v>
-      </c>
-      <c r="O52" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="53" spans="7:15" x14ac:dyDescent="0.45">
-      <c r="L53" t="s">
-        <v>86</v>
-      </c>
-      <c r="M53" t="s">
-        <v>87</v>
-      </c>
-      <c r="N53" t="s">
-        <v>88</v>
-      </c>
-      <c r="O53" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="54" spans="7:15" x14ac:dyDescent="0.45">
-      <c r="L54" t="s">
-        <v>86</v>
-      </c>
-      <c r="M54" t="s">
-        <v>184</v>
-      </c>
-      <c r="N54" t="s">
-        <v>185</v>
-      </c>
-      <c r="O54" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="55" spans="7:15" x14ac:dyDescent="0.45">
-      <c r="L55" t="s">
-        <v>86</v>
-      </c>
-      <c r="M55" t="s">
-        <v>102</v>
-      </c>
-      <c r="N55" t="s">
-        <v>103</v>
-      </c>
-      <c r="O55" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="56" spans="7:15" x14ac:dyDescent="0.45">
-      <c r="L56" t="s">
-        <v>86</v>
-      </c>
-      <c r="M56" t="s">
-        <v>126</v>
-      </c>
-      <c r="N56" t="s">
-        <v>127</v>
-      </c>
-      <c r="O56" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="57" spans="7:15" x14ac:dyDescent="0.45">
-      <c r="L57" t="s">
-        <v>86</v>
-      </c>
-      <c r="M57" t="s">
-        <v>165</v>
-      </c>
-      <c r="N57" t="s">
-        <v>166</v>
-      </c>
-      <c r="O57" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="58" spans="7:15" x14ac:dyDescent="0.45">
-      <c r="L58" t="s">
-        <v>86</v>
-      </c>
-      <c r="M58" t="s">
-        <v>155</v>
-      </c>
-      <c r="N58" t="s">
-        <v>156</v>
-      </c>
-      <c r="O58" t="s">
-        <v>169</v>
+      <c r="O69" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="70" spans="12:15" x14ac:dyDescent="0.25">
+      <c r="L70" t="s">
+        <v>86</v>
+      </c>
+      <c r="M70" t="s">
+        <v>208</v>
+      </c>
+      <c r="N70" t="s">
+        <v>209</v>
+      </c>
+      <c r="O70" t="s">
+        <v>185</v>
       </c>
     </row>
   </sheetData>
@@ -3313,21 +3829,21 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3954DD3-0F24-46DF-B268-7A98442D0282}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="7.265625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.73046875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.59765625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="29.796875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.59765625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.59765625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.6640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.19921875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="7.46484375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="4.9296875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="3.86328125" bestFit="1" customWidth="1"/>
-    <col min="12" max="14" width="4.73046875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="5.1328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="29.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="7.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="5" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="3.85546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="14" width="4.7109375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="5.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3337,28 +3853,28 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="C4:X57"/>
-  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="13.3984375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.73046875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.7109375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="4.86328125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.3984375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="5.3984375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="5.73046875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="4.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="5.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="5.7109375" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="5" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="6.265625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="4.265625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="16.86328125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="12.3984375" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="7.6640625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="8.59765625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="10.73046875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="4.28515625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="16.85546875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="10.7109375" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="10" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="9.06640625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="9" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="3:24" x14ac:dyDescent="0.45">
+    <row r="4" spans="3:24" x14ac:dyDescent="0.25">
       <c r="C4" t="s">
         <v>4</v>
       </c>
@@ -3372,7 +3888,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="3:24" x14ac:dyDescent="0.45">
+    <row r="5" spans="3:24" x14ac:dyDescent="0.25">
       <c r="C5" t="s">
         <v>3</v>
       </c>
@@ -3398,7 +3914,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="6" spans="3:24" x14ac:dyDescent="0.45">
+    <row r="6" spans="3:24" x14ac:dyDescent="0.25">
       <c r="D6" t="s">
         <v>6</v>
       </c>
@@ -3418,7 +3934,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="7" spans="3:24" x14ac:dyDescent="0.45">
+    <row r="7" spans="3:24" x14ac:dyDescent="0.25">
       <c r="D7" t="s">
         <v>7</v>
       </c>
@@ -3438,7 +3954,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="8" spans="3:24" x14ac:dyDescent="0.45">
+    <row r="8" spans="3:24" x14ac:dyDescent="0.25">
       <c r="D8" t="s">
         <v>8</v>
       </c>
@@ -3449,7 +3965,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="3:24" x14ac:dyDescent="0.45">
+    <row r="9" spans="3:24" x14ac:dyDescent="0.25">
       <c r="D9" t="s">
         <v>9</v>
       </c>
@@ -3460,7 +3976,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="10" spans="3:24" x14ac:dyDescent="0.45">
+    <row r="10" spans="3:24" x14ac:dyDescent="0.25">
       <c r="D10" t="s">
         <v>10</v>
       </c>
@@ -3474,7 +3990,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="11" spans="3:24" x14ac:dyDescent="0.45">
+    <row r="11" spans="3:24" x14ac:dyDescent="0.25">
       <c r="D11" t="s">
         <v>6</v>
       </c>
@@ -3500,7 +4016,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="12" spans="3:24" x14ac:dyDescent="0.45">
+    <row r="12" spans="3:24" x14ac:dyDescent="0.25">
       <c r="P12" s="2" t="s">
         <v>26</v>
       </c>
@@ -3517,7 +4033,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="13" spans="3:24" x14ac:dyDescent="0.45">
+    <row r="13" spans="3:24" x14ac:dyDescent="0.25">
       <c r="C13" t="s">
         <v>4</v>
       </c>
@@ -3543,7 +4059,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="14" spans="3:24" x14ac:dyDescent="0.45">
+    <row r="14" spans="3:24" x14ac:dyDescent="0.25">
       <c r="C14" t="s">
         <v>3</v>
       </c>
@@ -3581,7 +4097,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="15" spans="3:24" x14ac:dyDescent="0.45">
+    <row r="15" spans="3:24" x14ac:dyDescent="0.25">
       <c r="C15" t="s">
         <v>11</v>
       </c>
@@ -3619,7 +4135,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="16" spans="3:24" x14ac:dyDescent="0.45">
+    <row r="16" spans="3:24" x14ac:dyDescent="0.25">
       <c r="D16" t="s">
         <v>6</v>
       </c>
@@ -3651,7 +4167,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="17" spans="3:24" x14ac:dyDescent="0.45">
+    <row r="17" spans="3:24" x14ac:dyDescent="0.25">
       <c r="D17" t="s">
         <v>13</v>
       </c>
@@ -3685,7 +4201,7 @@
         <v>EN[_]Hydro*</v>
       </c>
     </row>
-    <row r="18" spans="3:24" x14ac:dyDescent="0.45">
+    <row r="18" spans="3:24" x14ac:dyDescent="0.25">
       <c r="D18" t="s">
         <v>13</v>
       </c>
@@ -3719,7 +4235,7 @@
         <v>E[_]SPV*</v>
       </c>
     </row>
-    <row r="19" spans="3:24" x14ac:dyDescent="0.45">
+    <row r="19" spans="3:24" x14ac:dyDescent="0.25">
       <c r="D19" t="s">
         <v>7</v>
       </c>
@@ -3753,7 +4269,7 @@
         <v>E[_]WOF*</v>
       </c>
     </row>
-    <row r="20" spans="3:24" x14ac:dyDescent="0.45">
+    <row r="20" spans="3:24" x14ac:dyDescent="0.25">
       <c r="D20" t="s">
         <v>8</v>
       </c>
@@ -3787,7 +4303,7 @@
         <v>E[_]WON*</v>
       </c>
     </row>
-    <row r="21" spans="3:24" x14ac:dyDescent="0.45">
+    <row r="21" spans="3:24" x14ac:dyDescent="0.25">
       <c r="D21" t="s">
         <v>9</v>
       </c>
@@ -3821,7 +4337,7 @@
         <v>EN[_]Hydro*</v>
       </c>
     </row>
-    <row r="22" spans="3:24" x14ac:dyDescent="0.45">
+    <row r="22" spans="3:24" x14ac:dyDescent="0.25">
       <c r="D22" t="s">
         <v>10</v>
       </c>
@@ -3855,7 +4371,7 @@
         <v>E[_]SPV*</v>
       </c>
     </row>
-    <row r="23" spans="3:24" x14ac:dyDescent="0.45">
+    <row r="23" spans="3:24" x14ac:dyDescent="0.25">
       <c r="P23" s="2" t="s">
         <v>30</v>
       </c>
@@ -3880,7 +4396,7 @@
         <v>E[_]WOF*</v>
       </c>
     </row>
-    <row r="24" spans="3:24" x14ac:dyDescent="0.45">
+    <row r="24" spans="3:24" x14ac:dyDescent="0.25">
       <c r="P24" s="2" t="s">
         <v>30</v>
       </c>
@@ -3906,12 +4422,12 @@
         <v>E[_]WON*</v>
       </c>
     </row>
-    <row r="27" spans="3:24" x14ac:dyDescent="0.45">
+    <row r="27" spans="3:24" x14ac:dyDescent="0.25">
       <c r="C27" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="28" spans="3:24" x14ac:dyDescent="0.45">
+    <row r="28" spans="3:24" x14ac:dyDescent="0.25">
       <c r="C28" t="s">
         <v>16</v>
       </c>
@@ -3931,7 +4447,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="29" spans="3:24" x14ac:dyDescent="0.45">
+    <row r="29" spans="3:24" x14ac:dyDescent="0.25">
       <c r="C29" t="s">
         <v>76</v>
       </c>
@@ -3942,7 +4458,7 @@
         <v>8.76</v>
       </c>
     </row>
-    <row r="30" spans="3:24" x14ac:dyDescent="0.45">
+    <row r="30" spans="3:24" x14ac:dyDescent="0.25">
       <c r="C30" t="s">
         <v>37</v>
       </c>
@@ -3956,7 +4472,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="31" spans="3:24" x14ac:dyDescent="0.45">
+    <row r="31" spans="3:24" x14ac:dyDescent="0.25">
       <c r="D31" t="s">
         <v>7</v>
       </c>
@@ -3967,7 +4483,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="32" spans="3:24" x14ac:dyDescent="0.45">
+    <row r="32" spans="3:24" x14ac:dyDescent="0.25">
       <c r="D32" t="s">
         <v>10</v>
       </c>
@@ -3978,7 +4494,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="33" spans="3:22" x14ac:dyDescent="0.45">
+    <row r="33" spans="3:22" x14ac:dyDescent="0.25">
       <c r="D33" t="s">
         <v>9</v>
       </c>
@@ -3989,7 +4505,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="3:22" x14ac:dyDescent="0.45">
+    <row r="34" spans="3:22" x14ac:dyDescent="0.25">
       <c r="C34" t="s">
         <v>17</v>
       </c>
@@ -4003,7 +4519,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="35" spans="3:22" x14ac:dyDescent="0.45">
+    <row r="35" spans="3:22" x14ac:dyDescent="0.25">
       <c r="C35" t="s">
         <v>85</v>
       </c>
@@ -4014,7 +4530,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="38" spans="3:22" ht="17.25" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="38" spans="3:22" ht="18" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C38" t="s">
         <v>19</v>
       </c>
@@ -4022,7 +4538,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="39" spans="3:22" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="39" spans="3:22" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C39" t="s">
         <v>20</v>
       </c>
@@ -4054,7 +4570,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="40" spans="3:22" x14ac:dyDescent="0.45">
+    <row r="40" spans="3:22" x14ac:dyDescent="0.25">
       <c r="C40" t="s">
         <v>14</v>
       </c>
@@ -4086,7 +4602,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="41" spans="3:22" x14ac:dyDescent="0.45">
+    <row r="41" spans="3:22" x14ac:dyDescent="0.25">
       <c r="C41" t="s">
         <v>15</v>
       </c>
@@ -4097,7 +4613,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="42" spans="3:22" x14ac:dyDescent="0.45">
+    <row r="42" spans="3:22" x14ac:dyDescent="0.25">
       <c r="C42" t="s">
         <v>41</v>
       </c>
@@ -4108,7 +4624,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="43" spans="3:22" ht="17.25" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="43" spans="3:22" ht="18" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C43" t="s">
         <v>39</v>
       </c>
@@ -4122,7 +4638,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="44" spans="3:22" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="44" spans="3:22" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C44" t="s">
         <v>40</v>
       </c>
@@ -4145,7 +4661,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="45" spans="3:22" x14ac:dyDescent="0.45">
+    <row r="45" spans="3:22" x14ac:dyDescent="0.25">
       <c r="P45" t="s">
         <v>81</v>
       </c>
@@ -4159,12 +4675,12 @@
         <v>80</v>
       </c>
     </row>
-    <row r="47" spans="3:22" x14ac:dyDescent="0.45">
+    <row r="47" spans="3:22" x14ac:dyDescent="0.25">
       <c r="C47" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="48" spans="3:22" x14ac:dyDescent="0.45">
+    <row r="48" spans="3:22" x14ac:dyDescent="0.25">
       <c r="C48" t="s">
         <v>1</v>
       </c>
@@ -4181,7 +4697,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="49" spans="3:13" x14ac:dyDescent="0.45">
+    <row r="49" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C49" t="s">
         <v>48</v>
       </c>
@@ -4198,7 +4714,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="50" spans="3:13" x14ac:dyDescent="0.45">
+    <row r="50" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C50" t="s">
         <v>53</v>
       </c>
@@ -4212,7 +4728,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="51" spans="3:13" x14ac:dyDescent="0.45">
+    <row r="51" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C51" t="s">
         <v>48</v>
       </c>
@@ -4223,12 +4739,12 @@
         <v>75</v>
       </c>
     </row>
-    <row r="54" spans="3:13" x14ac:dyDescent="0.45">
+    <row r="54" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C54" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="55" spans="3:13" x14ac:dyDescent="0.45">
+    <row r="55" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C55" t="s">
         <v>24</v>
       </c>
@@ -4263,7 +4779,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="56" spans="3:13" x14ac:dyDescent="0.45">
+    <row r="56" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C56" t="s">
         <v>62</v>
       </c>
@@ -4283,7 +4799,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="57" spans="3:13" x14ac:dyDescent="0.45">
+    <row r="57" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C57" t="s">
         <v>62</v>
       </c>

--- a/VerveStacks_POL_grids_kan50/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_POL_grids_kan50/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25928"/>
   <workbookPr updateLinks="never"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan51\SubRES_Tmpl\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC5F1B94-8D46-464F-BCD1-844899099654}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06207D76-FEBF-44F4-BE86-8127EF830D95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="368" yWindow="368" windowWidth="21599" windowHeight="12772" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AVA" sheetId="6" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1068" uniqueCount="212">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="928" uniqueCount="188">
   <si>
     <t>PSET_PN</t>
   </si>
@@ -307,13 +307,13 @@
     <t>at grid node - Gdynia_POL</t>
   </si>
   <si>
-    <t>en_gas_ccgt,en_gas_turbine,en_chp_gas_cc_ext,en_gas_ccs,en_coal_subcritical,en_coal_supercritical,en_coal_ultrasupercritical,en_coal_igcc,en_nuclear,en_nuclear_smr,en_biomass,en_chp_biomass_chips_ext,en_biomass_ccs,en_chp_biomass_pellets_ext_ccs,en_hop_gas_boiler,en_hop_biomass_chips,en_hop_electric_boiler,en_hp_air_10mw,en_chp_gas_cc_ext_ccs</t>
-  </si>
-  <si>
-    <t>Giszowiec_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Giszowiec_POL</t>
+    <t>en_gas_ccgt,en_gas_turbine,en_chp_gas_cc_ext,en_gas_ccs,en_coal_subcritical,en_coal_supercritical,en_coal_ultrasupercritical,en_coal_igcc,en_nuclear,en_nuclear_smr,en_biomass,en_chp_biomass_chips_ext,en_hop_gas_boiler,en_hop_biomass_chips,en_hop_electric_boiler,en_hp_air_10mw,en_chp_gas_cc_ext_ccs</t>
+  </si>
+  <si>
+    <t>Katowice_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Katowice_POL</t>
   </si>
   <si>
     <t>Radomsko_POL</t>
@@ -322,16 +322,10 @@
     <t>at grid node - Radomsko_POL</t>
   </si>
   <si>
-    <t>Swarzedz_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Swarzedz_POL</t>
-  </si>
-  <si>
-    <t>SiemianowiceSlaski_POL</t>
-  </si>
-  <si>
-    <t>at grid node - SiemianowiceSlaski_POL</t>
+    <t>Poznan_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Poznan_POL</t>
   </si>
   <si>
     <t>Krakow_POL</t>
@@ -340,10 +334,28 @@
     <t>at grid node - Krakow_POL</t>
   </si>
   <si>
-    <t>Staszow_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Staszow_POL</t>
+    <t>Mielec_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Mielec_POL</t>
+  </si>
+  <si>
+    <t>Lomza_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Lomza_POL</t>
+  </si>
+  <si>
+    <t>Wloclawek_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Wloclawek_POL</t>
+  </si>
+  <si>
+    <t>Konin_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Konin_POL</t>
   </si>
   <si>
     <t>Sosnowiec_POL</t>
@@ -352,22 +364,157 @@
     <t>at grid node - Sosnowiec_POL</t>
   </si>
   <si>
-    <t>Kolno_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Kolno_POL</t>
-  </si>
-  <si>
-    <t>Wloclawek_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Wloclawek_POL</t>
-  </si>
-  <si>
-    <t>Konin_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Konin_POL</t>
+    <t>Bydgoszcz_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Bydgoszcz_POL</t>
+  </si>
+  <si>
+    <t>Szczecin_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Szczecin_POL</t>
+  </si>
+  <si>
+    <t>Gdansk_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Gdansk_POL</t>
+  </si>
+  <si>
+    <t>GorzowWielkopolski_POL</t>
+  </si>
+  <si>
+    <t>at grid node - GorzowWielkopolski_POL</t>
+  </si>
+  <si>
+    <t>Grudziadz_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Grudziadz_POL</t>
+  </si>
+  <si>
+    <t>Lubin_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Lubin_POL</t>
+  </si>
+  <si>
+    <t>Olesnica_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Olesnica_POL</t>
+  </si>
+  <si>
+    <t>Pulawy_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Pulawy_POL</t>
+  </si>
+  <si>
+    <t>PiotrkowTrybunalsk_POL</t>
+  </si>
+  <si>
+    <t>at grid node - PiotrkowTrybunalsk_POL</t>
+  </si>
+  <si>
+    <t>Rzeszow_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Rzeszow_POL</t>
+  </si>
+  <si>
+    <t>Plock_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Plock_POL</t>
+  </si>
+  <si>
+    <t>Police_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Police_POL</t>
+  </si>
+  <si>
+    <t>Debica_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Debica_POL</t>
+  </si>
+  <si>
+    <t>Wroclaw_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Wroclaw_POL</t>
+  </si>
+  <si>
+    <t>Warsaw_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Warsaw_POL</t>
+  </si>
+  <si>
+    <t>Kwidzyn_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Kwidzyn_POL</t>
+  </si>
+  <si>
+    <t>ZielonaGora_POL</t>
+  </si>
+  <si>
+    <t>at grid node - ZielonaGora_POL</t>
+  </si>
+  <si>
+    <t>Bialystok_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Bialystok_POL</t>
+  </si>
+  <si>
+    <t>BielskoBiala_POL</t>
+  </si>
+  <si>
+    <t>at grid node - BielskoBiala_POL</t>
+  </si>
+  <si>
+    <t>Czestochowa_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Czestochowa_POL</t>
+  </si>
+  <si>
+    <t>Gliwice_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Gliwice_POL</t>
+  </si>
+  <si>
+    <t>Opole_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Opole_POL</t>
+  </si>
+  <si>
+    <t>Boleslawiec_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Boleslawiec_POL</t>
+  </si>
+  <si>
+    <t>en_battery_4h,en_battery_8h</t>
+  </si>
+  <si>
+    <t>Ustka_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Ustka_POL</t>
+  </si>
+  <si>
+    <t>Koszalin_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Koszalin_POL</t>
   </si>
   <si>
     <t>KedzierzynKozle_POL</t>
@@ -376,217 +523,49 @@
     <t>at grid node - KedzierzynKozle_POL</t>
   </si>
   <si>
-    <t>Torun_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Torun_POL</t>
-  </si>
-  <si>
-    <t>Police_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Police_POL</t>
-  </si>
-  <si>
-    <t>Rumia_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Rumia_POL</t>
-  </si>
-  <si>
-    <t>GorzowWielkopolski_POL</t>
-  </si>
-  <si>
-    <t>at grid node - GorzowWielkopolski_POL</t>
-  </si>
-  <si>
-    <t>Grudziadz_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Grudziadz_POL</t>
-  </si>
-  <si>
-    <t>NowaSol_POL</t>
-  </si>
-  <si>
-    <t>at grid node - NowaSol_POL</t>
-  </si>
-  <si>
-    <t>Kalisz_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Kalisz_POL</t>
-  </si>
-  <si>
-    <t>Radom_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Radom_POL</t>
-  </si>
-  <si>
-    <t>PiotrkowTrybunalsk_POL</t>
-  </si>
-  <si>
-    <t>at grid node - PiotrkowTrybunalsk_POL</t>
-  </si>
-  <si>
-    <t>OstrowMazowiecka_POL</t>
-  </si>
-  <si>
-    <t>at grid node - OstrowMazowiecka_POL</t>
-  </si>
-  <si>
-    <t>Tczew_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Tczew_POL</t>
-  </si>
-  <si>
-    <t>Plock_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Plock_POL</t>
-  </si>
-  <si>
-    <t>KamienPomorski_POL</t>
-  </si>
-  <si>
-    <t>at grid node - KamienPomorski_POL</t>
-  </si>
-  <si>
-    <t>Zory_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Zory_POL</t>
-  </si>
-  <si>
-    <t>Rzeszow_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Rzeszow_POL</t>
-  </si>
-  <si>
-    <t>Wroclaw_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Wroclaw_POL</t>
-  </si>
-  <si>
-    <t>Lukow_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Lukow_POL</t>
-  </si>
-  <si>
-    <t>Zabki_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Zabki_POL</t>
-  </si>
-  <si>
-    <t>Kwidzyn_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Kwidzyn_POL</t>
-  </si>
-  <si>
-    <t>Swidnik_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Swidnik_POL</t>
-  </si>
-  <si>
-    <t>ZielonaGora_POL</t>
-  </si>
-  <si>
-    <t>at grid node - ZielonaGora_POL</t>
-  </si>
-  <si>
-    <t>Bialystok_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Bialystok_POL</t>
-  </si>
-  <si>
-    <t>BielskoBiala_POL</t>
-  </si>
-  <si>
-    <t>at grid node - BielskoBiala_POL</t>
-  </si>
-  <si>
-    <t>Wloszczowa_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Wloszczowa_POL</t>
-  </si>
-  <si>
-    <t>Mikolow_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Mikolow_POL</t>
-  </si>
-  <si>
-    <t>Opole_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Opole_POL</t>
-  </si>
-  <si>
-    <t>Pulawy_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Pulawy_POL</t>
-  </si>
-  <si>
-    <t>Boleslawiec_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Boleslawiec_POL</t>
-  </si>
-  <si>
-    <t>en_battery_4h,en_battery_8h</t>
-  </si>
-  <si>
-    <t>Ustka_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Ustka_POL</t>
-  </si>
-  <si>
-    <t>Koszalin_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Koszalin_POL</t>
-  </si>
-  <si>
-    <t>Krapkowice_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Krapkowice_POL</t>
-  </si>
-  <si>
-    <t>Walbrzych_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Walbrzych_POL</t>
-  </si>
-  <si>
-    <t>Debica_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Debica_POL</t>
-  </si>
-  <si>
-    <t>Sanok_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Sanok_POL</t>
-  </si>
-  <si>
-    <t>Miastko_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Miastko_POL</t>
+    <t>Swidnica_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Swidnica_POL</t>
+  </si>
+  <si>
+    <t>Tarnow_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Tarnow_POL</t>
+  </si>
+  <si>
+    <t>Krosno_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Krosno_POL</t>
+  </si>
+  <si>
+    <t>Legnica_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Legnica_POL</t>
+  </si>
+  <si>
+    <t>e_demand,ev_battery,H2prd_Elc_PEM,H2prd_Elc_ALK</t>
+  </si>
+  <si>
+    <t>Grajewo_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Grajewo_POL</t>
+  </si>
+  <si>
+    <t>Kielce_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Kielce_POL</t>
+  </si>
+  <si>
+    <t>Slupsk_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Slupsk_POL</t>
   </si>
   <si>
     <t>OstrowiecSwietokrz_POL</t>
@@ -595,79 +574,28 @@
     <t>at grid node - OstrowiecSwietokrz_POL</t>
   </si>
   <si>
-    <t>e_demand,ev_battery,H2prd_Elc_PEM,H2prd_Elc_ALK</t>
+    <t>Olsztyn_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Olsztyn_POL</t>
+  </si>
+  <si>
+    <t>Elk_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Elk_POL</t>
+  </si>
+  <si>
+    <t>Zamosc_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Zamosc_POL</t>
   </si>
   <si>
     <t>Chelm_POL</t>
   </si>
   <si>
     <t>at grid node - Chelm_POL</t>
-  </si>
-  <si>
-    <t>Otwock_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Otwock_POL</t>
-  </si>
-  <si>
-    <t>Legnica_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Legnica_POL</t>
-  </si>
-  <si>
-    <t>Nowogard_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Nowogard_POL</t>
-  </si>
-  <si>
-    <t>Rybnik_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Rybnik_POL</t>
-  </si>
-  <si>
-    <t>Slupsk_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Slupsk_POL</t>
-  </si>
-  <si>
-    <t>Elk_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Elk_POL</t>
-  </si>
-  <si>
-    <t>Olsztyn_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Olsztyn_POL</t>
-  </si>
-  <si>
-    <t>Grajewo_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Grajewo_POL</t>
-  </si>
-  <si>
-    <t>Kielce_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Kielce_POL</t>
-  </si>
-  <si>
-    <t>TomaszowLubelski_POL</t>
-  </si>
-  <si>
-    <t>at grid node - TomaszowLubelski_POL</t>
-  </si>
-  <si>
-    <t>Wagrowiec_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Wagrowiec_POL</t>
   </si>
   <si>
     <t>h_demand</t>
@@ -1042,15 +970,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{268E9BAB-B98F-4B82-9042-51EABC9ED525}">
-  <dimension ref="B3:Y70"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="B3:Y58"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
-    <row r="3" spans="2:25" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B3" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="4" spans="2:25" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B4" t="s">
         <v>20</v>
       </c>
@@ -1058,7 +986,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="5" spans="2:25" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B5" t="s">
         <v>43</v>
       </c>
@@ -1066,7 +994,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="2:25" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B9" t="s">
         <v>69</v>
       </c>
@@ -1083,7 +1011,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="10" spans="2:25" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B10" t="s">
         <v>31</v>
       </c>
@@ -1145,7 +1073,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="2:25" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B11" t="s">
         <v>86</v>
       </c>
@@ -1162,52 +1090,52 @@
         <v>86</v>
       </c>
       <c r="H11" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
       <c r="I11" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="J11" t="s">
+        <v>154</v>
+      </c>
+      <c r="L11" t="s">
+        <v>86</v>
+      </c>
+      <c r="M11" t="s">
+        <v>167</v>
+      </c>
+      <c r="N11" t="s">
         <v>168</v>
       </c>
-      <c r="L11" t="s">
-        <v>86</v>
-      </c>
-      <c r="M11" t="s">
-        <v>183</v>
-      </c>
-      <c r="N11" t="s">
-        <v>184</v>
-      </c>
       <c r="O11" t="s">
-        <v>185</v>
+        <v>169</v>
       </c>
       <c r="Q11" t="s">
         <v>86</v>
       </c>
       <c r="R11" t="s">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="S11" t="s">
-        <v>131</v>
+        <v>101</v>
       </c>
       <c r="T11" t="s">
-        <v>210</v>
+        <v>186</v>
       </c>
       <c r="V11" t="s">
         <v>86</v>
       </c>
       <c r="W11" t="s">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="X11" t="s">
-        <v>131</v>
+        <v>101</v>
       </c>
       <c r="Y11" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="12" spans="2:25" x14ac:dyDescent="0.25">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="12" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B12" t="s">
         <v>86</v>
       </c>
@@ -1224,52 +1152,52 @@
         <v>86</v>
       </c>
       <c r="H12" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="I12" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="J12" t="s">
-        <v>168</v>
+        <v>154</v>
       </c>
       <c r="L12" t="s">
         <v>86</v>
       </c>
       <c r="M12" t="s">
-        <v>142</v>
+        <v>106</v>
       </c>
       <c r="N12" t="s">
-        <v>143</v>
+        <v>107</v>
       </c>
       <c r="O12" t="s">
-        <v>185</v>
+        <v>169</v>
       </c>
       <c r="Q12" t="s">
         <v>86</v>
       </c>
       <c r="R12" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
       <c r="S12" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="T12" t="s">
-        <v>210</v>
+        <v>186</v>
       </c>
       <c r="V12" t="s">
         <v>86</v>
       </c>
       <c r="W12" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
       <c r="X12" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="Y12" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="13" spans="2:25" x14ac:dyDescent="0.25">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="13" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B13" t="s">
         <v>86</v>
       </c>
@@ -1286,52 +1214,52 @@
         <v>86</v>
       </c>
       <c r="H13" t="s">
+        <v>142</v>
+      </c>
+      <c r="I13" t="s">
+        <v>143</v>
+      </c>
+      <c r="J13" t="s">
         <v>154</v>
       </c>
-      <c r="I13" t="s">
-        <v>155</v>
-      </c>
-      <c r="J13" t="s">
-        <v>168</v>
-      </c>
       <c r="L13" t="s">
         <v>86</v>
       </c>
       <c r="M13" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="N13" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="O13" t="s">
-        <v>185</v>
+        <v>169</v>
       </c>
       <c r="Q13" t="s">
         <v>86</v>
       </c>
       <c r="R13" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="S13" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="T13" t="s">
-        <v>210</v>
+        <v>186</v>
       </c>
       <c r="V13" t="s">
         <v>86</v>
       </c>
       <c r="W13" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="X13" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="Y13" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="14" spans="2:25" x14ac:dyDescent="0.25">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="14" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B14" t="s">
         <v>86</v>
       </c>
@@ -1348,52 +1276,52 @@
         <v>86</v>
       </c>
       <c r="H14" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="I14" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="J14" t="s">
-        <v>168</v>
+        <v>154</v>
       </c>
       <c r="L14" t="s">
         <v>86</v>
       </c>
       <c r="M14" t="s">
+        <v>172</v>
+      </c>
+      <c r="N14" t="s">
+        <v>173</v>
+      </c>
+      <c r="O14" t="s">
+        <v>169</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>86</v>
+      </c>
+      <c r="R14" t="s">
+        <v>142</v>
+      </c>
+      <c r="S14" t="s">
+        <v>143</v>
+      </c>
+      <c r="T14" t="s">
         <v>186</v>
       </c>
-      <c r="N14" t="s">
+      <c r="V14" t="s">
+        <v>86</v>
+      </c>
+      <c r="W14" t="s">
+        <v>142</v>
+      </c>
+      <c r="X14" t="s">
+        <v>143</v>
+      </c>
+      <c r="Y14" t="s">
         <v>187</v>
       </c>
-      <c r="O14" t="s">
-        <v>185</v>
-      </c>
-      <c r="Q14" t="s">
-        <v>86</v>
-      </c>
-      <c r="R14" t="s">
-        <v>154</v>
-      </c>
-      <c r="S14" t="s">
-        <v>155</v>
-      </c>
-      <c r="T14" t="s">
-        <v>210</v>
-      </c>
-      <c r="V14" t="s">
-        <v>86</v>
-      </c>
-      <c r="W14" t="s">
-        <v>154</v>
-      </c>
-      <c r="X14" t="s">
-        <v>155</v>
-      </c>
-      <c r="Y14" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="15" spans="2:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="15" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B15" t="s">
         <v>86</v>
       </c>
@@ -1416,46 +1344,46 @@
         <v>88</v>
       </c>
       <c r="J15" t="s">
-        <v>168</v>
+        <v>154</v>
       </c>
       <c r="L15" t="s">
         <v>86</v>
       </c>
       <c r="M15" t="s">
-        <v>138</v>
+        <v>94</v>
       </c>
       <c r="N15" t="s">
-        <v>139</v>
+        <v>95</v>
       </c>
       <c r="O15" t="s">
-        <v>185</v>
+        <v>169</v>
       </c>
       <c r="Q15" t="s">
         <v>86</v>
       </c>
       <c r="R15" t="s">
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="S15" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="T15" t="s">
-        <v>210</v>
+        <v>186</v>
       </c>
       <c r="V15" t="s">
         <v>86</v>
       </c>
       <c r="W15" t="s">
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="X15" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="Y15" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="16" spans="2:25" x14ac:dyDescent="0.25">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="16" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B16" t="s">
         <v>86</v>
       </c>
@@ -1478,46 +1406,46 @@
         <v>91</v>
       </c>
       <c r="J16" t="s">
-        <v>168</v>
+        <v>154</v>
       </c>
       <c r="L16" t="s">
         <v>86</v>
       </c>
       <c r="M16" t="s">
+        <v>116</v>
+      </c>
+      <c r="N16" t="s">
+        <v>117</v>
+      </c>
+      <c r="O16" t="s">
+        <v>169</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>86</v>
+      </c>
+      <c r="R16" t="s">
         <v>98</v>
       </c>
-      <c r="N16" t="s">
+      <c r="S16" t="s">
         <v>99</v>
       </c>
-      <c r="O16" t="s">
-        <v>185</v>
-      </c>
-      <c r="Q16" t="s">
-        <v>86</v>
-      </c>
-      <c r="R16" t="s">
-        <v>100</v>
-      </c>
-      <c r="S16" t="s">
-        <v>101</v>
-      </c>
       <c r="T16" t="s">
-        <v>210</v>
+        <v>186</v>
       </c>
       <c r="V16" t="s">
         <v>86</v>
       </c>
       <c r="W16" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="X16" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="Y16" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="17" spans="2:25" x14ac:dyDescent="0.25">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="17" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B17" t="s">
         <v>86</v>
       </c>
@@ -1540,46 +1468,46 @@
         <v>93</v>
       </c>
       <c r="J17" t="s">
-        <v>168</v>
+        <v>154</v>
       </c>
       <c r="L17" t="s">
         <v>86</v>
       </c>
       <c r="M17" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="N17" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="O17" t="s">
-        <v>185</v>
+        <v>169</v>
       </c>
       <c r="Q17" t="s">
         <v>86</v>
       </c>
       <c r="R17" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="S17" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="T17" t="s">
-        <v>210</v>
+        <v>186</v>
       </c>
       <c r="V17" t="s">
         <v>86</v>
       </c>
       <c r="W17" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="X17" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="Y17" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="18" spans="2:25" x14ac:dyDescent="0.25">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="18" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B18" t="s">
         <v>86</v>
       </c>
@@ -1602,46 +1530,46 @@
         <v>95</v>
       </c>
       <c r="J18" t="s">
-        <v>168</v>
+        <v>154</v>
       </c>
       <c r="L18" t="s">
         <v>86</v>
       </c>
       <c r="M18" t="s">
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="N18" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="O18" t="s">
-        <v>185</v>
+        <v>169</v>
       </c>
       <c r="Q18" t="s">
         <v>86</v>
       </c>
       <c r="R18" t="s">
-        <v>158</v>
+        <v>146</v>
       </c>
       <c r="S18" t="s">
-        <v>159</v>
+        <v>147</v>
       </c>
       <c r="T18" t="s">
-        <v>210</v>
+        <v>186</v>
       </c>
       <c r="V18" t="s">
         <v>86</v>
       </c>
       <c r="W18" t="s">
-        <v>158</v>
+        <v>146</v>
       </c>
       <c r="X18" t="s">
-        <v>159</v>
+        <v>147</v>
       </c>
       <c r="Y18" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="19" spans="2:25" x14ac:dyDescent="0.25">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="19" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B19" t="s">
         <v>86</v>
       </c>
@@ -1664,46 +1592,46 @@
         <v>97</v>
       </c>
       <c r="J19" t="s">
-        <v>168</v>
+        <v>154</v>
       </c>
       <c r="L19" t="s">
         <v>86</v>
       </c>
       <c r="M19" t="s">
-        <v>106</v>
+        <v>140</v>
       </c>
       <c r="N19" t="s">
-        <v>107</v>
+        <v>141</v>
       </c>
       <c r="O19" t="s">
-        <v>185</v>
+        <v>169</v>
       </c>
       <c r="Q19" t="s">
         <v>86</v>
       </c>
       <c r="R19" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="S19" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="T19" t="s">
-        <v>210</v>
+        <v>186</v>
       </c>
       <c r="V19" t="s">
         <v>86</v>
       </c>
       <c r="W19" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="X19" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="Y19" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="20" spans="2:25" x14ac:dyDescent="0.25">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="20" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B20" t="s">
         <v>86</v>
       </c>
@@ -1720,52 +1648,52 @@
         <v>86</v>
       </c>
       <c r="H20" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="I20" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="J20" t="s">
-        <v>168</v>
+        <v>154</v>
       </c>
       <c r="L20" t="s">
         <v>86</v>
       </c>
       <c r="M20" t="s">
-        <v>166</v>
+        <v>144</v>
       </c>
       <c r="N20" t="s">
-        <v>167</v>
+        <v>145</v>
       </c>
       <c r="O20" t="s">
-        <v>185</v>
+        <v>169</v>
       </c>
       <c r="Q20" t="s">
         <v>86</v>
       </c>
       <c r="R20" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="S20" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="T20" t="s">
-        <v>210</v>
+        <v>186</v>
       </c>
       <c r="V20" t="s">
         <v>86</v>
       </c>
       <c r="W20" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="X20" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="Y20" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="21" spans="2:25" x14ac:dyDescent="0.25">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="21" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B21" t="s">
         <v>86</v>
       </c>
@@ -1788,46 +1716,46 @@
         <v>103</v>
       </c>
       <c r="J21" t="s">
-        <v>168</v>
+        <v>154</v>
       </c>
       <c r="L21" t="s">
         <v>86</v>
       </c>
       <c r="M21" t="s">
-        <v>124</v>
+        <v>96</v>
       </c>
       <c r="N21" t="s">
-        <v>125</v>
+        <v>97</v>
       </c>
       <c r="O21" t="s">
-        <v>185</v>
+        <v>169</v>
       </c>
       <c r="Q21" t="s">
         <v>86</v>
       </c>
       <c r="R21" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="S21" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="T21" t="s">
-        <v>210</v>
+        <v>186</v>
       </c>
       <c r="V21" t="s">
         <v>86</v>
       </c>
       <c r="W21" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="X21" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="Y21" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="22" spans="2:25" x14ac:dyDescent="0.25">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="22" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B22" t="s">
         <v>86</v>
       </c>
@@ -1844,52 +1772,52 @@
         <v>86</v>
       </c>
       <c r="H22" t="s">
-        <v>104</v>
+        <v>146</v>
       </c>
       <c r="I22" t="s">
-        <v>105</v>
+        <v>147</v>
       </c>
       <c r="J22" t="s">
-        <v>168</v>
+        <v>154</v>
       </c>
       <c r="L22" t="s">
         <v>86</v>
       </c>
       <c r="M22" t="s">
-        <v>188</v>
+        <v>124</v>
       </c>
       <c r="N22" t="s">
-        <v>189</v>
+        <v>125</v>
       </c>
       <c r="O22" t="s">
-        <v>185</v>
+        <v>169</v>
       </c>
       <c r="Q22" t="s">
         <v>86</v>
       </c>
       <c r="R22" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="S22" t="s">
-        <v>97</v>
+        <v>111</v>
       </c>
       <c r="T22" t="s">
-        <v>210</v>
+        <v>186</v>
       </c>
       <c r="V22" t="s">
         <v>86</v>
       </c>
       <c r="W22" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="X22" t="s">
-        <v>97</v>
+        <v>111</v>
       </c>
       <c r="Y22" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="23" spans="2:25" x14ac:dyDescent="0.25">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="23" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B23" t="s">
         <v>86</v>
       </c>
@@ -1906,25 +1834,25 @@
         <v>86</v>
       </c>
       <c r="H23" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="I23" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="J23" t="s">
-        <v>168</v>
+        <v>154</v>
       </c>
       <c r="L23" t="s">
         <v>86</v>
       </c>
       <c r="M23" t="s">
-        <v>134</v>
+        <v>150</v>
       </c>
       <c r="N23" t="s">
-        <v>135</v>
+        <v>151</v>
       </c>
       <c r="O23" t="s">
-        <v>185</v>
+        <v>169</v>
       </c>
       <c r="Q23" t="s">
         <v>86</v>
@@ -1936,7 +1864,7 @@
         <v>115</v>
       </c>
       <c r="T23" t="s">
-        <v>210</v>
+        <v>186</v>
       </c>
       <c r="V23" t="s">
         <v>86</v>
@@ -1948,10 +1876,10 @@
         <v>115</v>
       </c>
       <c r="Y23" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="24" spans="2:25" x14ac:dyDescent="0.25">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="24" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B24" t="s">
         <v>86</v>
       </c>
@@ -1968,25 +1896,25 @@
         <v>86</v>
       </c>
       <c r="H24" t="s">
-        <v>158</v>
+        <v>106</v>
       </c>
       <c r="I24" t="s">
-        <v>159</v>
+        <v>107</v>
       </c>
       <c r="J24" t="s">
-        <v>168</v>
+        <v>154</v>
       </c>
       <c r="L24" t="s">
         <v>86</v>
       </c>
       <c r="M24" t="s">
-        <v>175</v>
+        <v>92</v>
       </c>
       <c r="N24" t="s">
-        <v>176</v>
+        <v>93</v>
       </c>
       <c r="O24" t="s">
-        <v>185</v>
+        <v>169</v>
       </c>
       <c r="Q24" t="s">
         <v>86</v>
@@ -1998,7 +1926,7 @@
         <v>119</v>
       </c>
       <c r="T24" t="s">
-        <v>210</v>
+        <v>186</v>
       </c>
       <c r="V24" t="s">
         <v>86</v>
@@ -2010,10 +1938,10 @@
         <v>119</v>
       </c>
       <c r="Y24" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="25" spans="2:25" x14ac:dyDescent="0.25">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="25" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B25" t="s">
         <v>86</v>
       </c>
@@ -2036,46 +1964,46 @@
         <v>109</v>
       </c>
       <c r="J25" t="s">
-        <v>168</v>
+        <v>154</v>
       </c>
       <c r="L25" t="s">
         <v>86</v>
       </c>
       <c r="M25" t="s">
-        <v>150</v>
+        <v>176</v>
       </c>
       <c r="N25" t="s">
-        <v>151</v>
+        <v>177</v>
       </c>
       <c r="O25" t="s">
-        <v>185</v>
+        <v>169</v>
       </c>
       <c r="Q25" t="s">
         <v>86</v>
       </c>
       <c r="R25" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="S25" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="T25" t="s">
-        <v>210</v>
+        <v>186</v>
       </c>
       <c r="V25" t="s">
         <v>86</v>
       </c>
       <c r="W25" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="X25" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="Y25" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="26" spans="2:25" x14ac:dyDescent="0.25">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="26" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B26" t="s">
         <v>86</v>
       </c>
@@ -2098,46 +2026,46 @@
         <v>111</v>
       </c>
       <c r="J26" t="s">
-        <v>168</v>
+        <v>154</v>
       </c>
       <c r="L26" t="s">
         <v>86</v>
       </c>
       <c r="M26" t="s">
-        <v>146</v>
+        <v>157</v>
       </c>
       <c r="N26" t="s">
-        <v>147</v>
+        <v>158</v>
       </c>
       <c r="O26" t="s">
-        <v>185</v>
+        <v>169</v>
       </c>
       <c r="Q26" t="s">
         <v>86</v>
       </c>
       <c r="R26" t="s">
-        <v>124</v>
+        <v>96</v>
       </c>
       <c r="S26" t="s">
-        <v>125</v>
+        <v>97</v>
       </c>
       <c r="T26" t="s">
-        <v>210</v>
+        <v>186</v>
       </c>
       <c r="V26" t="s">
         <v>86</v>
       </c>
       <c r="W26" t="s">
-        <v>124</v>
+        <v>96</v>
       </c>
       <c r="X26" t="s">
-        <v>125</v>
+        <v>97</v>
       </c>
       <c r="Y26" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="27" spans="2:25" x14ac:dyDescent="0.25">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="27" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B27" t="s">
         <v>86</v>
       </c>
@@ -2160,46 +2088,46 @@
         <v>113</v>
       </c>
       <c r="J27" t="s">
-        <v>168</v>
+        <v>154</v>
       </c>
       <c r="L27" t="s">
         <v>86</v>
       </c>
       <c r="M27" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="N27" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="O27" t="s">
-        <v>185</v>
+        <v>169</v>
       </c>
       <c r="Q27" t="s">
         <v>86</v>
       </c>
       <c r="R27" t="s">
-        <v>98</v>
+        <v>124</v>
       </c>
       <c r="S27" t="s">
-        <v>99</v>
+        <v>125</v>
       </c>
       <c r="T27" t="s">
-        <v>210</v>
+        <v>186</v>
       </c>
       <c r="V27" t="s">
         <v>86</v>
       </c>
       <c r="W27" t="s">
-        <v>98</v>
+        <v>124</v>
       </c>
       <c r="X27" t="s">
-        <v>99</v>
+        <v>125</v>
       </c>
       <c r="Y27" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="28" spans="2:25" x14ac:dyDescent="0.25">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="28" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B28" t="s">
         <v>86</v>
       </c>
@@ -2222,46 +2150,46 @@
         <v>115</v>
       </c>
       <c r="J28" t="s">
-        <v>168</v>
+        <v>154</v>
       </c>
       <c r="L28" t="s">
         <v>86</v>
       </c>
       <c r="M28" t="s">
-        <v>190</v>
+        <v>114</v>
       </c>
       <c r="N28" t="s">
-        <v>191</v>
+        <v>115</v>
       </c>
       <c r="O28" t="s">
-        <v>185</v>
+        <v>169</v>
       </c>
       <c r="Q28" t="s">
         <v>86</v>
       </c>
       <c r="R28" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="S28" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="T28" t="s">
-        <v>210</v>
+        <v>186</v>
       </c>
       <c r="V28" t="s">
         <v>86</v>
       </c>
       <c r="W28" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="X28" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="Y28" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="29" spans="2:25" x14ac:dyDescent="0.25">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="29" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B29" t="s">
         <v>86</v>
       </c>
@@ -2284,46 +2212,46 @@
         <v>117</v>
       </c>
       <c r="J29" t="s">
-        <v>168</v>
+        <v>154</v>
       </c>
       <c r="L29" t="s">
         <v>86</v>
       </c>
       <c r="M29" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="N29" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="O29" t="s">
-        <v>185</v>
+        <v>169</v>
       </c>
       <c r="Q29" t="s">
         <v>86</v>
       </c>
       <c r="R29" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="S29" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="T29" t="s">
-        <v>210</v>
+        <v>186</v>
       </c>
       <c r="V29" t="s">
         <v>86</v>
       </c>
       <c r="W29" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="X29" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="Y29" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="30" spans="2:25" x14ac:dyDescent="0.25">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="30" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B30" t="s">
         <v>86</v>
       </c>
@@ -2346,19 +2274,19 @@
         <v>119</v>
       </c>
       <c r="J30" t="s">
-        <v>168</v>
+        <v>154</v>
       </c>
       <c r="L30" t="s">
         <v>86</v>
       </c>
       <c r="M30" t="s">
-        <v>118</v>
+        <v>178</v>
       </c>
       <c r="N30" t="s">
-        <v>119</v>
+        <v>179</v>
       </c>
       <c r="O30" t="s">
-        <v>185</v>
+        <v>169</v>
       </c>
       <c r="Q30" t="s">
         <v>86</v>
@@ -2370,7 +2298,7 @@
         <v>95</v>
       </c>
       <c r="T30" t="s">
-        <v>210</v>
+        <v>186</v>
       </c>
       <c r="V30" t="s">
         <v>86</v>
@@ -2382,10 +2310,10 @@
         <v>95</v>
       </c>
       <c r="Y30" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="31" spans="2:25" x14ac:dyDescent="0.25">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="31" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B31" t="s">
         <v>86</v>
       </c>
@@ -2408,46 +2336,46 @@
         <v>121</v>
       </c>
       <c r="J31" t="s">
-        <v>168</v>
+        <v>154</v>
       </c>
       <c r="L31" t="s">
         <v>86</v>
       </c>
       <c r="M31" t="s">
-        <v>130</v>
+        <v>108</v>
       </c>
       <c r="N31" t="s">
-        <v>131</v>
+        <v>109</v>
       </c>
       <c r="O31" t="s">
-        <v>185</v>
+        <v>169</v>
       </c>
       <c r="Q31" t="s">
         <v>86</v>
       </c>
       <c r="R31" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="S31" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="T31" t="s">
-        <v>210</v>
+        <v>186</v>
       </c>
       <c r="V31" t="s">
         <v>86</v>
       </c>
       <c r="W31" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="X31" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="Y31" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="32" spans="2:25" x14ac:dyDescent="0.25">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="32" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B32" t="s">
         <v>86</v>
       </c>
@@ -2470,46 +2398,46 @@
         <v>123</v>
       </c>
       <c r="J32" t="s">
-        <v>168</v>
+        <v>154</v>
       </c>
       <c r="L32" t="s">
         <v>86</v>
       </c>
       <c r="M32" t="s">
-        <v>152</v>
+        <v>130</v>
       </c>
       <c r="N32" t="s">
-        <v>153</v>
+        <v>131</v>
       </c>
       <c r="O32" t="s">
-        <v>185</v>
+        <v>169</v>
       </c>
       <c r="Q32" t="s">
         <v>86</v>
       </c>
       <c r="R32" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="S32" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="T32" t="s">
-        <v>210</v>
+        <v>186</v>
       </c>
       <c r="V32" t="s">
         <v>86</v>
       </c>
       <c r="W32" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="X32" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="Y32" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="33" spans="2:25" x14ac:dyDescent="0.25">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="33" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B33" t="s">
         <v>86</v>
       </c>
@@ -2532,46 +2460,46 @@
         <v>125</v>
       </c>
       <c r="J33" t="s">
-        <v>168</v>
+        <v>154</v>
       </c>
       <c r="L33" t="s">
         <v>86</v>
       </c>
       <c r="M33" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="N33" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="O33" t="s">
-        <v>185</v>
+        <v>169</v>
       </c>
       <c r="Q33" t="s">
         <v>86</v>
       </c>
       <c r="R33" t="s">
-        <v>144</v>
+        <v>122</v>
       </c>
       <c r="S33" t="s">
-        <v>145</v>
+        <v>123</v>
       </c>
       <c r="T33" t="s">
-        <v>210</v>
+        <v>186</v>
       </c>
       <c r="V33" t="s">
         <v>86</v>
       </c>
       <c r="W33" t="s">
-        <v>144</v>
+        <v>122</v>
       </c>
       <c r="X33" t="s">
-        <v>145</v>
+        <v>123</v>
       </c>
       <c r="Y33" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="34" spans="2:25" x14ac:dyDescent="0.25">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="34" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B34" t="s">
         <v>86</v>
       </c>
@@ -2594,46 +2522,46 @@
         <v>127</v>
       </c>
       <c r="J34" t="s">
-        <v>168</v>
+        <v>154</v>
       </c>
       <c r="L34" t="s">
         <v>86</v>
       </c>
       <c r="M34" t="s">
-        <v>100</v>
+        <v>142</v>
       </c>
       <c r="N34" t="s">
-        <v>101</v>
+        <v>143</v>
       </c>
       <c r="O34" t="s">
-        <v>185</v>
+        <v>169</v>
       </c>
       <c r="Q34" t="s">
         <v>86</v>
       </c>
       <c r="R34" t="s">
-        <v>146</v>
+        <v>136</v>
       </c>
       <c r="S34" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
       <c r="T34" t="s">
-        <v>210</v>
+        <v>186</v>
       </c>
       <c r="V34" t="s">
         <v>86</v>
       </c>
       <c r="W34" t="s">
-        <v>146</v>
+        <v>136</v>
       </c>
       <c r="X34" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
       <c r="Y34" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="35" spans="2:25" x14ac:dyDescent="0.25">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="35" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B35" t="s">
         <v>86</v>
       </c>
@@ -2656,46 +2584,46 @@
         <v>129</v>
       </c>
       <c r="J35" t="s">
-        <v>168</v>
+        <v>154</v>
       </c>
       <c r="L35" t="s">
         <v>86</v>
       </c>
       <c r="M35" t="s">
+        <v>161</v>
+      </c>
+      <c r="N35" t="s">
         <v>162</v>
       </c>
-      <c r="N35" t="s">
-        <v>163</v>
-      </c>
       <c r="O35" t="s">
-        <v>185</v>
+        <v>169</v>
       </c>
       <c r="Q35" t="s">
         <v>86</v>
       </c>
       <c r="R35" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="S35" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="T35" t="s">
-        <v>210</v>
+        <v>186</v>
       </c>
       <c r="V35" t="s">
         <v>86</v>
       </c>
       <c r="W35" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="X35" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="Y35" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="36" spans="2:25" x14ac:dyDescent="0.25">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="36" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B36" t="s">
         <v>86</v>
       </c>
@@ -2712,52 +2640,52 @@
         <v>86</v>
       </c>
       <c r="H36" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="I36" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="J36" t="s">
-        <v>168</v>
+        <v>154</v>
       </c>
       <c r="L36" t="s">
         <v>86</v>
       </c>
       <c r="M36" t="s">
-        <v>192</v>
+        <v>98</v>
       </c>
       <c r="N36" t="s">
-        <v>193</v>
+        <v>99</v>
       </c>
       <c r="O36" t="s">
-        <v>185</v>
+        <v>169</v>
       </c>
       <c r="Q36" t="s">
         <v>86</v>
       </c>
       <c r="R36" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="S36" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="T36" t="s">
-        <v>210</v>
+        <v>186</v>
       </c>
       <c r="V36" t="s">
         <v>86</v>
       </c>
       <c r="W36" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="X36" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="Y36" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="37" spans="2:25" x14ac:dyDescent="0.25">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="37" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B37" t="s">
         <v>86</v>
       </c>
@@ -2774,52 +2702,52 @@
         <v>86</v>
       </c>
       <c r="H37" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="I37" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="J37" t="s">
-        <v>168</v>
+        <v>154</v>
       </c>
       <c r="L37" t="s">
         <v>86</v>
       </c>
       <c r="M37" t="s">
-        <v>96</v>
+        <v>128</v>
       </c>
       <c r="N37" t="s">
-        <v>97</v>
+        <v>129</v>
       </c>
       <c r="O37" t="s">
-        <v>185</v>
+        <v>169</v>
       </c>
       <c r="Q37" t="s">
         <v>86</v>
       </c>
       <c r="R37" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="S37" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="T37" t="s">
-        <v>210</v>
+        <v>186</v>
       </c>
       <c r="V37" t="s">
         <v>86</v>
       </c>
       <c r="W37" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="X37" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="Y37" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="38" spans="2:25" x14ac:dyDescent="0.25">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="38" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B38" t="s">
         <v>86</v>
       </c>
@@ -2836,52 +2764,52 @@
         <v>86</v>
       </c>
       <c r="H38" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="I38" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="J38" t="s">
-        <v>168</v>
+        <v>154</v>
       </c>
       <c r="L38" t="s">
         <v>86</v>
       </c>
       <c r="M38" t="s">
-        <v>169</v>
+        <v>136</v>
       </c>
       <c r="N38" t="s">
-        <v>170</v>
+        <v>137</v>
       </c>
       <c r="O38" t="s">
-        <v>185</v>
+        <v>169</v>
       </c>
       <c r="Q38" t="s">
         <v>86</v>
       </c>
       <c r="R38" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
       <c r="S38" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="T38" t="s">
-        <v>210</v>
+        <v>186</v>
       </c>
       <c r="V38" t="s">
         <v>86</v>
       </c>
       <c r="W38" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
       <c r="X38" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="Y38" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="39" spans="2:25" x14ac:dyDescent="0.25">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="39" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B39" t="s">
         <v>86</v>
       </c>
@@ -2898,52 +2826,52 @@
         <v>86</v>
       </c>
       <c r="H39" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="I39" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="J39" t="s">
-        <v>168</v>
+        <v>154</v>
       </c>
       <c r="L39" t="s">
         <v>86</v>
       </c>
       <c r="M39" t="s">
-        <v>194</v>
+        <v>132</v>
       </c>
       <c r="N39" t="s">
-        <v>195</v>
+        <v>133</v>
       </c>
       <c r="O39" t="s">
-        <v>185</v>
+        <v>169</v>
       </c>
       <c r="Q39" t="s">
         <v>86</v>
       </c>
       <c r="R39" t="s">
-        <v>90</v>
+        <v>152</v>
       </c>
       <c r="S39" t="s">
-        <v>91</v>
+        <v>153</v>
       </c>
       <c r="T39" t="s">
-        <v>210</v>
+        <v>186</v>
       </c>
       <c r="V39" t="s">
         <v>86</v>
       </c>
       <c r="W39" t="s">
-        <v>90</v>
+        <v>152</v>
       </c>
       <c r="X39" t="s">
-        <v>91</v>
+        <v>153</v>
       </c>
       <c r="Y39" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="40" spans="2:25" x14ac:dyDescent="0.25">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="40" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B40" t="s">
         <v>86</v>
       </c>
@@ -2960,52 +2888,28 @@
         <v>86</v>
       </c>
       <c r="H40" t="s">
-        <v>140</v>
+        <v>155</v>
       </c>
       <c r="I40" t="s">
-        <v>141</v>
+        <v>156</v>
       </c>
       <c r="J40" t="s">
-        <v>168</v>
+        <v>154</v>
       </c>
       <c r="L40" t="s">
         <v>86</v>
       </c>
       <c r="M40" t="s">
-        <v>179</v>
+        <v>120</v>
       </c>
       <c r="N40" t="s">
-        <v>180</v>
+        <v>121</v>
       </c>
       <c r="O40" t="s">
-        <v>185</v>
-      </c>
-      <c r="Q40" t="s">
-        <v>86</v>
-      </c>
-      <c r="R40" t="s">
-        <v>160</v>
-      </c>
-      <c r="S40" t="s">
-        <v>161</v>
-      </c>
-      <c r="T40" t="s">
-        <v>210</v>
-      </c>
-      <c r="V40" t="s">
-        <v>86</v>
-      </c>
-      <c r="W40" t="s">
-        <v>160</v>
-      </c>
-      <c r="X40" t="s">
-        <v>161</v>
-      </c>
-      <c r="Y40" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="41" spans="2:25" x14ac:dyDescent="0.25">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="41" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B41" t="s">
         <v>86</v>
       </c>
@@ -3022,52 +2926,28 @@
         <v>86</v>
       </c>
       <c r="H41" t="s">
-        <v>142</v>
+        <v>157</v>
       </c>
       <c r="I41" t="s">
-        <v>143</v>
+        <v>158</v>
       </c>
       <c r="J41" t="s">
-        <v>168</v>
+        <v>154</v>
       </c>
       <c r="L41" t="s">
         <v>86</v>
       </c>
       <c r="M41" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="N41" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="O41" t="s">
-        <v>185</v>
-      </c>
-      <c r="Q41" t="s">
-        <v>86</v>
-      </c>
-      <c r="R41" t="s">
-        <v>164</v>
-      </c>
-      <c r="S41" t="s">
-        <v>165</v>
-      </c>
-      <c r="T41" t="s">
-        <v>210</v>
-      </c>
-      <c r="V41" t="s">
-        <v>86</v>
-      </c>
-      <c r="W41" t="s">
-        <v>164</v>
-      </c>
-      <c r="X41" t="s">
-        <v>165</v>
-      </c>
-      <c r="Y41" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="42" spans="2:25" x14ac:dyDescent="0.25">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="42" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B42" t="s">
         <v>86</v>
       </c>
@@ -3084,52 +2964,28 @@
         <v>86</v>
       </c>
       <c r="H42" t="s">
-        <v>144</v>
+        <v>159</v>
       </c>
       <c r="I42" t="s">
-        <v>145</v>
+        <v>160</v>
       </c>
       <c r="J42" t="s">
-        <v>168</v>
+        <v>154</v>
       </c>
       <c r="L42" t="s">
         <v>86</v>
       </c>
       <c r="M42" t="s">
-        <v>116</v>
+        <v>104</v>
       </c>
       <c r="N42" t="s">
-        <v>117</v>
+        <v>105</v>
       </c>
       <c r="O42" t="s">
-        <v>185</v>
-      </c>
-      <c r="Q42" t="s">
-        <v>86</v>
-      </c>
-      <c r="R42" t="s">
-        <v>138</v>
-      </c>
-      <c r="S42" t="s">
-        <v>139</v>
-      </c>
-      <c r="T42" t="s">
-        <v>210</v>
-      </c>
-      <c r="V42" t="s">
-        <v>86</v>
-      </c>
-      <c r="W42" t="s">
-        <v>138</v>
-      </c>
-      <c r="X42" t="s">
-        <v>139</v>
-      </c>
-      <c r="Y42" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="43" spans="2:25" x14ac:dyDescent="0.25">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="43" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B43" t="s">
         <v>86</v>
       </c>
@@ -3146,679 +3002,307 @@
         <v>86</v>
       </c>
       <c r="H43" t="s">
+        <v>144</v>
+      </c>
+      <c r="I43" t="s">
+        <v>145</v>
+      </c>
+      <c r="J43" t="s">
+        <v>154</v>
+      </c>
+      <c r="L43" t="s">
+        <v>86</v>
+      </c>
+      <c r="M43" t="s">
+        <v>100</v>
+      </c>
+      <c r="N43" t="s">
+        <v>101</v>
+      </c>
+      <c r="O43" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="44" spans="2:25" x14ac:dyDescent="0.45">
+      <c r="G44" t="s">
+        <v>86</v>
+      </c>
+      <c r="H44" t="s">
+        <v>148</v>
+      </c>
+      <c r="I44" t="s">
+        <v>149</v>
+      </c>
+      <c r="J44" t="s">
+        <v>154</v>
+      </c>
+      <c r="L44" t="s">
+        <v>86</v>
+      </c>
+      <c r="M44" t="s">
+        <v>122</v>
+      </c>
+      <c r="N44" t="s">
+        <v>123</v>
+      </c>
+      <c r="O44" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="45" spans="2:25" x14ac:dyDescent="0.45">
+      <c r="G45" t="s">
+        <v>86</v>
+      </c>
+      <c r="H45" t="s">
+        <v>150</v>
+      </c>
+      <c r="I45" t="s">
+        <v>151</v>
+      </c>
+      <c r="J45" t="s">
+        <v>154</v>
+      </c>
+      <c r="L45" t="s">
+        <v>86</v>
+      </c>
+      <c r="M45" t="s">
         <v>146</v>
       </c>
-      <c r="I43" t="s">
+      <c r="N45" t="s">
         <v>147</v>
       </c>
-      <c r="J43" t="s">
-        <v>168</v>
-      </c>
-      <c r="L43" t="s">
-        <v>86</v>
-      </c>
-      <c r="M43" t="s">
-        <v>196</v>
-      </c>
-      <c r="N43" t="s">
-        <v>197</v>
-      </c>
-      <c r="O43" t="s">
+      <c r="O45" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="46" spans="2:25" x14ac:dyDescent="0.45">
+      <c r="G46" t="s">
+        <v>86</v>
+      </c>
+      <c r="H46" t="s">
+        <v>152</v>
+      </c>
+      <c r="I46" t="s">
+        <v>153</v>
+      </c>
+      <c r="J46" t="s">
+        <v>154</v>
+      </c>
+      <c r="L46" t="s">
+        <v>86</v>
+      </c>
+      <c r="M46" t="s">
+        <v>112</v>
+      </c>
+      <c r="N46" t="s">
+        <v>113</v>
+      </c>
+      <c r="O46" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="47" spans="2:25" x14ac:dyDescent="0.45">
+      <c r="G47" t="s">
+        <v>86</v>
+      </c>
+      <c r="H47" t="s">
+        <v>161</v>
+      </c>
+      <c r="I47" t="s">
+        <v>162</v>
+      </c>
+      <c r="J47" t="s">
+        <v>154</v>
+      </c>
+      <c r="L47" t="s">
+        <v>86</v>
+      </c>
+      <c r="M47" t="s">
+        <v>110</v>
+      </c>
+      <c r="N47" t="s">
+        <v>111</v>
+      </c>
+      <c r="O47" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="48" spans="2:25" x14ac:dyDescent="0.45">
+      <c r="G48" t="s">
+        <v>86</v>
+      </c>
+      <c r="H48" t="s">
+        <v>163</v>
+      </c>
+      <c r="I48" t="s">
+        <v>164</v>
+      </c>
+      <c r="J48" t="s">
+        <v>154</v>
+      </c>
+      <c r="L48" t="s">
+        <v>86</v>
+      </c>
+      <c r="M48" t="s">
+        <v>180</v>
+      </c>
+      <c r="N48" t="s">
+        <v>181</v>
+      </c>
+      <c r="O48" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="49" spans="7:15" x14ac:dyDescent="0.45">
+      <c r="G49" t="s">
+        <v>86</v>
+      </c>
+      <c r="H49" t="s">
+        <v>165</v>
+      </c>
+      <c r="I49" t="s">
+        <v>166</v>
+      </c>
+      <c r="J49" t="s">
+        <v>154</v>
+      </c>
+      <c r="L49" t="s">
+        <v>86</v>
+      </c>
+      <c r="M49" t="s">
+        <v>148</v>
+      </c>
+      <c r="N49" t="s">
+        <v>149</v>
+      </c>
+      <c r="O49" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="50" spans="7:15" x14ac:dyDescent="0.45">
+      <c r="L50" t="s">
+        <v>86</v>
+      </c>
+      <c r="M50" t="s">
+        <v>159</v>
+      </c>
+      <c r="N50" t="s">
+        <v>160</v>
+      </c>
+      <c r="O50" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="51" spans="7:15" x14ac:dyDescent="0.45">
+      <c r="L51" t="s">
+        <v>86</v>
+      </c>
+      <c r="M51" t="s">
+        <v>182</v>
+      </c>
+      <c r="N51" t="s">
+        <v>183</v>
+      </c>
+      <c r="O51" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="52" spans="7:15" x14ac:dyDescent="0.45">
+      <c r="L52" t="s">
+        <v>86</v>
+      </c>
+      <c r="M52" t="s">
+        <v>134</v>
+      </c>
+      <c r="N52" t="s">
+        <v>135</v>
+      </c>
+      <c r="O52" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="53" spans="7:15" x14ac:dyDescent="0.45">
+      <c r="L53" t="s">
+        <v>86</v>
+      </c>
+      <c r="M53" t="s">
+        <v>87</v>
+      </c>
+      <c r="N53" t="s">
+        <v>88</v>
+      </c>
+      <c r="O53" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="54" spans="7:15" x14ac:dyDescent="0.45">
+      <c r="L54" t="s">
+        <v>86</v>
+      </c>
+      <c r="M54" t="s">
+        <v>184</v>
+      </c>
+      <c r="N54" t="s">
         <v>185</v>
       </c>
-      <c r="Q43" t="s">
-        <v>86</v>
-      </c>
-      <c r="R43" t="s">
+      <c r="O54" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="55" spans="7:15" x14ac:dyDescent="0.45">
+      <c r="L55" t="s">
+        <v>86</v>
+      </c>
+      <c r="M55" t="s">
+        <v>102</v>
+      </c>
+      <c r="N55" t="s">
+        <v>103</v>
+      </c>
+      <c r="O55" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="56" spans="7:15" x14ac:dyDescent="0.45">
+      <c r="L56" t="s">
+        <v>86</v>
+      </c>
+      <c r="M56" t="s">
+        <v>126</v>
+      </c>
+      <c r="N56" t="s">
+        <v>127</v>
+      </c>
+      <c r="O56" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="57" spans="7:15" x14ac:dyDescent="0.45">
+      <c r="L57" t="s">
+        <v>86</v>
+      </c>
+      <c r="M57" t="s">
+        <v>165</v>
+      </c>
+      <c r="N57" t="s">
         <v>166</v>
       </c>
-      <c r="S43" t="s">
-        <v>167</v>
-      </c>
-      <c r="T43" t="s">
-        <v>210</v>
-      </c>
-      <c r="V43" t="s">
-        <v>86</v>
-      </c>
-      <c r="W43" t="s">
-        <v>166</v>
-      </c>
-      <c r="X43" t="s">
-        <v>167</v>
-      </c>
-      <c r="Y43" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="44" spans="2:25" x14ac:dyDescent="0.25">
-      <c r="B44" t="s">
-        <v>86</v>
-      </c>
-      <c r="C44" t="s">
-        <v>154</v>
-      </c>
-      <c r="D44" t="s">
+      <c r="O57" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="58" spans="7:15" x14ac:dyDescent="0.45">
+      <c r="L58" t="s">
+        <v>86</v>
+      </c>
+      <c r="M58" t="s">
         <v>155</v>
       </c>
-      <c r="E44" t="s">
-        <v>89</v>
-      </c>
-      <c r="G44" t="s">
-        <v>86</v>
-      </c>
-      <c r="H44" t="s">
-        <v>150</v>
-      </c>
-      <c r="I44" t="s">
-        <v>151</v>
-      </c>
-      <c r="J44" t="s">
-        <v>168</v>
-      </c>
-      <c r="L44" t="s">
-        <v>86</v>
-      </c>
-      <c r="M44" t="s">
-        <v>126</v>
-      </c>
-      <c r="N44" t="s">
-        <v>127</v>
-      </c>
-      <c r="O44" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="45" spans="2:25" x14ac:dyDescent="0.25">
-      <c r="B45" t="s">
-        <v>86</v>
-      </c>
-      <c r="C45" t="s">
+      <c r="N58" t="s">
         <v>156</v>
       </c>
-      <c r="D45" t="s">
-        <v>157</v>
-      </c>
-      <c r="E45" t="s">
-        <v>89</v>
-      </c>
-      <c r="G45" t="s">
-        <v>86</v>
-      </c>
-      <c r="H45" t="s">
-        <v>152</v>
-      </c>
-      <c r="I45" t="s">
-        <v>153</v>
-      </c>
-      <c r="J45" t="s">
-        <v>168</v>
-      </c>
-      <c r="L45" t="s">
-        <v>86</v>
-      </c>
-      <c r="M45" t="s">
-        <v>198</v>
-      </c>
-      <c r="N45" t="s">
-        <v>199</v>
-      </c>
-      <c r="O45" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="46" spans="2:25" x14ac:dyDescent="0.25">
-      <c r="B46" t="s">
-        <v>86</v>
-      </c>
-      <c r="C46" t="s">
-        <v>158</v>
-      </c>
-      <c r="D46" t="s">
-        <v>159</v>
-      </c>
-      <c r="E46" t="s">
-        <v>89</v>
-      </c>
-      <c r="G46" t="s">
-        <v>86</v>
-      </c>
-      <c r="H46" t="s">
-        <v>169</v>
-      </c>
-      <c r="I46" t="s">
-        <v>170</v>
-      </c>
-      <c r="J46" t="s">
-        <v>168</v>
-      </c>
-      <c r="L46" t="s">
-        <v>86</v>
-      </c>
-      <c r="M46" t="s">
-        <v>200</v>
-      </c>
-      <c r="N46" t="s">
-        <v>201</v>
-      </c>
-      <c r="O46" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="47" spans="2:25" x14ac:dyDescent="0.25">
-      <c r="B47" t="s">
-        <v>86</v>
-      </c>
-      <c r="C47" t="s">
-        <v>160</v>
-      </c>
-      <c r="D47" t="s">
-        <v>161</v>
-      </c>
-      <c r="E47" t="s">
-        <v>89</v>
-      </c>
-      <c r="G47" t="s">
-        <v>86</v>
-      </c>
-      <c r="H47" t="s">
-        <v>171</v>
-      </c>
-      <c r="I47" t="s">
-        <v>172</v>
-      </c>
-      <c r="J47" t="s">
-        <v>168</v>
-      </c>
-      <c r="L47" t="s">
-        <v>86</v>
-      </c>
-      <c r="M47" t="s">
-        <v>92</v>
-      </c>
-      <c r="N47" t="s">
-        <v>93</v>
-      </c>
-      <c r="O47" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="48" spans="2:25" x14ac:dyDescent="0.25">
-      <c r="B48" t="s">
-        <v>86</v>
-      </c>
-      <c r="C48" t="s">
-        <v>162</v>
-      </c>
-      <c r="D48" t="s">
-        <v>163</v>
-      </c>
-      <c r="E48" t="s">
-        <v>89</v>
-      </c>
-      <c r="G48" t="s">
-        <v>86</v>
-      </c>
-      <c r="H48" t="s">
-        <v>173</v>
-      </c>
-      <c r="I48" t="s">
-        <v>174</v>
-      </c>
-      <c r="J48" t="s">
-        <v>168</v>
-      </c>
-      <c r="L48" t="s">
-        <v>86</v>
-      </c>
-      <c r="M48" t="s">
-        <v>148</v>
-      </c>
-      <c r="N48" t="s">
-        <v>149</v>
-      </c>
-      <c r="O48" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="49" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B49" t="s">
-        <v>86</v>
-      </c>
-      <c r="C49" t="s">
-        <v>164</v>
-      </c>
-      <c r="D49" t="s">
-        <v>165</v>
-      </c>
-      <c r="E49" t="s">
-        <v>89</v>
-      </c>
-      <c r="G49" t="s">
-        <v>86</v>
-      </c>
-      <c r="H49" t="s">
-        <v>156</v>
-      </c>
-      <c r="I49" t="s">
-        <v>157</v>
-      </c>
-      <c r="J49" t="s">
-        <v>168</v>
-      </c>
-      <c r="L49" t="s">
-        <v>86</v>
-      </c>
-      <c r="M49" t="s">
-        <v>94</v>
-      </c>
-      <c r="N49" t="s">
-        <v>95</v>
-      </c>
-      <c r="O49" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="50" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B50" t="s">
-        <v>86</v>
-      </c>
-      <c r="C50" t="s">
-        <v>166</v>
-      </c>
-      <c r="D50" t="s">
-        <v>167</v>
-      </c>
-      <c r="E50" t="s">
-        <v>89</v>
-      </c>
-      <c r="G50" t="s">
-        <v>86</v>
-      </c>
-      <c r="H50" t="s">
-        <v>160</v>
-      </c>
-      <c r="I50" t="s">
-        <v>161</v>
-      </c>
-      <c r="J50" t="s">
-        <v>168</v>
-      </c>
-      <c r="L50" t="s">
-        <v>86</v>
-      </c>
-      <c r="M50" t="s">
-        <v>202</v>
-      </c>
-      <c r="N50" t="s">
-        <v>203</v>
-      </c>
-      <c r="O50" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="51" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="G51" t="s">
-        <v>86</v>
-      </c>
-      <c r="H51" t="s">
-        <v>162</v>
-      </c>
-      <c r="I51" t="s">
-        <v>163</v>
-      </c>
-      <c r="J51" t="s">
-        <v>168</v>
-      </c>
-      <c r="L51" t="s">
-        <v>86</v>
-      </c>
-      <c r="M51" t="s">
-        <v>171</v>
-      </c>
-      <c r="N51" t="s">
-        <v>172</v>
-      </c>
-      <c r="O51" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="52" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="G52" t="s">
-        <v>86</v>
-      </c>
-      <c r="H52" t="s">
-        <v>164</v>
-      </c>
-      <c r="I52" t="s">
-        <v>165</v>
-      </c>
-      <c r="J52" t="s">
-        <v>168</v>
-      </c>
-      <c r="L52" t="s">
-        <v>86</v>
-      </c>
-      <c r="M52" t="s">
-        <v>140</v>
-      </c>
-      <c r="N52" t="s">
-        <v>141</v>
-      </c>
-      <c r="O52" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="53" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="G53" t="s">
-        <v>86</v>
-      </c>
-      <c r="H53" t="s">
-        <v>166</v>
-      </c>
-      <c r="I53" t="s">
-        <v>167</v>
-      </c>
-      <c r="J53" t="s">
-        <v>168</v>
-      </c>
-      <c r="L53" t="s">
-        <v>86</v>
-      </c>
-      <c r="M53" t="s">
-        <v>90</v>
-      </c>
-      <c r="N53" t="s">
-        <v>91</v>
-      </c>
-      <c r="O53" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="54" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="G54" t="s">
-        <v>86</v>
-      </c>
-      <c r="H54" t="s">
-        <v>175</v>
-      </c>
-      <c r="I54" t="s">
-        <v>176</v>
-      </c>
-      <c r="J54" t="s">
-        <v>168</v>
-      </c>
-      <c r="L54" t="s">
-        <v>86</v>
-      </c>
-      <c r="M54" t="s">
-        <v>128</v>
-      </c>
-      <c r="N54" t="s">
-        <v>129</v>
-      </c>
-      <c r="O54" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="55" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="G55" t="s">
-        <v>86</v>
-      </c>
-      <c r="H55" t="s">
-        <v>177</v>
-      </c>
-      <c r="I55" t="s">
-        <v>178</v>
-      </c>
-      <c r="J55" t="s">
-        <v>168</v>
-      </c>
-      <c r="L55" t="s">
-        <v>86</v>
-      </c>
-      <c r="M55" t="s">
-        <v>132</v>
-      </c>
-      <c r="N55" t="s">
-        <v>133</v>
-      </c>
-      <c r="O55" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="56" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="G56" t="s">
-        <v>86</v>
-      </c>
-      <c r="H56" t="s">
-        <v>179</v>
-      </c>
-      <c r="I56" t="s">
-        <v>180</v>
-      </c>
-      <c r="J56" t="s">
-        <v>168</v>
-      </c>
-      <c r="L56" t="s">
-        <v>86</v>
-      </c>
-      <c r="M56" t="s">
-        <v>204</v>
-      </c>
-      <c r="N56" t="s">
-        <v>205</v>
-      </c>
-      <c r="O56" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="57" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="G57" t="s">
-        <v>86</v>
-      </c>
-      <c r="H57" t="s">
-        <v>181</v>
-      </c>
-      <c r="I57" t="s">
-        <v>182</v>
-      </c>
-      <c r="J57" t="s">
-        <v>168</v>
-      </c>
-      <c r="L57" t="s">
-        <v>86</v>
-      </c>
-      <c r="M57" t="s">
-        <v>181</v>
-      </c>
-      <c r="N57" t="s">
-        <v>182</v>
-      </c>
-      <c r="O57" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="58" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="L58" t="s">
-        <v>86</v>
-      </c>
-      <c r="M58" t="s">
-        <v>104</v>
-      </c>
-      <c r="N58" t="s">
-        <v>105</v>
-      </c>
       <c r="O58" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="59" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="L59" t="s">
-        <v>86</v>
-      </c>
-      <c r="M59" t="s">
-        <v>87</v>
-      </c>
-      <c r="N59" t="s">
-        <v>88</v>
-      </c>
-      <c r="O59" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="60" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="L60" t="s">
-        <v>86</v>
-      </c>
-      <c r="M60" t="s">
-        <v>156</v>
-      </c>
-      <c r="N60" t="s">
-        <v>157</v>
-      </c>
-      <c r="O60" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="61" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="L61" t="s">
-        <v>86</v>
-      </c>
-      <c r="M61" t="s">
-        <v>120</v>
-      </c>
-      <c r="N61" t="s">
-        <v>121</v>
-      </c>
-      <c r="O61" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="62" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="L62" t="s">
-        <v>86</v>
-      </c>
-      <c r="M62" t="s">
-        <v>114</v>
-      </c>
-      <c r="N62" t="s">
-        <v>115</v>
-      </c>
-      <c r="O62" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="63" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="L63" t="s">
-        <v>86</v>
-      </c>
-      <c r="M63" t="s">
-        <v>144</v>
-      </c>
-      <c r="N63" t="s">
-        <v>145</v>
-      </c>
-      <c r="O63" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="64" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="L64" t="s">
-        <v>86</v>
-      </c>
-      <c r="M64" t="s">
-        <v>122</v>
-      </c>
-      <c r="N64" t="s">
-        <v>123</v>
-      </c>
-      <c r="O64" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="65" spans="12:15" x14ac:dyDescent="0.25">
-      <c r="L65" t="s">
-        <v>86</v>
-      </c>
-      <c r="M65" t="s">
-        <v>112</v>
-      </c>
-      <c r="N65" t="s">
-        <v>113</v>
-      </c>
-      <c r="O65" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="66" spans="12:15" x14ac:dyDescent="0.25">
-      <c r="L66" t="s">
-        <v>86</v>
-      </c>
-      <c r="M66" t="s">
-        <v>110</v>
-      </c>
-      <c r="N66" t="s">
-        <v>111</v>
-      </c>
-      <c r="O66" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="67" spans="12:15" x14ac:dyDescent="0.25">
-      <c r="L67" t="s">
-        <v>86</v>
-      </c>
-      <c r="M67" t="s">
-        <v>158</v>
-      </c>
-      <c r="N67" t="s">
-        <v>159</v>
-      </c>
-      <c r="O67" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="68" spans="12:15" x14ac:dyDescent="0.25">
-      <c r="L68" t="s">
-        <v>86</v>
-      </c>
-      <c r="M68" t="s">
-        <v>206</v>
-      </c>
-      <c r="N68" t="s">
-        <v>207</v>
-      </c>
-      <c r="O68" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="69" spans="12:15" x14ac:dyDescent="0.25">
-      <c r="L69" t="s">
-        <v>86</v>
-      </c>
-      <c r="M69" t="s">
-        <v>164</v>
-      </c>
-      <c r="N69" t="s">
-        <v>165</v>
-      </c>
-      <c r="O69" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="70" spans="12:15" x14ac:dyDescent="0.25">
-      <c r="L70" t="s">
-        <v>86</v>
-      </c>
-      <c r="M70" t="s">
-        <v>208</v>
-      </c>
-      <c r="N70" t="s">
-        <v>209</v>
-      </c>
-      <c r="O70" t="s">
-        <v>185</v>
+        <v>169</v>
       </c>
     </row>
   </sheetData>
@@ -3829,21 +3313,21 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3954DD3-0F24-46DF-B268-7A98442D0282}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="29.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="7.42578125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="5" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="3.85546875" bestFit="1" customWidth="1"/>
-    <col min="12" max="14" width="4.7109375" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="5.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.73046875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.59765625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="29.796875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.59765625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.59765625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.19921875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="7.46484375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="4.9296875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="3.86328125" bestFit="1" customWidth="1"/>
+    <col min="12" max="14" width="4.73046875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="5.1328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3853,28 +3337,28 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="C4:X57"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="3" max="3" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.3984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.73046875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="4.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="5.42578125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="5.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="4.86328125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.3984375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="5.3984375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="5.73046875" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="5" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="6.28515625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="4.28515625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="16.85546875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="7.7109375" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="8.5703125" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="6.265625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="4.265625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="16.86328125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="12.3984375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="8.59765625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="10.73046875" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="10" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="9" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="9.06640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="3:24" x14ac:dyDescent="0.25">
+    <row r="4" spans="3:24" x14ac:dyDescent="0.45">
       <c r="C4" t="s">
         <v>4</v>
       </c>
@@ -3888,7 +3372,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="3:24" x14ac:dyDescent="0.25">
+    <row r="5" spans="3:24" x14ac:dyDescent="0.45">
       <c r="C5" t="s">
         <v>3</v>
       </c>
@@ -3914,7 +3398,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="6" spans="3:24" x14ac:dyDescent="0.25">
+    <row r="6" spans="3:24" x14ac:dyDescent="0.45">
       <c r="D6" t="s">
         <v>6</v>
       </c>
@@ -3934,7 +3418,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="7" spans="3:24" x14ac:dyDescent="0.25">
+    <row r="7" spans="3:24" x14ac:dyDescent="0.45">
       <c r="D7" t="s">
         <v>7</v>
       </c>
@@ -3954,7 +3438,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="8" spans="3:24" x14ac:dyDescent="0.25">
+    <row r="8" spans="3:24" x14ac:dyDescent="0.45">
       <c r="D8" t="s">
         <v>8</v>
       </c>
@@ -3965,7 +3449,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="3:24" x14ac:dyDescent="0.25">
+    <row r="9" spans="3:24" x14ac:dyDescent="0.45">
       <c r="D9" t="s">
         <v>9</v>
       </c>
@@ -3976,7 +3460,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="10" spans="3:24" x14ac:dyDescent="0.25">
+    <row r="10" spans="3:24" x14ac:dyDescent="0.45">
       <c r="D10" t="s">
         <v>10</v>
       </c>
@@ -3990,7 +3474,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="11" spans="3:24" x14ac:dyDescent="0.25">
+    <row r="11" spans="3:24" x14ac:dyDescent="0.45">
       <c r="D11" t="s">
         <v>6</v>
       </c>
@@ -4016,7 +3500,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="12" spans="3:24" x14ac:dyDescent="0.25">
+    <row r="12" spans="3:24" x14ac:dyDescent="0.45">
       <c r="P12" s="2" t="s">
         <v>26</v>
       </c>
@@ -4033,7 +3517,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="13" spans="3:24" x14ac:dyDescent="0.25">
+    <row r="13" spans="3:24" x14ac:dyDescent="0.45">
       <c r="C13" t="s">
         <v>4</v>
       </c>
@@ -4059,7 +3543,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="14" spans="3:24" x14ac:dyDescent="0.25">
+    <row r="14" spans="3:24" x14ac:dyDescent="0.45">
       <c r="C14" t="s">
         <v>3</v>
       </c>
@@ -4097,7 +3581,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="15" spans="3:24" x14ac:dyDescent="0.25">
+    <row r="15" spans="3:24" x14ac:dyDescent="0.45">
       <c r="C15" t="s">
         <v>11</v>
       </c>
@@ -4135,7 +3619,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="16" spans="3:24" x14ac:dyDescent="0.25">
+    <row r="16" spans="3:24" x14ac:dyDescent="0.45">
       <c r="D16" t="s">
         <v>6</v>
       </c>
@@ -4167,7 +3651,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="17" spans="3:24" x14ac:dyDescent="0.25">
+    <row r="17" spans="3:24" x14ac:dyDescent="0.45">
       <c r="D17" t="s">
         <v>13</v>
       </c>
@@ -4201,7 +3685,7 @@
         <v>EN[_]Hydro*</v>
       </c>
     </row>
-    <row r="18" spans="3:24" x14ac:dyDescent="0.25">
+    <row r="18" spans="3:24" x14ac:dyDescent="0.45">
       <c r="D18" t="s">
         <v>13</v>
       </c>
@@ -4235,7 +3719,7 @@
         <v>E[_]SPV*</v>
       </c>
     </row>
-    <row r="19" spans="3:24" x14ac:dyDescent="0.25">
+    <row r="19" spans="3:24" x14ac:dyDescent="0.45">
       <c r="D19" t="s">
         <v>7</v>
       </c>
@@ -4269,7 +3753,7 @@
         <v>E[_]WOF*</v>
       </c>
     </row>
-    <row r="20" spans="3:24" x14ac:dyDescent="0.25">
+    <row r="20" spans="3:24" x14ac:dyDescent="0.45">
       <c r="D20" t="s">
         <v>8</v>
       </c>
@@ -4303,7 +3787,7 @@
         <v>E[_]WON*</v>
       </c>
     </row>
-    <row r="21" spans="3:24" x14ac:dyDescent="0.25">
+    <row r="21" spans="3:24" x14ac:dyDescent="0.45">
       <c r="D21" t="s">
         <v>9</v>
       </c>
@@ -4337,7 +3821,7 @@
         <v>EN[_]Hydro*</v>
       </c>
     </row>
-    <row r="22" spans="3:24" x14ac:dyDescent="0.25">
+    <row r="22" spans="3:24" x14ac:dyDescent="0.45">
       <c r="D22" t="s">
         <v>10</v>
       </c>
@@ -4371,7 +3855,7 @@
         <v>E[_]SPV*</v>
       </c>
     </row>
-    <row r="23" spans="3:24" x14ac:dyDescent="0.25">
+    <row r="23" spans="3:24" x14ac:dyDescent="0.45">
       <c r="P23" s="2" t="s">
         <v>30</v>
       </c>
@@ -4396,7 +3880,7 @@
         <v>E[_]WOF*</v>
       </c>
     </row>
-    <row r="24" spans="3:24" x14ac:dyDescent="0.25">
+    <row r="24" spans="3:24" x14ac:dyDescent="0.45">
       <c r="P24" s="2" t="s">
         <v>30</v>
       </c>
@@ -4422,12 +3906,12 @@
         <v>E[_]WON*</v>
       </c>
     </row>
-    <row r="27" spans="3:24" x14ac:dyDescent="0.25">
+    <row r="27" spans="3:24" x14ac:dyDescent="0.45">
       <c r="C27" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="28" spans="3:24" x14ac:dyDescent="0.25">
+    <row r="28" spans="3:24" x14ac:dyDescent="0.45">
       <c r="C28" t="s">
         <v>16</v>
       </c>
@@ -4447,7 +3931,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="29" spans="3:24" x14ac:dyDescent="0.25">
+    <row r="29" spans="3:24" x14ac:dyDescent="0.45">
       <c r="C29" t="s">
         <v>76</v>
       </c>
@@ -4458,7 +3942,7 @@
         <v>8.76</v>
       </c>
     </row>
-    <row r="30" spans="3:24" x14ac:dyDescent="0.25">
+    <row r="30" spans="3:24" x14ac:dyDescent="0.45">
       <c r="C30" t="s">
         <v>37</v>
       </c>
@@ -4472,7 +3956,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="31" spans="3:24" x14ac:dyDescent="0.25">
+    <row r="31" spans="3:24" x14ac:dyDescent="0.45">
       <c r="D31" t="s">
         <v>7</v>
       </c>
@@ -4483,7 +3967,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="32" spans="3:24" x14ac:dyDescent="0.25">
+    <row r="32" spans="3:24" x14ac:dyDescent="0.45">
       <c r="D32" t="s">
         <v>10</v>
       </c>
@@ -4494,7 +3978,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="33" spans="3:22" x14ac:dyDescent="0.25">
+    <row r="33" spans="3:22" x14ac:dyDescent="0.45">
       <c r="D33" t="s">
         <v>9</v>
       </c>
@@ -4505,7 +3989,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="3:22" x14ac:dyDescent="0.25">
+    <row r="34" spans="3:22" x14ac:dyDescent="0.45">
       <c r="C34" t="s">
         <v>17</v>
       </c>
@@ -4519,7 +4003,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="35" spans="3:22" x14ac:dyDescent="0.25">
+    <row r="35" spans="3:22" x14ac:dyDescent="0.45">
       <c r="C35" t="s">
         <v>85</v>
       </c>
@@ -4530,7 +4014,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="38" spans="3:22" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="3:22" ht="17.25" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="C38" t="s">
         <v>19</v>
       </c>
@@ -4538,7 +4022,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="39" spans="3:22" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="3:22" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="C39" t="s">
         <v>20</v>
       </c>
@@ -4570,7 +4054,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="40" spans="3:22" x14ac:dyDescent="0.25">
+    <row r="40" spans="3:22" x14ac:dyDescent="0.45">
       <c r="C40" t="s">
         <v>14</v>
       </c>
@@ -4602,7 +4086,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="41" spans="3:22" x14ac:dyDescent="0.25">
+    <row r="41" spans="3:22" x14ac:dyDescent="0.45">
       <c r="C41" t="s">
         <v>15</v>
       </c>
@@ -4613,7 +4097,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="42" spans="3:22" x14ac:dyDescent="0.25">
+    <row r="42" spans="3:22" x14ac:dyDescent="0.45">
       <c r="C42" t="s">
         <v>41</v>
       </c>
@@ -4624,7 +4108,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="43" spans="3:22" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="3:22" ht="17.25" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="C43" t="s">
         <v>39</v>
       </c>
@@ -4638,7 +4122,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="44" spans="3:22" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="3:22" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="C44" t="s">
         <v>40</v>
       </c>
@@ -4661,7 +4145,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="45" spans="3:22" x14ac:dyDescent="0.25">
+    <row r="45" spans="3:22" x14ac:dyDescent="0.45">
       <c r="P45" t="s">
         <v>81</v>
       </c>
@@ -4675,12 +4159,12 @@
         <v>80</v>
       </c>
     </row>
-    <row r="47" spans="3:22" x14ac:dyDescent="0.25">
+    <row r="47" spans="3:22" x14ac:dyDescent="0.45">
       <c r="C47" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="48" spans="3:22" x14ac:dyDescent="0.25">
+    <row r="48" spans="3:22" x14ac:dyDescent="0.45">
       <c r="C48" t="s">
         <v>1</v>
       </c>
@@ -4697,7 +4181,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="49" spans="3:13" x14ac:dyDescent="0.25">
+    <row r="49" spans="3:13" x14ac:dyDescent="0.45">
       <c r="C49" t="s">
         <v>48</v>
       </c>
@@ -4714,7 +4198,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="50" spans="3:13" x14ac:dyDescent="0.25">
+    <row r="50" spans="3:13" x14ac:dyDescent="0.45">
       <c r="C50" t="s">
         <v>53</v>
       </c>
@@ -4728,7 +4212,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="51" spans="3:13" x14ac:dyDescent="0.25">
+    <row r="51" spans="3:13" x14ac:dyDescent="0.45">
       <c r="C51" t="s">
         <v>48</v>
       </c>
@@ -4739,12 +4223,12 @@
         <v>75</v>
       </c>
     </row>
-    <row r="54" spans="3:13" x14ac:dyDescent="0.25">
+    <row r="54" spans="3:13" x14ac:dyDescent="0.45">
       <c r="C54" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="55" spans="3:13" x14ac:dyDescent="0.25">
+    <row r="55" spans="3:13" x14ac:dyDescent="0.45">
       <c r="C55" t="s">
         <v>24</v>
       </c>
@@ -4779,7 +4263,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="56" spans="3:13" x14ac:dyDescent="0.25">
+    <row r="56" spans="3:13" x14ac:dyDescent="0.45">
       <c r="C56" t="s">
         <v>62</v>
       </c>
@@ -4799,7 +4283,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="57" spans="3:13" x14ac:dyDescent="0.25">
+    <row r="57" spans="3:13" x14ac:dyDescent="0.45">
       <c r="C57" t="s">
         <v>62</v>
       </c>

--- a/VerveStacks_POL_grids_kan50/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_POL_grids_kan50/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
   <workbookPr updateLinks="never"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06207D76-FEBF-44F4-BE86-8127EF830D95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB703F29-1DE6-407B-94FE-02C8564DA3C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="368" yWindow="368" windowWidth="21599" windowHeight="12772" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AVA" sheetId="6" r:id="rId1"/>
@@ -307,7 +307,7 @@
     <t>at grid node - Gdynia_POL</t>
   </si>
   <si>
-    <t>en_gas_ccgt,en_gas_turbine,en_chp_gas_cc_ext,en_gas_ccs,en_coal_subcritical,en_coal_supercritical,en_coal_ultrasupercritical,en_coal_igcc,en_nuclear,en_nuclear_smr,en_biomass,en_chp_biomass_chips_ext,en_hop_gas_boiler,en_hop_biomass_chips,en_hop_electric_boiler,en_hp_air_10mw,en_chp_gas_cc_ext_ccs</t>
+    <t>en_gas_ccgt,en_gas_turbine,en_chp_gas_cc_ext,en_gas_ccs,en_coal_subcritical,en_coal_supercritical,en_coal_ultrasupercritical,en_coal_igcc,en_nuclear,en_nuclear_smr,en_biomass,en_chp_biomass_chips_ext,en_biomass_ccs,en_chp_gas_cc_ext_ccs,en_chp_biomass_pellets_ext_ccs,en_hop_gas_boiler,en_hop_biomass_chips,en_hop_electric_boiler,en_hp_air_10mw,en_chp_gas_cc_ext_ccs</t>
   </si>
   <si>
     <t>Katowice_POL</t>
@@ -541,31 +541,37 @@
     <t>at grid node - Krosno_POL</t>
   </si>
   <si>
+    <t>e_demand,ev_battery,H2prd_Elc_PEM,H2prd_Elc_ALK</t>
+  </si>
+  <si>
+    <t>Kielce_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Kielce_POL</t>
+  </si>
+  <si>
+    <t>Slupsk_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Slupsk_POL</t>
+  </si>
+  <si>
+    <t>Grajewo_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Grajewo_POL</t>
+  </si>
+  <si>
     <t>Legnica_POL</t>
   </si>
   <si>
     <t>at grid node - Legnica_POL</t>
   </si>
   <si>
-    <t>e_demand,ev_battery,H2prd_Elc_PEM,H2prd_Elc_ALK</t>
-  </si>
-  <si>
-    <t>Grajewo_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Grajewo_POL</t>
-  </si>
-  <si>
-    <t>Kielce_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Kielce_POL</t>
-  </si>
-  <si>
-    <t>Slupsk_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Slupsk_POL</t>
+    <t>Olsztyn_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Olsztyn_POL</t>
   </si>
   <si>
     <t>OstrowiecSwietokrz_POL</t>
@@ -574,22 +580,16 @@
     <t>at grid node - OstrowiecSwietokrz_POL</t>
   </si>
   <si>
-    <t>Olsztyn_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Olsztyn_POL</t>
+    <t>Zamosc_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Zamosc_POL</t>
   </si>
   <si>
     <t>Elk_POL</t>
   </si>
   <si>
     <t>at grid node - Elk_POL</t>
-  </si>
-  <si>
-    <t>Zamosc_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Zamosc_POL</t>
   </si>
   <si>
     <t>Chelm_POL</t>
@@ -1102,13 +1102,13 @@
         <v>86</v>
       </c>
       <c r="M11" t="s">
-        <v>167</v>
+        <v>130</v>
       </c>
       <c r="N11" t="s">
-        <v>168</v>
+        <v>131</v>
       </c>
       <c r="O11" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="Q11" t="s">
         <v>86</v>
@@ -1164,13 +1164,13 @@
         <v>86</v>
       </c>
       <c r="M12" t="s">
-        <v>106</v>
+        <v>138</v>
       </c>
       <c r="N12" t="s">
-        <v>107</v>
+        <v>139</v>
       </c>
       <c r="O12" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="Q12" t="s">
         <v>86</v>
@@ -1226,13 +1226,13 @@
         <v>86</v>
       </c>
       <c r="M13" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="N13" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="O13" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="Q13" t="s">
         <v>86</v>
@@ -1288,13 +1288,13 @@
         <v>86</v>
       </c>
       <c r="M14" t="s">
-        <v>172</v>
+        <v>96</v>
       </c>
       <c r="N14" t="s">
-        <v>173</v>
+        <v>97</v>
       </c>
       <c r="O14" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="Q14" t="s">
         <v>86</v>
@@ -1350,13 +1350,13 @@
         <v>86</v>
       </c>
       <c r="M15" t="s">
-        <v>94</v>
+        <v>106</v>
       </c>
       <c r="N15" t="s">
-        <v>95</v>
+        <v>107</v>
       </c>
       <c r="O15" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="Q15" t="s">
         <v>86</v>
@@ -1412,13 +1412,13 @@
         <v>86</v>
       </c>
       <c r="M16" t="s">
-        <v>116</v>
+        <v>98</v>
       </c>
       <c r="N16" t="s">
-        <v>117</v>
+        <v>99</v>
       </c>
       <c r="O16" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="Q16" t="s">
         <v>86</v>
@@ -1474,13 +1474,13 @@
         <v>86</v>
       </c>
       <c r="M17" t="s">
-        <v>174</v>
+        <v>116</v>
       </c>
       <c r="N17" t="s">
-        <v>175</v>
+        <v>117</v>
       </c>
       <c r="O17" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="Q17" t="s">
         <v>86</v>
@@ -1536,13 +1536,13 @@
         <v>86</v>
       </c>
       <c r="M18" t="s">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="N18" t="s">
-        <v>91</v>
+        <v>111</v>
       </c>
       <c r="O18" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="Q18" t="s">
         <v>86</v>
@@ -1598,13 +1598,13 @@
         <v>86</v>
       </c>
       <c r="M19" t="s">
-        <v>140</v>
+        <v>157</v>
       </c>
       <c r="N19" t="s">
-        <v>141</v>
+        <v>158</v>
       </c>
       <c r="O19" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="Q19" t="s">
         <v>86</v>
@@ -1660,13 +1660,13 @@
         <v>86</v>
       </c>
       <c r="M20" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="N20" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="O20" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="Q20" t="s">
         <v>86</v>
@@ -1722,13 +1722,13 @@
         <v>86</v>
       </c>
       <c r="M21" t="s">
-        <v>96</v>
+        <v>152</v>
       </c>
       <c r="N21" t="s">
-        <v>97</v>
+        <v>153</v>
       </c>
       <c r="O21" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="Q21" t="s">
         <v>86</v>
@@ -1784,13 +1784,13 @@
         <v>86</v>
       </c>
       <c r="M22" t="s">
-        <v>124</v>
+        <v>144</v>
       </c>
       <c r="N22" t="s">
-        <v>125</v>
+        <v>145</v>
       </c>
       <c r="O22" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="Q22" t="s">
         <v>86</v>
@@ -1846,13 +1846,13 @@
         <v>86</v>
       </c>
       <c r="M23" t="s">
-        <v>150</v>
+        <v>124</v>
       </c>
       <c r="N23" t="s">
-        <v>151</v>
+        <v>125</v>
       </c>
       <c r="O23" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="Q23" t="s">
         <v>86</v>
@@ -1908,13 +1908,13 @@
         <v>86</v>
       </c>
       <c r="M24" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="N24" t="s">
-        <v>93</v>
+        <v>105</v>
       </c>
       <c r="O24" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="Q24" t="s">
         <v>86</v>
@@ -1970,13 +1970,13 @@
         <v>86</v>
       </c>
       <c r="M25" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="N25" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="O25" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="Q25" t="s">
         <v>86</v>
@@ -2032,13 +2032,13 @@
         <v>86</v>
       </c>
       <c r="M26" t="s">
-        <v>157</v>
+        <v>136</v>
       </c>
       <c r="N26" t="s">
-        <v>158</v>
+        <v>137</v>
       </c>
       <c r="O26" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="Q26" t="s">
         <v>86</v>
@@ -2094,13 +2094,13 @@
         <v>86</v>
       </c>
       <c r="M27" t="s">
-        <v>118</v>
+        <v>172</v>
       </c>
       <c r="N27" t="s">
-        <v>119</v>
+        <v>173</v>
       </c>
       <c r="O27" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="Q27" t="s">
         <v>86</v>
@@ -2156,13 +2156,13 @@
         <v>86</v>
       </c>
       <c r="M28" t="s">
-        <v>114</v>
+        <v>126</v>
       </c>
       <c r="N28" t="s">
-        <v>115</v>
+        <v>127</v>
       </c>
       <c r="O28" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="Q28" t="s">
         <v>86</v>
@@ -2218,13 +2218,13 @@
         <v>86</v>
       </c>
       <c r="M29" t="s">
-        <v>138</v>
+        <v>174</v>
       </c>
       <c r="N29" t="s">
-        <v>139</v>
+        <v>175</v>
       </c>
       <c r="O29" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="Q29" t="s">
         <v>86</v>
@@ -2280,13 +2280,13 @@
         <v>86</v>
       </c>
       <c r="M30" t="s">
-        <v>178</v>
+        <v>150</v>
       </c>
       <c r="N30" t="s">
-        <v>179</v>
+        <v>151</v>
       </c>
       <c r="O30" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="Q30" t="s">
         <v>86</v>
@@ -2342,13 +2342,13 @@
         <v>86</v>
       </c>
       <c r="M31" t="s">
-        <v>108</v>
+        <v>128</v>
       </c>
       <c r="N31" t="s">
-        <v>109</v>
+        <v>129</v>
       </c>
       <c r="O31" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="Q31" t="s">
         <v>86</v>
@@ -2404,13 +2404,13 @@
         <v>86</v>
       </c>
       <c r="M32" t="s">
-        <v>130</v>
+        <v>102</v>
       </c>
       <c r="N32" t="s">
-        <v>131</v>
+        <v>103</v>
       </c>
       <c r="O32" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="Q32" t="s">
         <v>86</v>
@@ -2466,13 +2466,13 @@
         <v>86</v>
       </c>
       <c r="M33" t="s">
-        <v>163</v>
+        <v>148</v>
       </c>
       <c r="N33" t="s">
-        <v>164</v>
+        <v>149</v>
       </c>
       <c r="O33" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="Q33" t="s">
         <v>86</v>
@@ -2528,13 +2528,13 @@
         <v>86</v>
       </c>
       <c r="M34" t="s">
-        <v>142</v>
+        <v>112</v>
       </c>
       <c r="N34" t="s">
-        <v>143</v>
+        <v>113</v>
       </c>
       <c r="O34" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="Q34" t="s">
         <v>86</v>
@@ -2590,13 +2590,13 @@
         <v>86</v>
       </c>
       <c r="M35" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="N35" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="O35" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="Q35" t="s">
         <v>86</v>
@@ -2652,13 +2652,13 @@
         <v>86</v>
       </c>
       <c r="M36" t="s">
-        <v>98</v>
+        <v>159</v>
       </c>
       <c r="N36" t="s">
-        <v>99</v>
+        <v>160</v>
       </c>
       <c r="O36" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="Q36" t="s">
         <v>86</v>
@@ -2714,13 +2714,13 @@
         <v>86</v>
       </c>
       <c r="M37" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="N37" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="O37" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="Q37" t="s">
         <v>86</v>
@@ -2776,13 +2776,13 @@
         <v>86</v>
       </c>
       <c r="M38" t="s">
-        <v>136</v>
+        <v>100</v>
       </c>
       <c r="N38" t="s">
-        <v>137</v>
+        <v>101</v>
       </c>
       <c r="O38" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="Q38" t="s">
         <v>86</v>
@@ -2838,13 +2838,13 @@
         <v>86</v>
       </c>
       <c r="M39" t="s">
-        <v>132</v>
+        <v>140</v>
       </c>
       <c r="N39" t="s">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="O39" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="Q39" t="s">
         <v>86</v>
@@ -2900,13 +2900,13 @@
         <v>86</v>
       </c>
       <c r="M40" t="s">
-        <v>120</v>
+        <v>176</v>
       </c>
       <c r="N40" t="s">
-        <v>121</v>
+        <v>177</v>
       </c>
       <c r="O40" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="41" spans="2:25" x14ac:dyDescent="0.45">
@@ -2938,13 +2938,13 @@
         <v>86</v>
       </c>
       <c r="M41" t="s">
-        <v>152</v>
+        <v>120</v>
       </c>
       <c r="N41" t="s">
-        <v>153</v>
+        <v>121</v>
       </c>
       <c r="O41" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="42" spans="2:25" x14ac:dyDescent="0.45">
@@ -2976,13 +2976,13 @@
         <v>86</v>
       </c>
       <c r="M42" t="s">
-        <v>104</v>
+        <v>122</v>
       </c>
       <c r="N42" t="s">
-        <v>105</v>
+        <v>123</v>
       </c>
       <c r="O42" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="43" spans="2:25" x14ac:dyDescent="0.45">
@@ -3014,13 +3014,13 @@
         <v>86</v>
       </c>
       <c r="M43" t="s">
-        <v>100</v>
+        <v>114</v>
       </c>
       <c r="N43" t="s">
-        <v>101</v>
+        <v>115</v>
       </c>
       <c r="O43" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="44" spans="2:25" x14ac:dyDescent="0.45">
@@ -3040,13 +3040,13 @@
         <v>86</v>
       </c>
       <c r="M44" t="s">
-        <v>122</v>
+        <v>92</v>
       </c>
       <c r="N44" t="s">
-        <v>123</v>
+        <v>93</v>
       </c>
       <c r="O44" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.45">
@@ -3066,13 +3066,13 @@
         <v>86</v>
       </c>
       <c r="M45" t="s">
-        <v>146</v>
+        <v>134</v>
       </c>
       <c r="N45" t="s">
-        <v>147</v>
+        <v>135</v>
       </c>
       <c r="O45" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="46" spans="2:25" x14ac:dyDescent="0.45">
@@ -3092,13 +3092,13 @@
         <v>86</v>
       </c>
       <c r="M46" t="s">
-        <v>112</v>
+        <v>155</v>
       </c>
       <c r="N46" t="s">
-        <v>113</v>
+        <v>156</v>
       </c>
       <c r="O46" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="47" spans="2:25" x14ac:dyDescent="0.45">
@@ -3118,13 +3118,13 @@
         <v>86</v>
       </c>
       <c r="M47" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="N47" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="O47" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="48" spans="2:25" x14ac:dyDescent="0.45">
@@ -3144,13 +3144,13 @@
         <v>86</v>
       </c>
       <c r="M48" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="N48" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="O48" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="49" spans="7:15" x14ac:dyDescent="0.45">
@@ -3170,13 +3170,13 @@
         <v>86</v>
       </c>
       <c r="M49" t="s">
-        <v>148</v>
+        <v>161</v>
       </c>
       <c r="N49" t="s">
-        <v>149</v>
+        <v>162</v>
       </c>
       <c r="O49" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="50" spans="7:15" x14ac:dyDescent="0.45">
@@ -3184,13 +3184,13 @@
         <v>86</v>
       </c>
       <c r="M50" t="s">
-        <v>159</v>
+        <v>87</v>
       </c>
       <c r="N50" t="s">
-        <v>160</v>
+        <v>88</v>
       </c>
       <c r="O50" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="51" spans="7:15" x14ac:dyDescent="0.45">
@@ -3198,13 +3198,13 @@
         <v>86</v>
       </c>
       <c r="M51" t="s">
-        <v>182</v>
+        <v>90</v>
       </c>
       <c r="N51" t="s">
-        <v>183</v>
+        <v>91</v>
       </c>
       <c r="O51" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="52" spans="7:15" x14ac:dyDescent="0.45">
@@ -3212,13 +3212,13 @@
         <v>86</v>
       </c>
       <c r="M52" t="s">
-        <v>134</v>
+        <v>180</v>
       </c>
       <c r="N52" t="s">
-        <v>135</v>
+        <v>181</v>
       </c>
       <c r="O52" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="53" spans="7:15" x14ac:dyDescent="0.45">
@@ -3226,13 +3226,13 @@
         <v>86</v>
       </c>
       <c r="M53" t="s">
-        <v>87</v>
+        <v>142</v>
       </c>
       <c r="N53" t="s">
-        <v>88</v>
+        <v>143</v>
       </c>
       <c r="O53" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="54" spans="7:15" x14ac:dyDescent="0.45">
@@ -3240,13 +3240,13 @@
         <v>86</v>
       </c>
       <c r="M54" t="s">
-        <v>184</v>
+        <v>94</v>
       </c>
       <c r="N54" t="s">
-        <v>185</v>
+        <v>95</v>
       </c>
       <c r="O54" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="55" spans="7:15" x14ac:dyDescent="0.45">
@@ -3254,13 +3254,13 @@
         <v>86</v>
       </c>
       <c r="M55" t="s">
-        <v>102</v>
+        <v>182</v>
       </c>
       <c r="N55" t="s">
-        <v>103</v>
+        <v>183</v>
       </c>
       <c r="O55" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="56" spans="7:15" x14ac:dyDescent="0.45">
@@ -3268,13 +3268,13 @@
         <v>86</v>
       </c>
       <c r="M56" t="s">
-        <v>126</v>
+        <v>184</v>
       </c>
       <c r="N56" t="s">
-        <v>127</v>
+        <v>185</v>
       </c>
       <c r="O56" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="57" spans="7:15" x14ac:dyDescent="0.45">
@@ -3282,13 +3282,13 @@
         <v>86</v>
       </c>
       <c r="M57" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="N57" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="O57" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="58" spans="7:15" x14ac:dyDescent="0.45">
@@ -3296,13 +3296,13 @@
         <v>86</v>
       </c>
       <c r="M58" t="s">
-        <v>155</v>
+        <v>108</v>
       </c>
       <c r="N58" t="s">
-        <v>156</v>
+        <v>109</v>
       </c>
       <c r="O58" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
   </sheetData>

--- a/VerveStacks_POL_grids_kan50/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_POL_grids_kan50/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB703F29-1DE6-407B-94FE-02C8564DA3C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52C3F361-E6B7-43DA-ACB6-A569CD47A093}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="928" uniqueCount="188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="984" uniqueCount="200">
   <si>
     <t>PSET_PN</t>
   </si>
@@ -400,10 +400,112 @@
     <t>at grid node - Lubin_POL</t>
   </si>
   <si>
-    <t>Olesnica_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Olesnica_POL</t>
+    <t>Kalisz_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Kalisz_POL</t>
+  </si>
+  <si>
+    <t>Radom_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Radom_POL</t>
+  </si>
+  <si>
+    <t>Lodz_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Lodz_POL</t>
+  </si>
+  <si>
+    <t>Ostroleka_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Ostroleka_POL</t>
+  </si>
+  <si>
+    <t>Plock_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Plock_POL</t>
+  </si>
+  <si>
+    <t>Police_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Police_POL</t>
+  </si>
+  <si>
+    <t>Rzeszow_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Rzeszow_POL</t>
+  </si>
+  <si>
+    <t>Wroclaw_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Wroclaw_POL</t>
+  </si>
+  <si>
+    <t>Lukow_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Lukow_POL</t>
+  </si>
+  <si>
+    <t>Warsaw_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Warsaw_POL</t>
+  </si>
+  <si>
+    <t>Kwidzyn_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Kwidzyn_POL</t>
+  </si>
+  <si>
+    <t>Lublin_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Lublin_POL</t>
+  </si>
+  <si>
+    <t>ZielonaGora_POL</t>
+  </si>
+  <si>
+    <t>at grid node - ZielonaGora_POL</t>
+  </si>
+  <si>
+    <t>Belchatow_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Belchatow_POL</t>
+  </si>
+  <si>
+    <t>Bialystok_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Bialystok_POL</t>
+  </si>
+  <si>
+    <t>BielskoBiala_POL</t>
+  </si>
+  <si>
+    <t>at grid node - BielskoBiala_POL</t>
+  </si>
+  <si>
+    <t>Czestochowa_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Czestochowa_POL</t>
+  </si>
+  <si>
+    <t>Opole_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Opole_POL</t>
   </si>
   <si>
     <t>Pulawy_POL</t>
@@ -412,90 +514,6 @@
     <t>at grid node - Pulawy_POL</t>
   </si>
   <si>
-    <t>PiotrkowTrybunalsk_POL</t>
-  </si>
-  <si>
-    <t>at grid node - PiotrkowTrybunalsk_POL</t>
-  </si>
-  <si>
-    <t>Rzeszow_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Rzeszow_POL</t>
-  </si>
-  <si>
-    <t>Plock_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Plock_POL</t>
-  </si>
-  <si>
-    <t>Police_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Police_POL</t>
-  </si>
-  <si>
-    <t>Debica_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Debica_POL</t>
-  </si>
-  <si>
-    <t>Wroclaw_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Wroclaw_POL</t>
-  </si>
-  <si>
-    <t>Warsaw_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Warsaw_POL</t>
-  </si>
-  <si>
-    <t>Kwidzyn_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Kwidzyn_POL</t>
-  </si>
-  <si>
-    <t>ZielonaGora_POL</t>
-  </si>
-  <si>
-    <t>at grid node - ZielonaGora_POL</t>
-  </si>
-  <si>
-    <t>Bialystok_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Bialystok_POL</t>
-  </si>
-  <si>
-    <t>BielskoBiala_POL</t>
-  </si>
-  <si>
-    <t>at grid node - BielskoBiala_POL</t>
-  </si>
-  <si>
-    <t>Czestochowa_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Czestochowa_POL</t>
-  </si>
-  <si>
-    <t>Gliwice_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Gliwice_POL</t>
-  </si>
-  <si>
-    <t>Opole_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Opole_POL</t>
-  </si>
-  <si>
     <t>Boleslawiec_POL</t>
   </si>
   <si>
@@ -544,58 +562,76 @@
     <t>e_demand,ev_battery,H2prd_Elc_PEM,H2prd_Elc_ALK</t>
   </si>
   <si>
+    <t>OstrowiecSwietokrz_POL</t>
+  </si>
+  <si>
+    <t>at grid node - OstrowiecSwietokrz_POL</t>
+  </si>
+  <si>
+    <t>Grajewo_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Grajewo_POL</t>
+  </si>
+  <si>
+    <t>Slupsk_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Slupsk_POL</t>
+  </si>
+  <si>
+    <t>Zamosc_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Zamosc_POL</t>
+  </si>
+  <si>
+    <t>Siedlce_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Siedlce_POL</t>
+  </si>
+  <si>
+    <t>Legnica_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Legnica_POL</t>
+  </si>
+  <si>
+    <t>Chelm_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Chelm_POL</t>
+  </si>
+  <si>
+    <t>Olsztyn_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Olsztyn_POL</t>
+  </si>
+  <si>
+    <t>Elk_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Elk_POL</t>
+  </si>
+  <si>
+    <t>Pila_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Pila_POL</t>
+  </si>
+  <si>
+    <t>Walbrzych_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Walbrzych_POL</t>
+  </si>
+  <si>
     <t>Kielce_POL</t>
   </si>
   <si>
     <t>at grid node - Kielce_POL</t>
-  </si>
-  <si>
-    <t>Slupsk_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Slupsk_POL</t>
-  </si>
-  <si>
-    <t>Grajewo_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Grajewo_POL</t>
-  </si>
-  <si>
-    <t>Legnica_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Legnica_POL</t>
-  </si>
-  <si>
-    <t>Olsztyn_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Olsztyn_POL</t>
-  </si>
-  <si>
-    <t>OstrowiecSwietokrz_POL</t>
-  </si>
-  <si>
-    <t>at grid node - OstrowiecSwietokrz_POL</t>
-  </si>
-  <si>
-    <t>Zamosc_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Zamosc_POL</t>
-  </si>
-  <si>
-    <t>Elk_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Elk_POL</t>
-  </si>
-  <si>
-    <t>Chelm_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Chelm_POL</t>
   </si>
   <si>
     <t>h_demand</t>
@@ -970,7 +1006,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{268E9BAB-B98F-4B82-9042-51EABC9ED525}">
-  <dimension ref="B3:Y58"/>
+  <dimension ref="B3:Y64"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
     <row r="3" spans="2:25" x14ac:dyDescent="0.45">
@@ -1090,49 +1126,49 @@
         <v>86</v>
       </c>
       <c r="H11" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="I11" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="J11" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="L11" t="s">
         <v>86</v>
       </c>
       <c r="M11" t="s">
-        <v>130</v>
+        <v>106</v>
       </c>
       <c r="N11" t="s">
-        <v>131</v>
+        <v>107</v>
       </c>
       <c r="O11" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="Q11" t="s">
         <v>86</v>
       </c>
       <c r="R11" t="s">
-        <v>100</v>
+        <v>126</v>
       </c>
       <c r="S11" t="s">
-        <v>101</v>
+        <v>127</v>
       </c>
       <c r="T11" t="s">
-        <v>186</v>
+        <v>198</v>
       </c>
       <c r="V11" t="s">
         <v>86</v>
       </c>
       <c r="W11" t="s">
-        <v>100</v>
+        <v>126</v>
       </c>
       <c r="X11" t="s">
-        <v>101</v>
+        <v>127</v>
       </c>
       <c r="Y11" t="s">
-        <v>187</v>
+        <v>199</v>
       </c>
     </row>
     <row r="12" spans="2:25" x14ac:dyDescent="0.45">
@@ -1158,43 +1194,43 @@
         <v>131</v>
       </c>
       <c r="J12" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="L12" t="s">
         <v>86</v>
       </c>
       <c r="M12" t="s">
-        <v>138</v>
+        <v>96</v>
       </c>
       <c r="N12" t="s">
-        <v>139</v>
+        <v>97</v>
       </c>
       <c r="O12" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="Q12" t="s">
         <v>86</v>
       </c>
       <c r="R12" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="S12" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="T12" t="s">
-        <v>186</v>
+        <v>198</v>
       </c>
       <c r="V12" t="s">
         <v>86</v>
       </c>
       <c r="W12" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="X12" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="Y12" t="s">
-        <v>187</v>
+        <v>199</v>
       </c>
     </row>
     <row r="13" spans="2:25" x14ac:dyDescent="0.45">
@@ -1214,25 +1250,25 @@
         <v>86</v>
       </c>
       <c r="H13" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="I13" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="J13" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="L13" t="s">
         <v>86</v>
       </c>
       <c r="M13" t="s">
-        <v>168</v>
+        <v>112</v>
       </c>
       <c r="N13" t="s">
-        <v>169</v>
+        <v>113</v>
       </c>
       <c r="O13" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="Q13" t="s">
         <v>86</v>
@@ -1244,7 +1280,7 @@
         <v>131</v>
       </c>
       <c r="T13" t="s">
-        <v>186</v>
+        <v>198</v>
       </c>
       <c r="V13" t="s">
         <v>86</v>
@@ -1256,7 +1292,7 @@
         <v>131</v>
       </c>
       <c r="Y13" t="s">
-        <v>187</v>
+        <v>199</v>
       </c>
     </row>
     <row r="14" spans="2:25" x14ac:dyDescent="0.45">
@@ -1282,43 +1318,43 @@
         <v>99</v>
       </c>
       <c r="J14" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="L14" t="s">
         <v>86</v>
       </c>
       <c r="M14" t="s">
-        <v>96</v>
+        <v>161</v>
       </c>
       <c r="N14" t="s">
-        <v>97</v>
+        <v>162</v>
       </c>
       <c r="O14" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="Q14" t="s">
         <v>86</v>
       </c>
       <c r="R14" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="S14" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="T14" t="s">
-        <v>186</v>
+        <v>198</v>
       </c>
       <c r="V14" t="s">
         <v>86</v>
       </c>
       <c r="W14" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="X14" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="Y14" t="s">
-        <v>187</v>
+        <v>199</v>
       </c>
     </row>
     <row r="15" spans="2:25" x14ac:dyDescent="0.45">
@@ -1344,19 +1380,19 @@
         <v>88</v>
       </c>
       <c r="J15" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="L15" t="s">
         <v>86</v>
       </c>
       <c r="M15" t="s">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="N15" t="s">
-        <v>107</v>
+        <v>119</v>
       </c>
       <c r="O15" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="Q15" t="s">
         <v>86</v>
@@ -1368,7 +1404,7 @@
         <v>91</v>
       </c>
       <c r="T15" t="s">
-        <v>186</v>
+        <v>198</v>
       </c>
       <c r="V15" t="s">
         <v>86</v>
@@ -1380,7 +1416,7 @@
         <v>91</v>
       </c>
       <c r="Y15" t="s">
-        <v>187</v>
+        <v>199</v>
       </c>
     </row>
     <row r="16" spans="2:25" x14ac:dyDescent="0.45">
@@ -1406,19 +1442,19 @@
         <v>91</v>
       </c>
       <c r="J16" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="L16" t="s">
         <v>86</v>
       </c>
       <c r="M16" t="s">
-        <v>98</v>
+        <v>124</v>
       </c>
       <c r="N16" t="s">
-        <v>99</v>
+        <v>125</v>
       </c>
       <c r="O16" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="Q16" t="s">
         <v>86</v>
@@ -1430,7 +1466,7 @@
         <v>99</v>
       </c>
       <c r="T16" t="s">
-        <v>186</v>
+        <v>198</v>
       </c>
       <c r="V16" t="s">
         <v>86</v>
@@ -1442,7 +1478,7 @@
         <v>99</v>
       </c>
       <c r="Y16" t="s">
-        <v>187</v>
+        <v>199</v>
       </c>
     </row>
     <row r="17" spans="2:25" x14ac:dyDescent="0.45">
@@ -1468,19 +1504,19 @@
         <v>93</v>
       </c>
       <c r="J17" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="L17" t="s">
         <v>86</v>
       </c>
       <c r="M17" t="s">
-        <v>116</v>
+        <v>174</v>
       </c>
       <c r="N17" t="s">
-        <v>117</v>
+        <v>175</v>
       </c>
       <c r="O17" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="Q17" t="s">
         <v>86</v>
@@ -1492,7 +1528,7 @@
         <v>113</v>
       </c>
       <c r="T17" t="s">
-        <v>186</v>
+        <v>198</v>
       </c>
       <c r="V17" t="s">
         <v>86</v>
@@ -1504,7 +1540,7 @@
         <v>113</v>
       </c>
       <c r="Y17" t="s">
-        <v>187</v>
+        <v>199</v>
       </c>
     </row>
     <row r="18" spans="2:25" x14ac:dyDescent="0.45">
@@ -1530,43 +1566,43 @@
         <v>95</v>
       </c>
       <c r="J18" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="L18" t="s">
         <v>86</v>
       </c>
       <c r="M18" t="s">
-        <v>110</v>
+        <v>176</v>
       </c>
       <c r="N18" t="s">
-        <v>111</v>
+        <v>177</v>
       </c>
       <c r="O18" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="Q18" t="s">
         <v>86</v>
       </c>
       <c r="R18" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="S18" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="T18" t="s">
-        <v>186</v>
+        <v>198</v>
       </c>
       <c r="V18" t="s">
         <v>86</v>
       </c>
       <c r="W18" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="X18" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="Y18" t="s">
-        <v>187</v>
+        <v>199</v>
       </c>
     </row>
     <row r="19" spans="2:25" x14ac:dyDescent="0.45">
@@ -1592,19 +1628,19 @@
         <v>97</v>
       </c>
       <c r="J19" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="L19" t="s">
         <v>86</v>
       </c>
       <c r="M19" t="s">
-        <v>157</v>
+        <v>178</v>
       </c>
       <c r="N19" t="s">
-        <v>158</v>
+        <v>179</v>
       </c>
       <c r="O19" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="Q19" t="s">
         <v>86</v>
@@ -1616,7 +1652,7 @@
         <v>105</v>
       </c>
       <c r="T19" t="s">
-        <v>186</v>
+        <v>198</v>
       </c>
       <c r="V19" t="s">
         <v>86</v>
@@ -1628,7 +1664,7 @@
         <v>105</v>
       </c>
       <c r="Y19" t="s">
-        <v>187</v>
+        <v>199</v>
       </c>
     </row>
     <row r="20" spans="2:25" x14ac:dyDescent="0.45">
@@ -1654,19 +1690,19 @@
         <v>101</v>
       </c>
       <c r="J20" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="L20" t="s">
         <v>86</v>
       </c>
       <c r="M20" t="s">
-        <v>146</v>
+        <v>167</v>
       </c>
       <c r="N20" t="s">
-        <v>147</v>
+        <v>168</v>
       </c>
       <c r="O20" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="Q20" t="s">
         <v>86</v>
@@ -1678,7 +1714,7 @@
         <v>107</v>
       </c>
       <c r="T20" t="s">
-        <v>186</v>
+        <v>198</v>
       </c>
       <c r="V20" t="s">
         <v>86</v>
@@ -1690,7 +1726,7 @@
         <v>107</v>
       </c>
       <c r="Y20" t="s">
-        <v>187</v>
+        <v>199</v>
       </c>
     </row>
     <row r="21" spans="2:25" x14ac:dyDescent="0.45">
@@ -1716,19 +1752,19 @@
         <v>103</v>
       </c>
       <c r="J21" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="L21" t="s">
         <v>86</v>
       </c>
       <c r="M21" t="s">
-        <v>152</v>
+        <v>169</v>
       </c>
       <c r="N21" t="s">
-        <v>153</v>
+        <v>170</v>
       </c>
       <c r="O21" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="Q21" t="s">
         <v>86</v>
@@ -1740,7 +1776,7 @@
         <v>109</v>
       </c>
       <c r="T21" t="s">
-        <v>186</v>
+        <v>198</v>
       </c>
       <c r="V21" t="s">
         <v>86</v>
@@ -1752,7 +1788,7 @@
         <v>109</v>
       </c>
       <c r="Y21" t="s">
-        <v>187</v>
+        <v>199</v>
       </c>
     </row>
     <row r="22" spans="2:25" x14ac:dyDescent="0.45">
@@ -1772,25 +1808,25 @@
         <v>86</v>
       </c>
       <c r="H22" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="I22" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="J22" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="L22" t="s">
         <v>86</v>
       </c>
       <c r="M22" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="N22" t="s">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="O22" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="Q22" t="s">
         <v>86</v>
@@ -1802,7 +1838,7 @@
         <v>111</v>
       </c>
       <c r="T22" t="s">
-        <v>186</v>
+        <v>198</v>
       </c>
       <c r="V22" t="s">
         <v>86</v>
@@ -1814,7 +1850,7 @@
         <v>111</v>
       </c>
       <c r="Y22" t="s">
-        <v>187</v>
+        <v>199</v>
       </c>
     </row>
     <row r="23" spans="2:25" x14ac:dyDescent="0.45">
@@ -1840,19 +1876,19 @@
         <v>105</v>
       </c>
       <c r="J23" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="L23" t="s">
         <v>86</v>
       </c>
       <c r="M23" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="N23" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="O23" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="Q23" t="s">
         <v>86</v>
@@ -1864,7 +1900,7 @@
         <v>115</v>
       </c>
       <c r="T23" t="s">
-        <v>186</v>
+        <v>198</v>
       </c>
       <c r="V23" t="s">
         <v>86</v>
@@ -1876,7 +1912,7 @@
         <v>115</v>
       </c>
       <c r="Y23" t="s">
-        <v>187</v>
+        <v>199</v>
       </c>
     </row>
     <row r="24" spans="2:25" x14ac:dyDescent="0.45">
@@ -1902,19 +1938,19 @@
         <v>107</v>
       </c>
       <c r="J24" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="L24" t="s">
         <v>86</v>
       </c>
       <c r="M24" t="s">
-        <v>104</v>
+        <v>148</v>
       </c>
       <c r="N24" t="s">
-        <v>105</v>
+        <v>149</v>
       </c>
       <c r="O24" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="Q24" t="s">
         <v>86</v>
@@ -1926,7 +1962,7 @@
         <v>119</v>
       </c>
       <c r="T24" t="s">
-        <v>186</v>
+        <v>198</v>
       </c>
       <c r="V24" t="s">
         <v>86</v>
@@ -1938,7 +1974,7 @@
         <v>119</v>
       </c>
       <c r="Y24" t="s">
-        <v>187</v>
+        <v>199</v>
       </c>
     </row>
     <row r="25" spans="2:25" x14ac:dyDescent="0.45">
@@ -1964,19 +2000,19 @@
         <v>109</v>
       </c>
       <c r="J25" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="L25" t="s">
         <v>86</v>
       </c>
       <c r="M25" t="s">
-        <v>170</v>
+        <v>100</v>
       </c>
       <c r="N25" t="s">
-        <v>171</v>
+        <v>101</v>
       </c>
       <c r="O25" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="Q25" t="s">
         <v>86</v>
@@ -1988,7 +2024,7 @@
         <v>121</v>
       </c>
       <c r="T25" t="s">
-        <v>186</v>
+        <v>198</v>
       </c>
       <c r="V25" t="s">
         <v>86</v>
@@ -2000,7 +2036,7 @@
         <v>121</v>
       </c>
       <c r="Y25" t="s">
-        <v>187</v>
+        <v>199</v>
       </c>
     </row>
     <row r="26" spans="2:25" x14ac:dyDescent="0.45">
@@ -2026,19 +2062,19 @@
         <v>111</v>
       </c>
       <c r="J26" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="L26" t="s">
         <v>86</v>
       </c>
       <c r="M26" t="s">
-        <v>136</v>
+        <v>146</v>
       </c>
       <c r="N26" t="s">
-        <v>137</v>
+        <v>147</v>
       </c>
       <c r="O26" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="Q26" t="s">
         <v>86</v>
@@ -2050,7 +2086,7 @@
         <v>97</v>
       </c>
       <c r="T26" t="s">
-        <v>186</v>
+        <v>198</v>
       </c>
       <c r="V26" t="s">
         <v>86</v>
@@ -2062,7 +2098,7 @@
         <v>97</v>
       </c>
       <c r="Y26" t="s">
-        <v>187</v>
+        <v>199</v>
       </c>
     </row>
     <row r="27" spans="2:25" x14ac:dyDescent="0.45">
@@ -2088,19 +2124,19 @@
         <v>113</v>
       </c>
       <c r="J27" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="L27" t="s">
         <v>86</v>
       </c>
       <c r="M27" t="s">
-        <v>172</v>
+        <v>142</v>
       </c>
       <c r="N27" t="s">
-        <v>173</v>
+        <v>143</v>
       </c>
       <c r="O27" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="Q27" t="s">
         <v>86</v>
@@ -2112,7 +2148,7 @@
         <v>125</v>
       </c>
       <c r="T27" t="s">
-        <v>186</v>
+        <v>198</v>
       </c>
       <c r="V27" t="s">
         <v>86</v>
@@ -2124,7 +2160,7 @@
         <v>125</v>
       </c>
       <c r="Y27" t="s">
-        <v>187</v>
+        <v>199</v>
       </c>
     </row>
     <row r="28" spans="2:25" x14ac:dyDescent="0.45">
@@ -2150,43 +2186,43 @@
         <v>115</v>
       </c>
       <c r="J28" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="L28" t="s">
         <v>86</v>
       </c>
       <c r="M28" t="s">
-        <v>126</v>
+        <v>156</v>
       </c>
       <c r="N28" t="s">
-        <v>127</v>
+        <v>157</v>
       </c>
       <c r="O28" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="Q28" t="s">
         <v>86</v>
       </c>
       <c r="R28" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="S28" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="T28" t="s">
-        <v>186</v>
+        <v>198</v>
       </c>
       <c r="V28" t="s">
         <v>86</v>
       </c>
       <c r="W28" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="X28" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="Y28" t="s">
-        <v>187</v>
+        <v>199</v>
       </c>
     </row>
     <row r="29" spans="2:25" x14ac:dyDescent="0.45">
@@ -2212,43 +2248,43 @@
         <v>117</v>
       </c>
       <c r="J29" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="L29" t="s">
         <v>86</v>
       </c>
       <c r="M29" t="s">
-        <v>174</v>
+        <v>138</v>
       </c>
       <c r="N29" t="s">
-        <v>175</v>
+        <v>139</v>
       </c>
       <c r="O29" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="Q29" t="s">
         <v>86</v>
       </c>
       <c r="R29" t="s">
-        <v>128</v>
+        <v>94</v>
       </c>
       <c r="S29" t="s">
-        <v>129</v>
+        <v>95</v>
       </c>
       <c r="T29" t="s">
-        <v>186</v>
+        <v>198</v>
       </c>
       <c r="V29" t="s">
         <v>86</v>
       </c>
       <c r="W29" t="s">
-        <v>128</v>
+        <v>94</v>
       </c>
       <c r="X29" t="s">
-        <v>129</v>
+        <v>95</v>
       </c>
       <c r="Y29" t="s">
-        <v>187</v>
+        <v>199</v>
       </c>
     </row>
     <row r="30" spans="2:25" x14ac:dyDescent="0.45">
@@ -2274,43 +2310,43 @@
         <v>119</v>
       </c>
       <c r="J30" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="L30" t="s">
         <v>86</v>
       </c>
       <c r="M30" t="s">
-        <v>150</v>
+        <v>180</v>
       </c>
       <c r="N30" t="s">
-        <v>151</v>
+        <v>181</v>
       </c>
       <c r="O30" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="Q30" t="s">
         <v>86</v>
       </c>
       <c r="R30" t="s">
-        <v>94</v>
+        <v>132</v>
       </c>
       <c r="S30" t="s">
-        <v>95</v>
+        <v>133</v>
       </c>
       <c r="T30" t="s">
-        <v>186</v>
+        <v>198</v>
       </c>
       <c r="V30" t="s">
         <v>86</v>
       </c>
       <c r="W30" t="s">
-        <v>94</v>
+        <v>132</v>
       </c>
       <c r="X30" t="s">
-        <v>95</v>
+        <v>133</v>
       </c>
       <c r="Y30" t="s">
-        <v>187</v>
+        <v>199</v>
       </c>
     </row>
     <row r="31" spans="2:25" x14ac:dyDescent="0.45">
@@ -2336,43 +2372,43 @@
         <v>121</v>
       </c>
       <c r="J31" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="L31" t="s">
         <v>86</v>
       </c>
       <c r="M31" t="s">
-        <v>128</v>
+        <v>140</v>
       </c>
       <c r="N31" t="s">
-        <v>129</v>
+        <v>141</v>
       </c>
       <c r="O31" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="Q31" t="s">
         <v>86</v>
       </c>
       <c r="R31" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="S31" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="T31" t="s">
-        <v>186</v>
+        <v>198</v>
       </c>
       <c r="V31" t="s">
         <v>86</v>
       </c>
       <c r="W31" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="X31" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="Y31" t="s">
-        <v>187</v>
+        <v>199</v>
       </c>
     </row>
     <row r="32" spans="2:25" x14ac:dyDescent="0.45">
@@ -2398,43 +2434,43 @@
         <v>123</v>
       </c>
       <c r="J32" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="L32" t="s">
         <v>86</v>
       </c>
       <c r="M32" t="s">
-        <v>102</v>
+        <v>182</v>
       </c>
       <c r="N32" t="s">
-        <v>103</v>
+        <v>183</v>
       </c>
       <c r="O32" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="Q32" t="s">
         <v>86</v>
       </c>
       <c r="R32" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="S32" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="T32" t="s">
-        <v>186</v>
+        <v>198</v>
       </c>
       <c r="V32" t="s">
         <v>86</v>
       </c>
       <c r="W32" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="X32" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="Y32" t="s">
-        <v>187</v>
+        <v>199</v>
       </c>
     </row>
     <row r="33" spans="2:25" x14ac:dyDescent="0.45">
@@ -2460,43 +2496,43 @@
         <v>125</v>
       </c>
       <c r="J33" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="L33" t="s">
         <v>86</v>
       </c>
       <c r="M33" t="s">
-        <v>148</v>
+        <v>104</v>
       </c>
       <c r="N33" t="s">
-        <v>149</v>
+        <v>105</v>
       </c>
       <c r="O33" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="Q33" t="s">
         <v>86</v>
       </c>
       <c r="R33" t="s">
-        <v>122</v>
+        <v>138</v>
       </c>
       <c r="S33" t="s">
-        <v>123</v>
+        <v>139</v>
       </c>
       <c r="T33" t="s">
-        <v>186</v>
+        <v>198</v>
       </c>
       <c r="V33" t="s">
         <v>86</v>
       </c>
       <c r="W33" t="s">
-        <v>122</v>
+        <v>138</v>
       </c>
       <c r="X33" t="s">
-        <v>123</v>
+        <v>139</v>
       </c>
       <c r="Y33" t="s">
-        <v>187</v>
+        <v>199</v>
       </c>
     </row>
     <row r="34" spans="2:25" x14ac:dyDescent="0.45">
@@ -2522,43 +2558,43 @@
         <v>127</v>
       </c>
       <c r="J34" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="L34" t="s">
         <v>86</v>
       </c>
       <c r="M34" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="N34" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="O34" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="Q34" t="s">
         <v>86</v>
       </c>
       <c r="R34" t="s">
-        <v>136</v>
+        <v>102</v>
       </c>
       <c r="S34" t="s">
-        <v>137</v>
+        <v>103</v>
       </c>
       <c r="T34" t="s">
-        <v>186</v>
+        <v>198</v>
       </c>
       <c r="V34" t="s">
         <v>86</v>
       </c>
       <c r="W34" t="s">
-        <v>136</v>
+        <v>102</v>
       </c>
       <c r="X34" t="s">
-        <v>137</v>
+        <v>103</v>
       </c>
       <c r="Y34" t="s">
-        <v>187</v>
+        <v>199</v>
       </c>
     </row>
     <row r="35" spans="2:25" x14ac:dyDescent="0.45">
@@ -2584,43 +2620,43 @@
         <v>129</v>
       </c>
       <c r="J35" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="L35" t="s">
         <v>86</v>
       </c>
       <c r="M35" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="N35" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="O35" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="Q35" t="s">
         <v>86</v>
       </c>
       <c r="R35" t="s">
-        <v>102</v>
+        <v>142</v>
       </c>
       <c r="S35" t="s">
-        <v>103</v>
+        <v>143</v>
       </c>
       <c r="T35" t="s">
-        <v>186</v>
+        <v>198</v>
       </c>
       <c r="V35" t="s">
         <v>86</v>
       </c>
       <c r="W35" t="s">
-        <v>102</v>
+        <v>142</v>
       </c>
       <c r="X35" t="s">
-        <v>103</v>
+        <v>143</v>
       </c>
       <c r="Y35" t="s">
-        <v>187</v>
+        <v>199</v>
       </c>
     </row>
     <row r="36" spans="2:25" x14ac:dyDescent="0.45">
@@ -2646,43 +2682,43 @@
         <v>133</v>
       </c>
       <c r="J36" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="L36" t="s">
         <v>86</v>
       </c>
       <c r="M36" t="s">
-        <v>159</v>
+        <v>116</v>
       </c>
       <c r="N36" t="s">
-        <v>160</v>
+        <v>117</v>
       </c>
       <c r="O36" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="Q36" t="s">
         <v>86</v>
       </c>
       <c r="R36" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="S36" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="T36" t="s">
-        <v>186</v>
+        <v>198</v>
       </c>
       <c r="V36" t="s">
         <v>86</v>
       </c>
       <c r="W36" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="X36" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="Y36" t="s">
-        <v>187</v>
+        <v>199</v>
       </c>
     </row>
     <row r="37" spans="2:25" x14ac:dyDescent="0.45">
@@ -2708,43 +2744,43 @@
         <v>135</v>
       </c>
       <c r="J37" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="L37" t="s">
         <v>86</v>
       </c>
       <c r="M37" t="s">
-        <v>132</v>
+        <v>184</v>
       </c>
       <c r="N37" t="s">
-        <v>133</v>
+        <v>185</v>
       </c>
       <c r="O37" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="Q37" t="s">
         <v>86</v>
       </c>
       <c r="R37" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="S37" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="T37" t="s">
-        <v>186</v>
+        <v>198</v>
       </c>
       <c r="V37" t="s">
         <v>86</v>
       </c>
       <c r="W37" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="X37" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="Y37" t="s">
-        <v>187</v>
+        <v>199</v>
       </c>
     </row>
     <row r="38" spans="2:25" x14ac:dyDescent="0.45">
@@ -2770,43 +2806,43 @@
         <v>137</v>
       </c>
       <c r="J38" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="L38" t="s">
         <v>86</v>
       </c>
       <c r="M38" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="N38" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="O38" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="Q38" t="s">
         <v>86</v>
       </c>
       <c r="R38" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="S38" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="T38" t="s">
-        <v>186</v>
+        <v>198</v>
       </c>
       <c r="V38" t="s">
         <v>86</v>
       </c>
       <c r="W38" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="X38" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="Y38" t="s">
-        <v>187</v>
+        <v>199</v>
       </c>
     </row>
     <row r="39" spans="2:25" x14ac:dyDescent="0.45">
@@ -2826,49 +2862,49 @@
         <v>86</v>
       </c>
       <c r="H39" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="I39" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="J39" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="L39" t="s">
         <v>86</v>
       </c>
       <c r="M39" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="N39" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="O39" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="Q39" t="s">
         <v>86</v>
       </c>
       <c r="R39" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="S39" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="T39" t="s">
-        <v>186</v>
+        <v>198</v>
       </c>
       <c r="V39" t="s">
         <v>86</v>
       </c>
       <c r="W39" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="X39" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="Y39" t="s">
-        <v>187</v>
+        <v>199</v>
       </c>
     </row>
     <row r="40" spans="2:25" x14ac:dyDescent="0.45">
@@ -2888,25 +2924,49 @@
         <v>86</v>
       </c>
       <c r="H40" t="s">
-        <v>155</v>
+        <v>142</v>
       </c>
       <c r="I40" t="s">
-        <v>156</v>
+        <v>143</v>
       </c>
       <c r="J40" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="L40" t="s">
         <v>86</v>
       </c>
       <c r="M40" t="s">
-        <v>176</v>
+        <v>87</v>
       </c>
       <c r="N40" t="s">
-        <v>177</v>
+        <v>88</v>
       </c>
       <c r="O40" t="s">
-        <v>167</v>
+        <v>173</v>
+      </c>
+      <c r="Q40" t="s">
+        <v>86</v>
+      </c>
+      <c r="R40" t="s">
+        <v>158</v>
+      </c>
+      <c r="S40" t="s">
+        <v>159</v>
+      </c>
+      <c r="T40" t="s">
+        <v>198</v>
+      </c>
+      <c r="V40" t="s">
+        <v>86</v>
+      </c>
+      <c r="W40" t="s">
+        <v>158</v>
+      </c>
+      <c r="X40" t="s">
+        <v>159</v>
+      </c>
+      <c r="Y40" t="s">
+        <v>199</v>
       </c>
     </row>
     <row r="41" spans="2:25" x14ac:dyDescent="0.45">
@@ -2926,25 +2986,25 @@
         <v>86</v>
       </c>
       <c r="H41" t="s">
-        <v>157</v>
+        <v>144</v>
       </c>
       <c r="I41" t="s">
-        <v>158</v>
+        <v>145</v>
       </c>
       <c r="J41" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="L41" t="s">
         <v>86</v>
       </c>
       <c r="M41" t="s">
-        <v>120</v>
+        <v>186</v>
       </c>
       <c r="N41" t="s">
-        <v>121</v>
+        <v>187</v>
       </c>
       <c r="O41" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
     </row>
     <row r="42" spans="2:25" x14ac:dyDescent="0.45">
@@ -2964,25 +3024,25 @@
         <v>86</v>
       </c>
       <c r="H42" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="I42" t="s">
+        <v>162</v>
+      </c>
+      <c r="J42" t="s">
         <v>160</v>
       </c>
-      <c r="J42" t="s">
-        <v>154</v>
-      </c>
       <c r="L42" t="s">
         <v>86</v>
       </c>
       <c r="M42" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="N42" t="s">
-        <v>123</v>
+        <v>109</v>
       </c>
       <c r="O42" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
     </row>
     <row r="43" spans="2:25" x14ac:dyDescent="0.45">
@@ -3002,103 +3062,139 @@
         <v>86</v>
       </c>
       <c r="H43" t="s">
-        <v>144</v>
+        <v>163</v>
       </c>
       <c r="I43" t="s">
-        <v>145</v>
+        <v>164</v>
       </c>
       <c r="J43" t="s">
+        <v>160</v>
+      </c>
+      <c r="L43" t="s">
+        <v>86</v>
+      </c>
+      <c r="M43" t="s">
+        <v>98</v>
+      </c>
+      <c r="N43" t="s">
+        <v>99</v>
+      </c>
+      <c r="O43" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="44" spans="2:25" x14ac:dyDescent="0.45">
+      <c r="B44" t="s">
+        <v>86</v>
+      </c>
+      <c r="C44" t="s">
         <v>154</v>
       </c>
-      <c r="L43" t="s">
-        <v>86</v>
-      </c>
-      <c r="M43" t="s">
-        <v>114</v>
-      </c>
-      <c r="N43" t="s">
-        <v>115</v>
-      </c>
-      <c r="O43" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="44" spans="2:25" x14ac:dyDescent="0.45">
+      <c r="D44" t="s">
+        <v>155</v>
+      </c>
+      <c r="E44" t="s">
+        <v>89</v>
+      </c>
       <c r="G44" t="s">
         <v>86</v>
       </c>
       <c r="H44" t="s">
-        <v>148</v>
+        <v>165</v>
       </c>
       <c r="I44" t="s">
-        <v>149</v>
+        <v>166</v>
       </c>
       <c r="J44" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="L44" t="s">
         <v>86</v>
       </c>
       <c r="M44" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="N44" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="O44" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.45">
+      <c r="B45" t="s">
+        <v>86</v>
+      </c>
+      <c r="C45" t="s">
+        <v>156</v>
+      </c>
+      <c r="D45" t="s">
+        <v>157</v>
+      </c>
+      <c r="E45" t="s">
+        <v>89</v>
+      </c>
       <c r="G45" t="s">
         <v>86</v>
       </c>
       <c r="H45" t="s">
+        <v>146</v>
+      </c>
+      <c r="I45" t="s">
+        <v>147</v>
+      </c>
+      <c r="J45" t="s">
+        <v>160</v>
+      </c>
+      <c r="L45" t="s">
+        <v>86</v>
+      </c>
+      <c r="M45" t="s">
+        <v>132</v>
+      </c>
+      <c r="N45" t="s">
+        <v>133</v>
+      </c>
+      <c r="O45" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="46" spans="2:25" x14ac:dyDescent="0.45">
+      <c r="B46" t="s">
+        <v>86</v>
+      </c>
+      <c r="C46" t="s">
+        <v>158</v>
+      </c>
+      <c r="D46" t="s">
+        <v>159</v>
+      </c>
+      <c r="E46" t="s">
+        <v>89</v>
+      </c>
+      <c r="G46" t="s">
+        <v>86</v>
+      </c>
+      <c r="H46" t="s">
         <v>150</v>
       </c>
-      <c r="I45" t="s">
+      <c r="I46" t="s">
         <v>151</v>
       </c>
-      <c r="J45" t="s">
-        <v>154</v>
-      </c>
-      <c r="L45" t="s">
-        <v>86</v>
-      </c>
-      <c r="M45" t="s">
-        <v>134</v>
-      </c>
-      <c r="N45" t="s">
-        <v>135</v>
-      </c>
-      <c r="O45" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="46" spans="2:25" x14ac:dyDescent="0.45">
-      <c r="G46" t="s">
-        <v>86</v>
-      </c>
-      <c r="H46" t="s">
-        <v>152</v>
-      </c>
-      <c r="I46" t="s">
-        <v>153</v>
-      </c>
       <c r="J46" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="L46" t="s">
         <v>86</v>
       </c>
       <c r="M46" t="s">
-        <v>155</v>
+        <v>188</v>
       </c>
       <c r="N46" t="s">
-        <v>156</v>
+        <v>189</v>
       </c>
       <c r="O46" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
     </row>
     <row r="47" spans="2:25" x14ac:dyDescent="0.45">
@@ -3106,25 +3202,25 @@
         <v>86</v>
       </c>
       <c r="H47" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="I47" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="J47" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="L47" t="s">
         <v>86</v>
       </c>
       <c r="M47" t="s">
-        <v>118</v>
+        <v>190</v>
       </c>
       <c r="N47" t="s">
-        <v>119</v>
+        <v>191</v>
       </c>
       <c r="O47" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
     </row>
     <row r="48" spans="2:25" x14ac:dyDescent="0.45">
@@ -3132,25 +3228,25 @@
         <v>86</v>
       </c>
       <c r="H48" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="I48" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="J48" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="L48" t="s">
         <v>86</v>
       </c>
       <c r="M48" t="s">
-        <v>178</v>
+        <v>192</v>
       </c>
       <c r="N48" t="s">
-        <v>179</v>
+        <v>193</v>
       </c>
       <c r="O48" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
     </row>
     <row r="49" spans="7:15" x14ac:dyDescent="0.45">
@@ -3158,67 +3254,103 @@
         <v>86</v>
       </c>
       <c r="H49" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="I49" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="J49" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="L49" t="s">
         <v>86</v>
       </c>
       <c r="M49" t="s">
-        <v>161</v>
+        <v>94</v>
       </c>
       <c r="N49" t="s">
-        <v>162</v>
+        <v>95</v>
       </c>
       <c r="O49" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="50" spans="7:15" x14ac:dyDescent="0.45">
+      <c r="G50" t="s">
+        <v>86</v>
+      </c>
+      <c r="H50" t="s">
         <v>167</v>
       </c>
-    </row>
-    <row r="50" spans="7:15" x14ac:dyDescent="0.45">
+      <c r="I50" t="s">
+        <v>168</v>
+      </c>
+      <c r="J50" t="s">
+        <v>160</v>
+      </c>
       <c r="L50" t="s">
         <v>86</v>
       </c>
       <c r="M50" t="s">
-        <v>87</v>
+        <v>122</v>
       </c>
       <c r="N50" t="s">
-        <v>88</v>
+        <v>123</v>
       </c>
       <c r="O50" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
     </row>
     <row r="51" spans="7:15" x14ac:dyDescent="0.45">
+      <c r="G51" t="s">
+        <v>86</v>
+      </c>
+      <c r="H51" t="s">
+        <v>169</v>
+      </c>
+      <c r="I51" t="s">
+        <v>170</v>
+      </c>
+      <c r="J51" t="s">
+        <v>160</v>
+      </c>
       <c r="L51" t="s">
         <v>86</v>
       </c>
       <c r="M51" t="s">
-        <v>90</v>
+        <v>136</v>
       </c>
       <c r="N51" t="s">
-        <v>91</v>
+        <v>137</v>
       </c>
       <c r="O51" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
     </row>
     <row r="52" spans="7:15" x14ac:dyDescent="0.45">
+      <c r="G52" t="s">
+        <v>86</v>
+      </c>
+      <c r="H52" t="s">
+        <v>171</v>
+      </c>
+      <c r="I52" t="s">
+        <v>172</v>
+      </c>
+      <c r="J52" t="s">
+        <v>160</v>
+      </c>
       <c r="L52" t="s">
         <v>86</v>
       </c>
       <c r="M52" t="s">
-        <v>180</v>
+        <v>114</v>
       </c>
       <c r="N52" t="s">
-        <v>181</v>
+        <v>115</v>
       </c>
       <c r="O52" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
     </row>
     <row r="53" spans="7:15" x14ac:dyDescent="0.45">
@@ -3226,13 +3358,13 @@
         <v>86</v>
       </c>
       <c r="M53" t="s">
-        <v>142</v>
+        <v>165</v>
       </c>
       <c r="N53" t="s">
-        <v>143</v>
+        <v>166</v>
       </c>
       <c r="O53" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
     </row>
     <row r="54" spans="7:15" x14ac:dyDescent="0.45">
@@ -3240,13 +3372,13 @@
         <v>86</v>
       </c>
       <c r="M54" t="s">
-        <v>94</v>
+        <v>158</v>
       </c>
       <c r="N54" t="s">
-        <v>95</v>
+        <v>159</v>
       </c>
       <c r="O54" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
     </row>
     <row r="55" spans="7:15" x14ac:dyDescent="0.45">
@@ -3254,13 +3386,13 @@
         <v>86</v>
       </c>
       <c r="M55" t="s">
-        <v>182</v>
+        <v>154</v>
       </c>
       <c r="N55" t="s">
-        <v>183</v>
+        <v>155</v>
       </c>
       <c r="O55" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
     </row>
     <row r="56" spans="7:15" x14ac:dyDescent="0.45">
@@ -3268,13 +3400,13 @@
         <v>86</v>
       </c>
       <c r="M56" t="s">
-        <v>184</v>
+        <v>171</v>
       </c>
       <c r="N56" t="s">
-        <v>185</v>
+        <v>172</v>
       </c>
       <c r="O56" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
     </row>
     <row r="57" spans="7:15" x14ac:dyDescent="0.45">
@@ -3282,13 +3414,13 @@
         <v>86</v>
       </c>
       <c r="M57" t="s">
-        <v>163</v>
+        <v>128</v>
       </c>
       <c r="N57" t="s">
-        <v>164</v>
+        <v>129</v>
       </c>
       <c r="O57" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
     </row>
     <row r="58" spans="7:15" x14ac:dyDescent="0.45">
@@ -3296,13 +3428,97 @@
         <v>86</v>
       </c>
       <c r="M58" t="s">
-        <v>108</v>
+        <v>120</v>
       </c>
       <c r="N58" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="O58" t="s">
-        <v>167</v>
+        <v>173</v>
+      </c>
+    </row>
+    <row r="59" spans="7:15" x14ac:dyDescent="0.45">
+      <c r="L59" t="s">
+        <v>86</v>
+      </c>
+      <c r="M59" t="s">
+        <v>150</v>
+      </c>
+      <c r="N59" t="s">
+        <v>151</v>
+      </c>
+      <c r="O59" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="60" spans="7:15" x14ac:dyDescent="0.45">
+      <c r="L60" t="s">
+        <v>86</v>
+      </c>
+      <c r="M60" t="s">
+        <v>194</v>
+      </c>
+      <c r="N60" t="s">
+        <v>195</v>
+      </c>
+      <c r="O60" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="61" spans="7:15" x14ac:dyDescent="0.45">
+      <c r="L61" t="s">
+        <v>86</v>
+      </c>
+      <c r="M61" t="s">
+        <v>144</v>
+      </c>
+      <c r="N61" t="s">
+        <v>145</v>
+      </c>
+      <c r="O61" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="62" spans="7:15" x14ac:dyDescent="0.45">
+      <c r="L62" t="s">
+        <v>86</v>
+      </c>
+      <c r="M62" t="s">
+        <v>130</v>
+      </c>
+      <c r="N62" t="s">
+        <v>131</v>
+      </c>
+      <c r="O62" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="63" spans="7:15" x14ac:dyDescent="0.45">
+      <c r="L63" t="s">
+        <v>86</v>
+      </c>
+      <c r="M63" t="s">
+        <v>92</v>
+      </c>
+      <c r="N63" t="s">
+        <v>93</v>
+      </c>
+      <c r="O63" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="64" spans="7:15" x14ac:dyDescent="0.45">
+      <c r="L64" t="s">
+        <v>86</v>
+      </c>
+      <c r="M64" t="s">
+        <v>196</v>
+      </c>
+      <c r="N64" t="s">
+        <v>197</v>
+      </c>
+      <c r="O64" t="s">
+        <v>173</v>
       </c>
     </row>
   </sheetData>

--- a/VerveStacks_POL_grids_kan50/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_POL_grids_kan50/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52C3F361-E6B7-43DA-ACB6-A569CD47A093}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DF58408-AA7E-43A6-8512-0427E8D12CF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="984" uniqueCount="200">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="980" uniqueCount="196">
   <si>
     <t>PSET_PN</t>
   </si>
@@ -328,10 +328,10 @@
     <t>at grid node - Poznan_POL</t>
   </si>
   <si>
-    <t>Krakow_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Krakow_POL</t>
+    <t>Skawina_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Skawina_POL</t>
   </si>
   <si>
     <t>Mielec_POL</t>
@@ -418,12 +418,6 @@
     <t>at grid node - Lodz_POL</t>
   </si>
   <si>
-    <t>Ostroleka_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Ostroleka_POL</t>
-  </si>
-  <si>
     <t>Plock_POL</t>
   </si>
   <si>
@@ -502,6 +496,12 @@
     <t>at grid node - Czestochowa_POL</t>
   </si>
   <si>
+    <t>Zabrze_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Zabrze_POL</t>
+  </si>
+  <si>
     <t>Opole_POL</t>
   </si>
   <si>
@@ -523,16 +523,10 @@
     <t>en_battery_4h,en_battery_8h</t>
   </si>
   <si>
-    <t>Ustka_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Ustka_POL</t>
-  </si>
-  <si>
-    <t>Koszalin_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Koszalin_POL</t>
+    <t>Slupsk_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Slupsk_POL</t>
   </si>
   <si>
     <t>KedzierzynKozle_POL</t>
@@ -562,76 +556,70 @@
     <t>e_demand,ev_battery,H2prd_Elc_PEM,H2prd_Elc_ALK</t>
   </si>
   <si>
+    <t>Siedlce_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Siedlce_POL</t>
+  </si>
+  <si>
+    <t>Elk_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Elk_POL</t>
+  </si>
+  <si>
+    <t>Walbrzych_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Walbrzych_POL</t>
+  </si>
+  <si>
+    <t>Olsztyn_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Olsztyn_POL</t>
+  </si>
+  <si>
+    <t>Zamosc_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Zamosc_POL</t>
+  </si>
+  <si>
+    <t>Kielce_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Kielce_POL</t>
+  </si>
+  <si>
     <t>OstrowiecSwietokrz_POL</t>
   </si>
   <si>
     <t>at grid node - OstrowiecSwietokrz_POL</t>
   </si>
   <si>
+    <t>Legnica_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Legnica_POL</t>
+  </si>
+  <si>
+    <t>Chelm_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Chelm_POL</t>
+  </si>
+  <si>
+    <t>Pila_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Pila_POL</t>
+  </si>
+  <si>
     <t>Grajewo_POL</t>
   </si>
   <si>
     <t>at grid node - Grajewo_POL</t>
-  </si>
-  <si>
-    <t>Slupsk_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Slupsk_POL</t>
-  </si>
-  <si>
-    <t>Zamosc_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Zamosc_POL</t>
-  </si>
-  <si>
-    <t>Siedlce_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Siedlce_POL</t>
-  </si>
-  <si>
-    <t>Legnica_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Legnica_POL</t>
-  </si>
-  <si>
-    <t>Chelm_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Chelm_POL</t>
-  </si>
-  <si>
-    <t>Olsztyn_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Olsztyn_POL</t>
-  </si>
-  <si>
-    <t>Elk_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Elk_POL</t>
-  </si>
-  <si>
-    <t>Pila_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Pila_POL</t>
-  </si>
-  <si>
-    <t>Walbrzych_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Walbrzych_POL</t>
-  </si>
-  <si>
-    <t>Kielce_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Kielce_POL</t>
   </si>
   <si>
     <t>h_demand</t>
@@ -1006,7 +994,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{268E9BAB-B98F-4B82-9042-51EABC9ED525}">
-  <dimension ref="B3:Y64"/>
+  <dimension ref="B3:Y62"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
     <row r="3" spans="2:25" x14ac:dyDescent="0.45">
@@ -1126,10 +1114,10 @@
         <v>86</v>
       </c>
       <c r="H11" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="I11" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="J11" t="s">
         <v>160</v>
@@ -1138,37 +1126,37 @@
         <v>86</v>
       </c>
       <c r="M11" t="s">
-        <v>106</v>
+        <v>154</v>
       </c>
       <c r="N11" t="s">
-        <v>107</v>
+        <v>155</v>
       </c>
       <c r="O11" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="Q11" t="s">
         <v>86</v>
       </c>
       <c r="R11" t="s">
-        <v>126</v>
+        <v>100</v>
       </c>
       <c r="S11" t="s">
-        <v>127</v>
+        <v>101</v>
       </c>
       <c r="T11" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="V11" t="s">
         <v>86</v>
       </c>
       <c r="W11" t="s">
-        <v>126</v>
+        <v>100</v>
       </c>
       <c r="X11" t="s">
-        <v>127</v>
+        <v>101</v>
       </c>
       <c r="Y11" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
     </row>
     <row r="12" spans="2:25" x14ac:dyDescent="0.45">
@@ -1188,10 +1176,10 @@
         <v>86</v>
       </c>
       <c r="H12" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="I12" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="J12" t="s">
         <v>160</v>
@@ -1200,37 +1188,37 @@
         <v>86</v>
       </c>
       <c r="M12" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="N12" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="O12" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="Q12" t="s">
         <v>86</v>
       </c>
       <c r="R12" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="S12" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="T12" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="V12" t="s">
         <v>86</v>
       </c>
       <c r="W12" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="X12" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="Y12" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
     </row>
     <row r="13" spans="2:25" x14ac:dyDescent="0.45">
@@ -1250,10 +1238,10 @@
         <v>86</v>
       </c>
       <c r="H13" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="I13" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="J13" t="s">
         <v>160</v>
@@ -1262,37 +1250,37 @@
         <v>86</v>
       </c>
       <c r="M13" t="s">
-        <v>112</v>
+        <v>169</v>
       </c>
       <c r="N13" t="s">
-        <v>113</v>
+        <v>170</v>
       </c>
       <c r="O13" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="Q13" t="s">
         <v>86</v>
       </c>
       <c r="R13" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="S13" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="T13" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="V13" t="s">
         <v>86</v>
       </c>
       <c r="W13" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="X13" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="Y13" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
     </row>
     <row r="14" spans="2:25" x14ac:dyDescent="0.45">
@@ -1324,37 +1312,37 @@
         <v>86</v>
       </c>
       <c r="M14" t="s">
-        <v>161</v>
+        <v>128</v>
       </c>
       <c r="N14" t="s">
-        <v>162</v>
+        <v>129</v>
       </c>
       <c r="O14" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="Q14" t="s">
         <v>86</v>
       </c>
       <c r="R14" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="S14" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="T14" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="V14" t="s">
         <v>86</v>
       </c>
       <c r="W14" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="X14" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="Y14" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
     </row>
     <row r="15" spans="2:25" x14ac:dyDescent="0.45">
@@ -1386,13 +1374,13 @@
         <v>86</v>
       </c>
       <c r="M15" t="s">
-        <v>118</v>
+        <v>134</v>
       </c>
       <c r="N15" t="s">
-        <v>119</v>
+        <v>135</v>
       </c>
       <c r="O15" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="Q15" t="s">
         <v>86</v>
@@ -1404,7 +1392,7 @@
         <v>91</v>
       </c>
       <c r="T15" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="V15" t="s">
         <v>86</v>
@@ -1416,7 +1404,7 @@
         <v>91</v>
       </c>
       <c r="Y15" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
     </row>
     <row r="16" spans="2:25" x14ac:dyDescent="0.45">
@@ -1448,13 +1436,13 @@
         <v>86</v>
       </c>
       <c r="M16" t="s">
-        <v>124</v>
+        <v>172</v>
       </c>
       <c r="N16" t="s">
-        <v>125</v>
+        <v>173</v>
       </c>
       <c r="O16" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="Q16" t="s">
         <v>86</v>
@@ -1466,7 +1454,7 @@
         <v>99</v>
       </c>
       <c r="T16" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="V16" t="s">
         <v>86</v>
@@ -1478,7 +1466,7 @@
         <v>99</v>
       </c>
       <c r="Y16" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
     </row>
     <row r="17" spans="2:25" x14ac:dyDescent="0.45">
@@ -1510,13 +1498,13 @@
         <v>86</v>
       </c>
       <c r="M17" t="s">
-        <v>174</v>
+        <v>161</v>
       </c>
       <c r="N17" t="s">
-        <v>175</v>
+        <v>162</v>
       </c>
       <c r="O17" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="Q17" t="s">
         <v>86</v>
@@ -1528,7 +1516,7 @@
         <v>113</v>
       </c>
       <c r="T17" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="V17" t="s">
         <v>86</v>
@@ -1540,7 +1528,7 @@
         <v>113</v>
       </c>
       <c r="Y17" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
     </row>
     <row r="18" spans="2:25" x14ac:dyDescent="0.45">
@@ -1572,37 +1560,37 @@
         <v>86</v>
       </c>
       <c r="M18" t="s">
-        <v>176</v>
+        <v>144</v>
       </c>
       <c r="N18" t="s">
-        <v>177</v>
+        <v>145</v>
       </c>
       <c r="O18" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="Q18" t="s">
         <v>86</v>
       </c>
       <c r="R18" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="S18" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="T18" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="V18" t="s">
         <v>86</v>
       </c>
       <c r="W18" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="X18" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="Y18" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
     </row>
     <row r="19" spans="2:25" x14ac:dyDescent="0.45">
@@ -1634,13 +1622,13 @@
         <v>86</v>
       </c>
       <c r="M19" t="s">
-        <v>178</v>
+        <v>106</v>
       </c>
       <c r="N19" t="s">
-        <v>179</v>
+        <v>107</v>
       </c>
       <c r="O19" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="Q19" t="s">
         <v>86</v>
@@ -1652,7 +1640,7 @@
         <v>105</v>
       </c>
       <c r="T19" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="V19" t="s">
         <v>86</v>
@@ -1664,7 +1652,7 @@
         <v>105</v>
       </c>
       <c r="Y19" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
     </row>
     <row r="20" spans="2:25" x14ac:dyDescent="0.45">
@@ -1696,13 +1684,13 @@
         <v>86</v>
       </c>
       <c r="M20" t="s">
-        <v>167</v>
+        <v>108</v>
       </c>
       <c r="N20" t="s">
-        <v>168</v>
+        <v>109</v>
       </c>
       <c r="O20" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="Q20" t="s">
         <v>86</v>
@@ -1714,7 +1702,7 @@
         <v>107</v>
       </c>
       <c r="T20" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="V20" t="s">
         <v>86</v>
@@ -1726,7 +1714,7 @@
         <v>107</v>
       </c>
       <c r="Y20" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
     </row>
     <row r="21" spans="2:25" x14ac:dyDescent="0.45">
@@ -1758,13 +1746,13 @@
         <v>86</v>
       </c>
       <c r="M21" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="N21" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="O21" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="Q21" t="s">
         <v>86</v>
@@ -1776,7 +1764,7 @@
         <v>109</v>
       </c>
       <c r="T21" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="V21" t="s">
         <v>86</v>
@@ -1788,7 +1776,7 @@
         <v>109</v>
       </c>
       <c r="Y21" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
     </row>
     <row r="22" spans="2:25" x14ac:dyDescent="0.45">
@@ -1808,10 +1796,10 @@
         <v>86</v>
       </c>
       <c r="H22" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="I22" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="J22" t="s">
         <v>160</v>
@@ -1820,13 +1808,13 @@
         <v>86</v>
       </c>
       <c r="M22" t="s">
-        <v>152</v>
+        <v>142</v>
       </c>
       <c r="N22" t="s">
-        <v>153</v>
+        <v>143</v>
       </c>
       <c r="O22" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="Q22" t="s">
         <v>86</v>
@@ -1838,7 +1826,7 @@
         <v>111</v>
       </c>
       <c r="T22" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="V22" t="s">
         <v>86</v>
@@ -1850,7 +1838,7 @@
         <v>111</v>
       </c>
       <c r="Y22" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
     </row>
     <row r="23" spans="2:25" x14ac:dyDescent="0.45">
@@ -1882,13 +1870,13 @@
         <v>86</v>
       </c>
       <c r="M23" t="s">
-        <v>126</v>
+        <v>100</v>
       </c>
       <c r="N23" t="s">
-        <v>127</v>
+        <v>101</v>
       </c>
       <c r="O23" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="Q23" t="s">
         <v>86</v>
@@ -1900,7 +1888,7 @@
         <v>115</v>
       </c>
       <c r="T23" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="V23" t="s">
         <v>86</v>
@@ -1912,7 +1900,7 @@
         <v>115</v>
       </c>
       <c r="Y23" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
     </row>
     <row r="24" spans="2:25" x14ac:dyDescent="0.45">
@@ -1944,13 +1932,13 @@
         <v>86</v>
       </c>
       <c r="M24" t="s">
-        <v>148</v>
+        <v>176</v>
       </c>
       <c r="N24" t="s">
-        <v>149</v>
+        <v>177</v>
       </c>
       <c r="O24" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="Q24" t="s">
         <v>86</v>
@@ -1962,7 +1950,7 @@
         <v>119</v>
       </c>
       <c r="T24" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="V24" t="s">
         <v>86</v>
@@ -1974,7 +1962,7 @@
         <v>119</v>
       </c>
       <c r="Y24" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
     </row>
     <row r="25" spans="2:25" x14ac:dyDescent="0.45">
@@ -2006,13 +1994,13 @@
         <v>86</v>
       </c>
       <c r="M25" t="s">
-        <v>100</v>
+        <v>148</v>
       </c>
       <c r="N25" t="s">
-        <v>101</v>
+        <v>149</v>
       </c>
       <c r="O25" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="Q25" t="s">
         <v>86</v>
@@ -2024,7 +2012,7 @@
         <v>121</v>
       </c>
       <c r="T25" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="V25" t="s">
         <v>86</v>
@@ -2036,7 +2024,7 @@
         <v>121</v>
       </c>
       <c r="Y25" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
     </row>
     <row r="26" spans="2:25" x14ac:dyDescent="0.45">
@@ -2068,13 +2056,13 @@
         <v>86</v>
       </c>
       <c r="M26" t="s">
-        <v>146</v>
+        <v>124</v>
       </c>
       <c r="N26" t="s">
-        <v>147</v>
+        <v>125</v>
       </c>
       <c r="O26" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="Q26" t="s">
         <v>86</v>
@@ -2086,7 +2074,7 @@
         <v>97</v>
       </c>
       <c r="T26" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="V26" t="s">
         <v>86</v>
@@ -2098,7 +2086,7 @@
         <v>97</v>
       </c>
       <c r="Y26" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
     </row>
     <row r="27" spans="2:25" x14ac:dyDescent="0.45">
@@ -2130,13 +2118,13 @@
         <v>86</v>
       </c>
       <c r="M27" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="N27" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="O27" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="Q27" t="s">
         <v>86</v>
@@ -2148,7 +2136,7 @@
         <v>125</v>
       </c>
       <c r="T27" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="V27" t="s">
         <v>86</v>
@@ -2160,7 +2148,7 @@
         <v>125</v>
       </c>
       <c r="Y27" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
     </row>
     <row r="28" spans="2:25" x14ac:dyDescent="0.45">
@@ -2192,37 +2180,37 @@
         <v>86</v>
       </c>
       <c r="M28" t="s">
-        <v>156</v>
+        <v>92</v>
       </c>
       <c r="N28" t="s">
-        <v>157</v>
+        <v>93</v>
       </c>
       <c r="O28" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="Q28" t="s">
         <v>86</v>
       </c>
       <c r="R28" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="S28" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="T28" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="V28" t="s">
         <v>86</v>
       </c>
       <c r="W28" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="X28" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="Y28" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
     </row>
     <row r="29" spans="2:25" x14ac:dyDescent="0.45">
@@ -2254,13 +2242,13 @@
         <v>86</v>
       </c>
       <c r="M29" t="s">
-        <v>138</v>
+        <v>156</v>
       </c>
       <c r="N29" t="s">
-        <v>139</v>
+        <v>157</v>
       </c>
       <c r="O29" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="Q29" t="s">
         <v>86</v>
@@ -2272,7 +2260,7 @@
         <v>95</v>
       </c>
       <c r="T29" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="V29" t="s">
         <v>86</v>
@@ -2284,7 +2272,7 @@
         <v>95</v>
       </c>
       <c r="Y29" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
     </row>
     <row r="30" spans="2:25" x14ac:dyDescent="0.45">
@@ -2316,37 +2304,37 @@
         <v>86</v>
       </c>
       <c r="M30" t="s">
-        <v>180</v>
+        <v>163</v>
       </c>
       <c r="N30" t="s">
-        <v>181</v>
+        <v>164</v>
       </c>
       <c r="O30" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="Q30" t="s">
         <v>86</v>
       </c>
       <c r="R30" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="S30" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="T30" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="V30" t="s">
         <v>86</v>
       </c>
       <c r="W30" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="X30" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="Y30" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
     </row>
     <row r="31" spans="2:25" x14ac:dyDescent="0.45">
@@ -2378,37 +2366,37 @@
         <v>86</v>
       </c>
       <c r="M31" t="s">
-        <v>140</v>
+        <v>126</v>
       </c>
       <c r="N31" t="s">
-        <v>141</v>
+        <v>127</v>
       </c>
       <c r="O31" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="Q31" t="s">
         <v>86</v>
       </c>
       <c r="R31" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="S31" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="T31" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="V31" t="s">
         <v>86</v>
       </c>
       <c r="W31" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="X31" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="Y31" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
     </row>
     <row r="32" spans="2:25" x14ac:dyDescent="0.45">
@@ -2440,37 +2428,37 @@
         <v>86</v>
       </c>
       <c r="M32" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="N32" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="O32" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="Q32" t="s">
         <v>86</v>
       </c>
       <c r="R32" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="S32" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="T32" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="V32" t="s">
         <v>86</v>
       </c>
       <c r="W32" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="X32" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="Y32" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
     </row>
     <row r="33" spans="2:25" x14ac:dyDescent="0.45">
@@ -2502,37 +2490,37 @@
         <v>86</v>
       </c>
       <c r="M33" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="N33" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="O33" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="Q33" t="s">
         <v>86</v>
       </c>
       <c r="R33" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="S33" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="T33" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="V33" t="s">
         <v>86</v>
       </c>
       <c r="W33" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="X33" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="Y33" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
     </row>
     <row r="34" spans="2:25" x14ac:dyDescent="0.45">
@@ -2564,13 +2552,13 @@
         <v>86</v>
       </c>
       <c r="M34" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="N34" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="O34" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="Q34" t="s">
         <v>86</v>
@@ -2582,7 +2570,7 @@
         <v>103</v>
       </c>
       <c r="T34" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="V34" t="s">
         <v>86</v>
@@ -2594,7 +2582,7 @@
         <v>103</v>
       </c>
       <c r="Y34" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
     </row>
     <row r="35" spans="2:25" x14ac:dyDescent="0.45">
@@ -2614,10 +2602,10 @@
         <v>86</v>
       </c>
       <c r="H35" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="I35" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="J35" t="s">
         <v>160</v>
@@ -2626,37 +2614,37 @@
         <v>86</v>
       </c>
       <c r="M35" t="s">
-        <v>163</v>
+        <v>180</v>
       </c>
       <c r="N35" t="s">
-        <v>164</v>
+        <v>181</v>
       </c>
       <c r="O35" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="Q35" t="s">
         <v>86</v>
       </c>
       <c r="R35" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="S35" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="T35" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="V35" t="s">
         <v>86</v>
       </c>
       <c r="W35" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="X35" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="Y35" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
     </row>
     <row r="36" spans="2:25" x14ac:dyDescent="0.45">
@@ -2688,37 +2676,37 @@
         <v>86</v>
       </c>
       <c r="M36" t="s">
-        <v>116</v>
+        <v>138</v>
       </c>
       <c r="N36" t="s">
-        <v>117</v>
+        <v>139</v>
       </c>
       <c r="O36" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="Q36" t="s">
         <v>86</v>
       </c>
       <c r="R36" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="S36" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="T36" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="V36" t="s">
         <v>86</v>
       </c>
       <c r="W36" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="X36" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="Y36" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
     </row>
     <row r="37" spans="2:25" x14ac:dyDescent="0.45">
@@ -2750,37 +2738,37 @@
         <v>86</v>
       </c>
       <c r="M37" t="s">
-        <v>184</v>
+        <v>167</v>
       </c>
       <c r="N37" t="s">
-        <v>185</v>
+        <v>168</v>
       </c>
       <c r="O37" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="Q37" t="s">
         <v>86</v>
       </c>
       <c r="R37" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="S37" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="T37" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="V37" t="s">
         <v>86</v>
       </c>
       <c r="W37" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="X37" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="Y37" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
     </row>
     <row r="38" spans="2:25" x14ac:dyDescent="0.45">
@@ -2812,37 +2800,37 @@
         <v>86</v>
       </c>
       <c r="M38" t="s">
-        <v>102</v>
+        <v>182</v>
       </c>
       <c r="N38" t="s">
-        <v>103</v>
+        <v>183</v>
       </c>
       <c r="O38" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="Q38" t="s">
         <v>86</v>
       </c>
       <c r="R38" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="S38" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="T38" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="V38" t="s">
         <v>86</v>
       </c>
       <c r="W38" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="X38" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="Y38" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
     </row>
     <row r="39" spans="2:25" x14ac:dyDescent="0.45">
@@ -2862,10 +2850,10 @@
         <v>86</v>
       </c>
       <c r="H39" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="I39" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="J39" t="s">
         <v>160</v>
@@ -2874,37 +2862,37 @@
         <v>86</v>
       </c>
       <c r="M39" t="s">
-        <v>134</v>
+        <v>96</v>
       </c>
       <c r="N39" t="s">
-        <v>135</v>
+        <v>97</v>
       </c>
       <c r="O39" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="Q39" t="s">
         <v>86</v>
       </c>
       <c r="R39" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="S39" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="T39" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="V39" t="s">
         <v>86</v>
       </c>
       <c r="W39" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="X39" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="Y39" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
     </row>
     <row r="40" spans="2:25" x14ac:dyDescent="0.45">
@@ -2936,37 +2924,37 @@
         <v>86</v>
       </c>
       <c r="M40" t="s">
-        <v>87</v>
+        <v>110</v>
       </c>
       <c r="N40" t="s">
-        <v>88</v>
+        <v>111</v>
       </c>
       <c r="O40" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="Q40" t="s">
         <v>86</v>
       </c>
       <c r="R40" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="S40" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="T40" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="V40" t="s">
         <v>86</v>
       </c>
       <c r="W40" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="X40" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="Y40" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
     </row>
     <row r="41" spans="2:25" x14ac:dyDescent="0.45">
@@ -2986,10 +2974,10 @@
         <v>86</v>
       </c>
       <c r="H41" t="s">
-        <v>144</v>
+        <v>161</v>
       </c>
       <c r="I41" t="s">
-        <v>145</v>
+        <v>162</v>
       </c>
       <c r="J41" t="s">
         <v>160</v>
@@ -2998,13 +2986,37 @@
         <v>86</v>
       </c>
       <c r="M41" t="s">
-        <v>186</v>
+        <v>102</v>
       </c>
       <c r="N41" t="s">
-        <v>187</v>
+        <v>103</v>
       </c>
       <c r="O41" t="s">
-        <v>173</v>
+        <v>171</v>
+      </c>
+      <c r="Q41" t="s">
+        <v>86</v>
+      </c>
+      <c r="R41" t="s">
+        <v>158</v>
+      </c>
+      <c r="S41" t="s">
+        <v>159</v>
+      </c>
+      <c r="T41" t="s">
+        <v>194</v>
+      </c>
+      <c r="V41" t="s">
+        <v>86</v>
+      </c>
+      <c r="W41" t="s">
+        <v>158</v>
+      </c>
+      <c r="X41" t="s">
+        <v>159</v>
+      </c>
+      <c r="Y41" t="s">
+        <v>195</v>
       </c>
     </row>
     <row r="42" spans="2:25" x14ac:dyDescent="0.45">
@@ -3024,10 +3036,10 @@
         <v>86</v>
       </c>
       <c r="H42" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="I42" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="J42" t="s">
         <v>160</v>
@@ -3036,13 +3048,13 @@
         <v>86</v>
       </c>
       <c r="M42" t="s">
-        <v>108</v>
+        <v>184</v>
       </c>
       <c r="N42" t="s">
-        <v>109</v>
+        <v>185</v>
       </c>
       <c r="O42" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="43" spans="2:25" x14ac:dyDescent="0.45">
@@ -3062,10 +3074,10 @@
         <v>86</v>
       </c>
       <c r="H43" t="s">
-        <v>163</v>
+        <v>144</v>
       </c>
       <c r="I43" t="s">
-        <v>164</v>
+        <v>145</v>
       </c>
       <c r="J43" t="s">
         <v>160</v>
@@ -3074,13 +3086,13 @@
         <v>86</v>
       </c>
       <c r="M43" t="s">
-        <v>98</v>
+        <v>146</v>
       </c>
       <c r="N43" t="s">
-        <v>99</v>
+        <v>147</v>
       </c>
       <c r="O43" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="44" spans="2:25" x14ac:dyDescent="0.45">
@@ -3100,10 +3112,10 @@
         <v>86</v>
       </c>
       <c r="H44" t="s">
-        <v>165</v>
+        <v>148</v>
       </c>
       <c r="I44" t="s">
-        <v>166</v>
+        <v>149</v>
       </c>
       <c r="J44" t="s">
         <v>160</v>
@@ -3112,13 +3124,13 @@
         <v>86</v>
       </c>
       <c r="M44" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="N44" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="O44" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.45">
@@ -3138,10 +3150,10 @@
         <v>86</v>
       </c>
       <c r="H45" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="I45" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="J45" t="s">
         <v>160</v>
@@ -3150,13 +3162,13 @@
         <v>86</v>
       </c>
       <c r="M45" t="s">
-        <v>132</v>
+        <v>186</v>
       </c>
       <c r="N45" t="s">
-        <v>133</v>
+        <v>187</v>
       </c>
       <c r="O45" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="46" spans="2:25" x14ac:dyDescent="0.45">
@@ -3176,10 +3188,10 @@
         <v>86</v>
       </c>
       <c r="H46" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="I46" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="J46" t="s">
         <v>160</v>
@@ -3194,7 +3206,7 @@
         <v>189</v>
       </c>
       <c r="O46" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="47" spans="2:25" x14ac:dyDescent="0.45">
@@ -3202,10 +3214,10 @@
         <v>86</v>
       </c>
       <c r="H47" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="I47" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="J47" t="s">
         <v>160</v>
@@ -3214,13 +3226,13 @@
         <v>86</v>
       </c>
       <c r="M47" t="s">
-        <v>190</v>
+        <v>116</v>
       </c>
       <c r="N47" t="s">
-        <v>191</v>
+        <v>117</v>
       </c>
       <c r="O47" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="48" spans="2:25" x14ac:dyDescent="0.45">
@@ -3228,10 +3240,10 @@
         <v>86</v>
       </c>
       <c r="H48" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="I48" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="J48" t="s">
         <v>160</v>
@@ -3240,13 +3252,13 @@
         <v>86</v>
       </c>
       <c r="M48" t="s">
-        <v>192</v>
+        <v>104</v>
       </c>
       <c r="N48" t="s">
-        <v>193</v>
+        <v>105</v>
       </c>
       <c r="O48" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="49" spans="7:15" x14ac:dyDescent="0.45">
@@ -3254,10 +3266,10 @@
         <v>86</v>
       </c>
       <c r="H49" t="s">
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="I49" t="s">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="J49" t="s">
         <v>160</v>
@@ -3266,13 +3278,13 @@
         <v>86</v>
       </c>
       <c r="M49" t="s">
-        <v>94</v>
+        <v>114</v>
       </c>
       <c r="N49" t="s">
-        <v>95</v>
+        <v>115</v>
       </c>
       <c r="O49" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="50" spans="7:15" x14ac:dyDescent="0.45">
@@ -3292,13 +3304,13 @@
         <v>86</v>
       </c>
       <c r="M50" t="s">
-        <v>122</v>
+        <v>190</v>
       </c>
       <c r="N50" t="s">
-        <v>123</v>
+        <v>191</v>
       </c>
       <c r="O50" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="51" spans="7:15" x14ac:dyDescent="0.45">
@@ -3318,39 +3330,27 @@
         <v>86</v>
       </c>
       <c r="M51" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="N51" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="O51" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="52" spans="7:15" x14ac:dyDescent="0.45">
-      <c r="G52" t="s">
-        <v>86</v>
-      </c>
-      <c r="H52" t="s">
-        <v>171</v>
-      </c>
-      <c r="I52" t="s">
-        <v>172</v>
-      </c>
-      <c r="J52" t="s">
-        <v>160</v>
-      </c>
       <c r="L52" t="s">
         <v>86</v>
       </c>
       <c r="M52" t="s">
-        <v>114</v>
+        <v>192</v>
       </c>
       <c r="N52" t="s">
-        <v>115</v>
+        <v>193</v>
       </c>
       <c r="O52" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="53" spans="7:15" x14ac:dyDescent="0.45">
@@ -3358,13 +3358,13 @@
         <v>86</v>
       </c>
       <c r="M53" t="s">
-        <v>165</v>
+        <v>90</v>
       </c>
       <c r="N53" t="s">
-        <v>166</v>
+        <v>91</v>
       </c>
       <c r="O53" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="54" spans="7:15" x14ac:dyDescent="0.45">
@@ -3372,13 +3372,13 @@
         <v>86</v>
       </c>
       <c r="M54" t="s">
-        <v>158</v>
+        <v>130</v>
       </c>
       <c r="N54" t="s">
-        <v>159</v>
+        <v>131</v>
       </c>
       <c r="O54" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="55" spans="7:15" x14ac:dyDescent="0.45">
@@ -3386,13 +3386,13 @@
         <v>86</v>
       </c>
       <c r="M55" t="s">
-        <v>154</v>
+        <v>165</v>
       </c>
       <c r="N55" t="s">
-        <v>155</v>
+        <v>166</v>
       </c>
       <c r="O55" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="56" spans="7:15" x14ac:dyDescent="0.45">
@@ -3400,13 +3400,13 @@
         <v>86</v>
       </c>
       <c r="M56" t="s">
-        <v>171</v>
+        <v>152</v>
       </c>
       <c r="N56" t="s">
-        <v>172</v>
+        <v>153</v>
       </c>
       <c r="O56" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="57" spans="7:15" x14ac:dyDescent="0.45">
@@ -3414,13 +3414,13 @@
         <v>86</v>
       </c>
       <c r="M57" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="N57" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="O57" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="58" spans="7:15" x14ac:dyDescent="0.45">
@@ -3428,13 +3428,13 @@
         <v>86</v>
       </c>
       <c r="M58" t="s">
-        <v>120</v>
+        <v>158</v>
       </c>
       <c r="N58" t="s">
-        <v>121</v>
+        <v>159</v>
       </c>
       <c r="O58" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="59" spans="7:15" x14ac:dyDescent="0.45">
@@ -3442,13 +3442,13 @@
         <v>86</v>
       </c>
       <c r="M59" t="s">
-        <v>150</v>
+        <v>118</v>
       </c>
       <c r="N59" t="s">
-        <v>151</v>
+        <v>119</v>
       </c>
       <c r="O59" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="60" spans="7:15" x14ac:dyDescent="0.45">
@@ -3456,13 +3456,13 @@
         <v>86</v>
       </c>
       <c r="M60" t="s">
-        <v>194</v>
+        <v>120</v>
       </c>
       <c r="N60" t="s">
-        <v>195</v>
+        <v>121</v>
       </c>
       <c r="O60" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="61" spans="7:15" x14ac:dyDescent="0.45">
@@ -3470,13 +3470,13 @@
         <v>86</v>
       </c>
       <c r="M61" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="N61" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="O61" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="62" spans="7:15" x14ac:dyDescent="0.45">
@@ -3484,41 +3484,13 @@
         <v>86</v>
       </c>
       <c r="M62" t="s">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="N62" t="s">
-        <v>131</v>
+        <v>141</v>
       </c>
       <c r="O62" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="63" spans="7:15" x14ac:dyDescent="0.45">
-      <c r="L63" t="s">
-        <v>86</v>
-      </c>
-      <c r="M63" t="s">
-        <v>92</v>
-      </c>
-      <c r="N63" t="s">
-        <v>93</v>
-      </c>
-      <c r="O63" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="64" spans="7:15" x14ac:dyDescent="0.45">
-      <c r="L64" t="s">
-        <v>86</v>
-      </c>
-      <c r="M64" t="s">
-        <v>196</v>
-      </c>
-      <c r="N64" t="s">
-        <v>197</v>
-      </c>
-      <c r="O64" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
   </sheetData>

--- a/VerveStacks_POL_grids_kan50/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_POL_grids_kan50/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DF58408-AA7E-43A6-8512-0427E8D12CF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54054DC5-6DED-4561-A777-7A93D965FC74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -556,70 +556,70 @@
     <t>e_demand,ev_battery,H2prd_Elc_PEM,H2prd_Elc_ALK</t>
   </si>
   <si>
+    <t>OstrowiecSwietokrz_POL</t>
+  </si>
+  <si>
+    <t>at grid node - OstrowiecSwietokrz_POL</t>
+  </si>
+  <si>
     <t>Siedlce_POL</t>
   </si>
   <si>
     <t>at grid node - Siedlce_POL</t>
   </si>
   <si>
+    <t>Kielce_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Kielce_POL</t>
+  </si>
+  <si>
+    <t>Pila_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Pila_POL</t>
+  </si>
+  <si>
+    <t>Walbrzych_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Walbrzych_POL</t>
+  </si>
+  <si>
+    <t>Legnica_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Legnica_POL</t>
+  </si>
+  <si>
+    <t>Olsztyn_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Olsztyn_POL</t>
+  </si>
+  <si>
+    <t>Zamosc_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Zamosc_POL</t>
+  </si>
+  <si>
+    <t>Grajewo_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Grajewo_POL</t>
+  </si>
+  <si>
     <t>Elk_POL</t>
   </si>
   <si>
     <t>at grid node - Elk_POL</t>
   </si>
   <si>
-    <t>Walbrzych_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Walbrzych_POL</t>
-  </si>
-  <si>
-    <t>Olsztyn_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Olsztyn_POL</t>
-  </si>
-  <si>
-    <t>Zamosc_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Zamosc_POL</t>
-  </si>
-  <si>
-    <t>Kielce_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Kielce_POL</t>
-  </si>
-  <si>
-    <t>OstrowiecSwietokrz_POL</t>
-  </si>
-  <si>
-    <t>at grid node - OstrowiecSwietokrz_POL</t>
-  </si>
-  <si>
-    <t>Legnica_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Legnica_POL</t>
-  </si>
-  <si>
     <t>Chelm_POL</t>
   </si>
   <si>
     <t>at grid node - Chelm_POL</t>
-  </si>
-  <si>
-    <t>Pila_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Pila_POL</t>
-  </si>
-  <si>
-    <t>Grajewo_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Grajewo_POL</t>
   </si>
   <si>
     <t>h_demand</t>
@@ -1126,10 +1126,10 @@
         <v>86</v>
       </c>
       <c r="M11" t="s">
-        <v>154</v>
+        <v>120</v>
       </c>
       <c r="N11" t="s">
-        <v>155</v>
+        <v>121</v>
       </c>
       <c r="O11" t="s">
         <v>171</v>
@@ -1188,10 +1188,10 @@
         <v>86</v>
       </c>
       <c r="M12" t="s">
-        <v>87</v>
+        <v>118</v>
       </c>
       <c r="N12" t="s">
-        <v>88</v>
+        <v>119</v>
       </c>
       <c r="O12" t="s">
         <v>171</v>
@@ -1250,10 +1250,10 @@
         <v>86</v>
       </c>
       <c r="M13" t="s">
-        <v>169</v>
+        <v>126</v>
       </c>
       <c r="N13" t="s">
-        <v>170</v>
+        <v>127</v>
       </c>
       <c r="O13" t="s">
         <v>171</v>
@@ -1312,10 +1312,10 @@
         <v>86</v>
       </c>
       <c r="M14" t="s">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="N14" t="s">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="O14" t="s">
         <v>171</v>
@@ -1374,10 +1374,10 @@
         <v>86</v>
       </c>
       <c r="M15" t="s">
-        <v>134</v>
+        <v>165</v>
       </c>
       <c r="N15" t="s">
-        <v>135</v>
+        <v>166</v>
       </c>
       <c r="O15" t="s">
         <v>171</v>
@@ -1498,10 +1498,10 @@
         <v>86</v>
       </c>
       <c r="M17" t="s">
-        <v>161</v>
+        <v>174</v>
       </c>
       <c r="N17" t="s">
-        <v>162</v>
+        <v>175</v>
       </c>
       <c r="O17" t="s">
         <v>171</v>
@@ -1560,10 +1560,10 @@
         <v>86</v>
       </c>
       <c r="M18" t="s">
-        <v>144</v>
+        <v>100</v>
       </c>
       <c r="N18" t="s">
-        <v>145</v>
+        <v>101</v>
       </c>
       <c r="O18" t="s">
         <v>171</v>
@@ -1622,10 +1622,10 @@
         <v>86</v>
       </c>
       <c r="M19" t="s">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="N19" t="s">
-        <v>107</v>
+        <v>93</v>
       </c>
       <c r="O19" t="s">
         <v>171</v>
@@ -1684,10 +1684,10 @@
         <v>86</v>
       </c>
       <c r="M20" t="s">
-        <v>108</v>
+        <v>176</v>
       </c>
       <c r="N20" t="s">
-        <v>109</v>
+        <v>177</v>
       </c>
       <c r="O20" t="s">
         <v>171</v>
@@ -1746,10 +1746,10 @@
         <v>86</v>
       </c>
       <c r="M21" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="N21" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="O21" t="s">
         <v>171</v>
@@ -1808,10 +1808,10 @@
         <v>86</v>
       </c>
       <c r="M22" t="s">
-        <v>142</v>
+        <v>158</v>
       </c>
       <c r="N22" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
       <c r="O22" t="s">
         <v>171</v>
@@ -1870,10 +1870,10 @@
         <v>86</v>
       </c>
       <c r="M23" t="s">
-        <v>100</v>
+        <v>161</v>
       </c>
       <c r="N23" t="s">
-        <v>101</v>
+        <v>162</v>
       </c>
       <c r="O23" t="s">
         <v>171</v>
@@ -1932,10 +1932,10 @@
         <v>86</v>
       </c>
       <c r="M24" t="s">
-        <v>176</v>
+        <v>152</v>
       </c>
       <c r="N24" t="s">
-        <v>177</v>
+        <v>153</v>
       </c>
       <c r="O24" t="s">
         <v>171</v>
@@ -1994,10 +1994,10 @@
         <v>86</v>
       </c>
       <c r="M25" t="s">
-        <v>148</v>
+        <v>94</v>
       </c>
       <c r="N25" t="s">
-        <v>149</v>
+        <v>95</v>
       </c>
       <c r="O25" t="s">
         <v>171</v>
@@ -2056,10 +2056,10 @@
         <v>86</v>
       </c>
       <c r="M26" t="s">
-        <v>124</v>
+        <v>140</v>
       </c>
       <c r="N26" t="s">
-        <v>125</v>
+        <v>141</v>
       </c>
       <c r="O26" t="s">
         <v>171</v>
@@ -2118,10 +2118,10 @@
         <v>86</v>
       </c>
       <c r="M27" t="s">
-        <v>136</v>
+        <v>122</v>
       </c>
       <c r="N27" t="s">
-        <v>137</v>
+        <v>123</v>
       </c>
       <c r="O27" t="s">
         <v>171</v>
@@ -2180,10 +2180,10 @@
         <v>86</v>
       </c>
       <c r="M28" t="s">
-        <v>92</v>
+        <v>114</v>
       </c>
       <c r="N28" t="s">
-        <v>93</v>
+        <v>115</v>
       </c>
       <c r="O28" t="s">
         <v>171</v>
@@ -2242,10 +2242,10 @@
         <v>86</v>
       </c>
       <c r="M29" t="s">
-        <v>156</v>
+        <v>130</v>
       </c>
       <c r="N29" t="s">
-        <v>157</v>
+        <v>131</v>
       </c>
       <c r="O29" t="s">
         <v>171</v>
@@ -2304,10 +2304,10 @@
         <v>86</v>
       </c>
       <c r="M30" t="s">
-        <v>163</v>
+        <v>102</v>
       </c>
       <c r="N30" t="s">
-        <v>164</v>
+        <v>103</v>
       </c>
       <c r="O30" t="s">
         <v>171</v>
@@ -2366,10 +2366,10 @@
         <v>86</v>
       </c>
       <c r="M31" t="s">
-        <v>126</v>
+        <v>148</v>
       </c>
       <c r="N31" t="s">
-        <v>127</v>
+        <v>149</v>
       </c>
       <c r="O31" t="s">
         <v>171</v>
@@ -2428,10 +2428,10 @@
         <v>86</v>
       </c>
       <c r="M32" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="N32" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="O32" t="s">
         <v>171</v>
@@ -2490,10 +2490,10 @@
         <v>86</v>
       </c>
       <c r="M33" t="s">
-        <v>98</v>
+        <v>124</v>
       </c>
       <c r="N33" t="s">
-        <v>99</v>
+        <v>125</v>
       </c>
       <c r="O33" t="s">
         <v>171</v>
@@ -2552,10 +2552,10 @@
         <v>86</v>
       </c>
       <c r="M34" t="s">
-        <v>112</v>
+        <v>150</v>
       </c>
       <c r="N34" t="s">
-        <v>113</v>
+        <v>151</v>
       </c>
       <c r="O34" t="s">
         <v>171</v>
@@ -2614,10 +2614,10 @@
         <v>86</v>
       </c>
       <c r="M35" t="s">
-        <v>180</v>
+        <v>128</v>
       </c>
       <c r="N35" t="s">
-        <v>181</v>
+        <v>129</v>
       </c>
       <c r="O35" t="s">
         <v>171</v>
@@ -2676,10 +2676,10 @@
         <v>86</v>
       </c>
       <c r="M36" t="s">
-        <v>138</v>
+        <v>182</v>
       </c>
       <c r="N36" t="s">
-        <v>139</v>
+        <v>183</v>
       </c>
       <c r="O36" t="s">
         <v>171</v>
@@ -2738,10 +2738,10 @@
         <v>86</v>
       </c>
       <c r="M37" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="N37" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="O37" t="s">
         <v>171</v>
@@ -2800,10 +2800,10 @@
         <v>86</v>
       </c>
       <c r="M38" t="s">
-        <v>182</v>
+        <v>138</v>
       </c>
       <c r="N38" t="s">
-        <v>183</v>
+        <v>139</v>
       </c>
       <c r="O38" t="s">
         <v>171</v>
@@ -2862,10 +2862,10 @@
         <v>86</v>
       </c>
       <c r="M39" t="s">
-        <v>96</v>
+        <v>154</v>
       </c>
       <c r="N39" t="s">
-        <v>97</v>
+        <v>155</v>
       </c>
       <c r="O39" t="s">
         <v>171</v>
@@ -2924,10 +2924,10 @@
         <v>86</v>
       </c>
       <c r="M40" t="s">
-        <v>110</v>
+        <v>96</v>
       </c>
       <c r="N40" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="O40" t="s">
         <v>171</v>
@@ -2986,10 +2986,10 @@
         <v>86</v>
       </c>
       <c r="M41" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="N41" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="O41" t="s">
         <v>171</v>
@@ -3048,10 +3048,10 @@
         <v>86</v>
       </c>
       <c r="M42" t="s">
-        <v>184</v>
+        <v>167</v>
       </c>
       <c r="N42" t="s">
-        <v>185</v>
+        <v>168</v>
       </c>
       <c r="O42" t="s">
         <v>171</v>
@@ -3086,10 +3086,10 @@
         <v>86</v>
       </c>
       <c r="M43" t="s">
-        <v>146</v>
+        <v>132</v>
       </c>
       <c r="N43" t="s">
-        <v>147</v>
+        <v>133</v>
       </c>
       <c r="O43" t="s">
         <v>171</v>
@@ -3124,10 +3124,10 @@
         <v>86</v>
       </c>
       <c r="M44" t="s">
-        <v>94</v>
+        <v>110</v>
       </c>
       <c r="N44" t="s">
-        <v>95</v>
+        <v>111</v>
       </c>
       <c r="O44" t="s">
         <v>171</v>
@@ -3162,10 +3162,10 @@
         <v>86</v>
       </c>
       <c r="M45" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="N45" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="O45" t="s">
         <v>171</v>
@@ -3200,10 +3200,10 @@
         <v>86</v>
       </c>
       <c r="M46" t="s">
-        <v>188</v>
+        <v>90</v>
       </c>
       <c r="N46" t="s">
-        <v>189</v>
+        <v>91</v>
       </c>
       <c r="O46" t="s">
         <v>171</v>
@@ -3226,10 +3226,10 @@
         <v>86</v>
       </c>
       <c r="M47" t="s">
-        <v>116</v>
+        <v>146</v>
       </c>
       <c r="N47" t="s">
-        <v>117</v>
+        <v>147</v>
       </c>
       <c r="O47" t="s">
         <v>171</v>
@@ -3278,10 +3278,10 @@
         <v>86</v>
       </c>
       <c r="M49" t="s">
-        <v>114</v>
+        <v>142</v>
       </c>
       <c r="N49" t="s">
-        <v>115</v>
+        <v>143</v>
       </c>
       <c r="O49" t="s">
         <v>171</v>
@@ -3304,10 +3304,10 @@
         <v>86</v>
       </c>
       <c r="M50" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="N50" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="O50" t="s">
         <v>171</v>
@@ -3330,10 +3330,10 @@
         <v>86</v>
       </c>
       <c r="M51" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="N51" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="O51" t="s">
         <v>171</v>
@@ -3344,10 +3344,10 @@
         <v>86</v>
       </c>
       <c r="M52" t="s">
-        <v>192</v>
+        <v>156</v>
       </c>
       <c r="N52" t="s">
-        <v>193</v>
+        <v>157</v>
       </c>
       <c r="O52" t="s">
         <v>171</v>
@@ -3358,10 +3358,10 @@
         <v>86</v>
       </c>
       <c r="M53" t="s">
-        <v>90</v>
+        <v>144</v>
       </c>
       <c r="N53" t="s">
-        <v>91</v>
+        <v>145</v>
       </c>
       <c r="O53" t="s">
         <v>171</v>
@@ -3372,10 +3372,10 @@
         <v>86</v>
       </c>
       <c r="M54" t="s">
-        <v>130</v>
+        <v>87</v>
       </c>
       <c r="N54" t="s">
-        <v>131</v>
+        <v>88</v>
       </c>
       <c r="O54" t="s">
         <v>171</v>
@@ -3386,10 +3386,10 @@
         <v>86</v>
       </c>
       <c r="M55" t="s">
-        <v>165</v>
+        <v>188</v>
       </c>
       <c r="N55" t="s">
-        <v>166</v>
+        <v>189</v>
       </c>
       <c r="O55" t="s">
         <v>171</v>
@@ -3400,10 +3400,10 @@
         <v>86</v>
       </c>
       <c r="M56" t="s">
-        <v>152</v>
+        <v>112</v>
       </c>
       <c r="N56" t="s">
-        <v>153</v>
+        <v>113</v>
       </c>
       <c r="O56" t="s">
         <v>171</v>
@@ -3414,10 +3414,10 @@
         <v>86</v>
       </c>
       <c r="M57" t="s">
-        <v>122</v>
+        <v>190</v>
       </c>
       <c r="N57" t="s">
-        <v>123</v>
+        <v>191</v>
       </c>
       <c r="O57" t="s">
         <v>171</v>
@@ -3428,10 +3428,10 @@
         <v>86</v>
       </c>
       <c r="M58" t="s">
-        <v>158</v>
+        <v>108</v>
       </c>
       <c r="N58" t="s">
-        <v>159</v>
+        <v>109</v>
       </c>
       <c r="O58" t="s">
         <v>171</v>
@@ -3442,10 +3442,10 @@
         <v>86</v>
       </c>
       <c r="M59" t="s">
-        <v>118</v>
+        <v>106</v>
       </c>
       <c r="N59" t="s">
-        <v>119</v>
+        <v>107</v>
       </c>
       <c r="O59" t="s">
         <v>171</v>
@@ -3456,10 +3456,10 @@
         <v>86</v>
       </c>
       <c r="M60" t="s">
-        <v>120</v>
+        <v>163</v>
       </c>
       <c r="N60" t="s">
-        <v>121</v>
+        <v>164</v>
       </c>
       <c r="O60" t="s">
         <v>171</v>
@@ -3470,10 +3470,10 @@
         <v>86</v>
       </c>
       <c r="M61" t="s">
-        <v>150</v>
+        <v>192</v>
       </c>
       <c r="N61" t="s">
-        <v>151</v>
+        <v>193</v>
       </c>
       <c r="O61" t="s">
         <v>171</v>
@@ -3484,10 +3484,10 @@
         <v>86</v>
       </c>
       <c r="M62" t="s">
-        <v>140</v>
+        <v>116</v>
       </c>
       <c r="N62" t="s">
-        <v>141</v>
+        <v>117</v>
       </c>
       <c r="O62" t="s">
         <v>171</v>

--- a/VerveStacks_POL_grids_kan50/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_POL_grids_kan50/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54054DC5-6DED-4561-A777-7A93D965FC74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCCFC7B7-9496-41ED-9290-9591ED5D9353}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -556,70 +556,70 @@
     <t>e_demand,ev_battery,H2prd_Elc_PEM,H2prd_Elc_ALK</t>
   </si>
   <si>
+    <t>Pila_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Pila_POL</t>
+  </si>
+  <si>
+    <t>Zamosc_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Zamosc_POL</t>
+  </si>
+  <si>
+    <t>Elk_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Elk_POL</t>
+  </si>
+  <si>
+    <t>Siedlce_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Siedlce_POL</t>
+  </si>
+  <si>
+    <t>Legnica_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Legnica_POL</t>
+  </si>
+  <si>
+    <t>Kielce_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Kielce_POL</t>
+  </si>
+  <si>
+    <t>Olsztyn_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Olsztyn_POL</t>
+  </si>
+  <si>
     <t>OstrowiecSwietokrz_POL</t>
   </si>
   <si>
     <t>at grid node - OstrowiecSwietokrz_POL</t>
   </si>
   <si>
-    <t>Siedlce_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Siedlce_POL</t>
-  </si>
-  <si>
-    <t>Kielce_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Kielce_POL</t>
-  </si>
-  <si>
-    <t>Pila_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Pila_POL</t>
-  </si>
-  <si>
     <t>Walbrzych_POL</t>
   </si>
   <si>
     <t>at grid node - Walbrzych_POL</t>
   </si>
   <si>
-    <t>Legnica_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Legnica_POL</t>
-  </si>
-  <si>
-    <t>Olsztyn_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Olsztyn_POL</t>
-  </si>
-  <si>
-    <t>Zamosc_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Zamosc_POL</t>
+    <t>Chelm_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Chelm_POL</t>
   </si>
   <si>
     <t>Grajewo_POL</t>
   </si>
   <si>
     <t>at grid node - Grajewo_POL</t>
-  </si>
-  <si>
-    <t>Elk_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Elk_POL</t>
-  </si>
-  <si>
-    <t>Chelm_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Chelm_POL</t>
   </si>
   <si>
     <t>h_demand</t>
@@ -1126,10 +1126,10 @@
         <v>86</v>
       </c>
       <c r="M11" t="s">
-        <v>120</v>
+        <v>102</v>
       </c>
       <c r="N11" t="s">
-        <v>121</v>
+        <v>103</v>
       </c>
       <c r="O11" t="s">
         <v>171</v>
@@ -1188,10 +1188,10 @@
         <v>86</v>
       </c>
       <c r="M12" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="N12" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="O12" t="s">
         <v>171</v>
@@ -1250,10 +1250,10 @@
         <v>86</v>
       </c>
       <c r="M13" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="N13" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="O13" t="s">
         <v>171</v>
@@ -1312,10 +1312,10 @@
         <v>86</v>
       </c>
       <c r="M14" t="s">
-        <v>136</v>
+        <v>100</v>
       </c>
       <c r="N14" t="s">
-        <v>137</v>
+        <v>101</v>
       </c>
       <c r="O14" t="s">
         <v>171</v>
@@ -1374,10 +1374,10 @@
         <v>86</v>
       </c>
       <c r="M15" t="s">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="N15" t="s">
-        <v>166</v>
+        <v>173</v>
       </c>
       <c r="O15" t="s">
         <v>171</v>
@@ -1436,10 +1436,10 @@
         <v>86</v>
       </c>
       <c r="M16" t="s">
-        <v>172</v>
+        <v>104</v>
       </c>
       <c r="N16" t="s">
-        <v>173</v>
+        <v>105</v>
       </c>
       <c r="O16" t="s">
         <v>171</v>
@@ -1498,10 +1498,10 @@
         <v>86</v>
       </c>
       <c r="M17" t="s">
-        <v>174</v>
+        <v>136</v>
       </c>
       <c r="N17" t="s">
-        <v>175</v>
+        <v>137</v>
       </c>
       <c r="O17" t="s">
         <v>171</v>
@@ -1560,10 +1560,10 @@
         <v>86</v>
       </c>
       <c r="M18" t="s">
-        <v>100</v>
+        <v>161</v>
       </c>
       <c r="N18" t="s">
-        <v>101</v>
+        <v>162</v>
       </c>
       <c r="O18" t="s">
         <v>171</v>
@@ -1622,10 +1622,10 @@
         <v>86</v>
       </c>
       <c r="M19" t="s">
-        <v>92</v>
+        <v>174</v>
       </c>
       <c r="N19" t="s">
-        <v>93</v>
+        <v>175</v>
       </c>
       <c r="O19" t="s">
         <v>171</v>
@@ -1746,10 +1746,10 @@
         <v>86</v>
       </c>
       <c r="M21" t="s">
-        <v>178</v>
+        <v>134</v>
       </c>
       <c r="N21" t="s">
-        <v>179</v>
+        <v>135</v>
       </c>
       <c r="O21" t="s">
         <v>171</v>
@@ -1808,10 +1808,10 @@
         <v>86</v>
       </c>
       <c r="M22" t="s">
-        <v>158</v>
+        <v>178</v>
       </c>
       <c r="N22" t="s">
-        <v>159</v>
+        <v>179</v>
       </c>
       <c r="O22" t="s">
         <v>171</v>
@@ -1870,10 +1870,10 @@
         <v>86</v>
       </c>
       <c r="M23" t="s">
-        <v>161</v>
+        <v>152</v>
       </c>
       <c r="N23" t="s">
-        <v>162</v>
+        <v>153</v>
       </c>
       <c r="O23" t="s">
         <v>171</v>
@@ -1932,10 +1932,10 @@
         <v>86</v>
       </c>
       <c r="M24" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="N24" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="O24" t="s">
         <v>171</v>
@@ -1994,10 +1994,10 @@
         <v>86</v>
       </c>
       <c r="M25" t="s">
-        <v>94</v>
+        <v>106</v>
       </c>
       <c r="N25" t="s">
-        <v>95</v>
+        <v>107</v>
       </c>
       <c r="O25" t="s">
         <v>171</v>
@@ -2056,10 +2056,10 @@
         <v>86</v>
       </c>
       <c r="M26" t="s">
-        <v>140</v>
+        <v>110</v>
       </c>
       <c r="N26" t="s">
-        <v>141</v>
+        <v>111</v>
       </c>
       <c r="O26" t="s">
         <v>171</v>
@@ -2118,10 +2118,10 @@
         <v>86</v>
       </c>
       <c r="M27" t="s">
-        <v>122</v>
+        <v>142</v>
       </c>
       <c r="N27" t="s">
-        <v>123</v>
+        <v>143</v>
       </c>
       <c r="O27" t="s">
         <v>171</v>
@@ -2180,10 +2180,10 @@
         <v>86</v>
       </c>
       <c r="M28" t="s">
-        <v>114</v>
+        <v>165</v>
       </c>
       <c r="N28" t="s">
-        <v>115</v>
+        <v>166</v>
       </c>
       <c r="O28" t="s">
         <v>171</v>
@@ -2242,10 +2242,10 @@
         <v>86</v>
       </c>
       <c r="M29" t="s">
-        <v>130</v>
+        <v>158</v>
       </c>
       <c r="N29" t="s">
-        <v>131</v>
+        <v>159</v>
       </c>
       <c r="O29" t="s">
         <v>171</v>
@@ -2304,10 +2304,10 @@
         <v>86</v>
       </c>
       <c r="M30" t="s">
-        <v>102</v>
+        <v>144</v>
       </c>
       <c r="N30" t="s">
-        <v>103</v>
+        <v>145</v>
       </c>
       <c r="O30" t="s">
         <v>171</v>
@@ -2366,10 +2366,10 @@
         <v>86</v>
       </c>
       <c r="M31" t="s">
-        <v>148</v>
+        <v>126</v>
       </c>
       <c r="N31" t="s">
-        <v>149</v>
+        <v>127</v>
       </c>
       <c r="O31" t="s">
         <v>171</v>
@@ -2428,10 +2428,10 @@
         <v>86</v>
       </c>
       <c r="M32" t="s">
-        <v>180</v>
+        <v>132</v>
       </c>
       <c r="N32" t="s">
-        <v>181</v>
+        <v>133</v>
       </c>
       <c r="O32" t="s">
         <v>171</v>
@@ -2490,10 +2490,10 @@
         <v>86</v>
       </c>
       <c r="M33" t="s">
-        <v>124</v>
+        <v>98</v>
       </c>
       <c r="N33" t="s">
-        <v>125</v>
+        <v>99</v>
       </c>
       <c r="O33" t="s">
         <v>171</v>
@@ -2552,10 +2552,10 @@
         <v>86</v>
       </c>
       <c r="M34" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="N34" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="O34" t="s">
         <v>171</v>
@@ -2614,10 +2614,10 @@
         <v>86</v>
       </c>
       <c r="M35" t="s">
-        <v>128</v>
+        <v>154</v>
       </c>
       <c r="N35" t="s">
-        <v>129</v>
+        <v>155</v>
       </c>
       <c r="O35" t="s">
         <v>171</v>
@@ -2676,10 +2676,10 @@
         <v>86</v>
       </c>
       <c r="M36" t="s">
-        <v>182</v>
+        <v>169</v>
       </c>
       <c r="N36" t="s">
-        <v>183</v>
+        <v>170</v>
       </c>
       <c r="O36" t="s">
         <v>171</v>
@@ -2738,10 +2738,10 @@
         <v>86</v>
       </c>
       <c r="M37" t="s">
-        <v>169</v>
+        <v>90</v>
       </c>
       <c r="N37" t="s">
-        <v>170</v>
+        <v>91</v>
       </c>
       <c r="O37" t="s">
         <v>171</v>
@@ -2800,10 +2800,10 @@
         <v>86</v>
       </c>
       <c r="M38" t="s">
-        <v>138</v>
+        <v>92</v>
       </c>
       <c r="N38" t="s">
-        <v>139</v>
+        <v>93</v>
       </c>
       <c r="O38" t="s">
         <v>171</v>
@@ -2862,10 +2862,10 @@
         <v>86</v>
       </c>
       <c r="M39" t="s">
-        <v>154</v>
+        <v>112</v>
       </c>
       <c r="N39" t="s">
-        <v>155</v>
+        <v>113</v>
       </c>
       <c r="O39" t="s">
         <v>171</v>
@@ -2924,10 +2924,10 @@
         <v>86</v>
       </c>
       <c r="M40" t="s">
-        <v>96</v>
+        <v>180</v>
       </c>
       <c r="N40" t="s">
-        <v>97</v>
+        <v>181</v>
       </c>
       <c r="O40" t="s">
         <v>171</v>
@@ -2986,10 +2986,10 @@
         <v>86</v>
       </c>
       <c r="M41" t="s">
-        <v>98</v>
+        <v>146</v>
       </c>
       <c r="N41" t="s">
-        <v>99</v>
+        <v>147</v>
       </c>
       <c r="O41" t="s">
         <v>171</v>
@@ -3048,10 +3048,10 @@
         <v>86</v>
       </c>
       <c r="M42" t="s">
-        <v>167</v>
+        <v>182</v>
       </c>
       <c r="N42" t="s">
-        <v>168</v>
+        <v>183</v>
       </c>
       <c r="O42" t="s">
         <v>171</v>
@@ -3086,10 +3086,10 @@
         <v>86</v>
       </c>
       <c r="M43" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="N43" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="O43" t="s">
         <v>171</v>
@@ -3124,10 +3124,10 @@
         <v>86</v>
       </c>
       <c r="M44" t="s">
-        <v>110</v>
+        <v>94</v>
       </c>
       <c r="N44" t="s">
-        <v>111</v>
+        <v>95</v>
       </c>
       <c r="O44" t="s">
         <v>171</v>
@@ -3162,10 +3162,10 @@
         <v>86</v>
       </c>
       <c r="M45" t="s">
-        <v>184</v>
+        <v>116</v>
       </c>
       <c r="N45" t="s">
-        <v>185</v>
+        <v>117</v>
       </c>
       <c r="O45" t="s">
         <v>171</v>
@@ -3200,10 +3200,10 @@
         <v>86</v>
       </c>
       <c r="M46" t="s">
-        <v>90</v>
+        <v>184</v>
       </c>
       <c r="N46" t="s">
-        <v>91</v>
+        <v>185</v>
       </c>
       <c r="O46" t="s">
         <v>171</v>
@@ -3226,10 +3226,10 @@
         <v>86</v>
       </c>
       <c r="M47" t="s">
-        <v>146</v>
+        <v>163</v>
       </c>
       <c r="N47" t="s">
-        <v>147</v>
+        <v>164</v>
       </c>
       <c r="O47" t="s">
         <v>171</v>
@@ -3252,10 +3252,10 @@
         <v>86</v>
       </c>
       <c r="M48" t="s">
-        <v>104</v>
+        <v>186</v>
       </c>
       <c r="N48" t="s">
-        <v>105</v>
+        <v>187</v>
       </c>
       <c r="O48" t="s">
         <v>171</v>
@@ -3278,10 +3278,10 @@
         <v>86</v>
       </c>
       <c r="M49" t="s">
-        <v>142</v>
+        <v>96</v>
       </c>
       <c r="N49" t="s">
-        <v>143</v>
+        <v>97</v>
       </c>
       <c r="O49" t="s">
         <v>171</v>
@@ -3304,10 +3304,10 @@
         <v>86</v>
       </c>
       <c r="M50" t="s">
-        <v>186</v>
+        <v>150</v>
       </c>
       <c r="N50" t="s">
-        <v>187</v>
+        <v>151</v>
       </c>
       <c r="O50" t="s">
         <v>171</v>
@@ -3330,10 +3330,10 @@
         <v>86</v>
       </c>
       <c r="M51" t="s">
-        <v>134</v>
+        <v>188</v>
       </c>
       <c r="N51" t="s">
-        <v>135</v>
+        <v>189</v>
       </c>
       <c r="O51" t="s">
         <v>171</v>
@@ -3344,10 +3344,10 @@
         <v>86</v>
       </c>
       <c r="M52" t="s">
-        <v>156</v>
+        <v>118</v>
       </c>
       <c r="N52" t="s">
-        <v>157</v>
+        <v>119</v>
       </c>
       <c r="O52" t="s">
         <v>171</v>
@@ -3358,10 +3358,10 @@
         <v>86</v>
       </c>
       <c r="M53" t="s">
-        <v>144</v>
+        <v>114</v>
       </c>
       <c r="N53" t="s">
-        <v>145</v>
+        <v>115</v>
       </c>
       <c r="O53" t="s">
         <v>171</v>
@@ -3372,10 +3372,10 @@
         <v>86</v>
       </c>
       <c r="M54" t="s">
-        <v>87</v>
+        <v>140</v>
       </c>
       <c r="N54" t="s">
-        <v>88</v>
+        <v>141</v>
       </c>
       <c r="O54" t="s">
         <v>171</v>
@@ -3386,10 +3386,10 @@
         <v>86</v>
       </c>
       <c r="M55" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="N55" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="O55" t="s">
         <v>171</v>
@@ -3400,10 +3400,10 @@
         <v>86</v>
       </c>
       <c r="M56" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="N56" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="O56" t="s">
         <v>171</v>
@@ -3414,10 +3414,10 @@
         <v>86</v>
       </c>
       <c r="M57" t="s">
-        <v>190</v>
+        <v>120</v>
       </c>
       <c r="N57" t="s">
-        <v>191</v>
+        <v>121</v>
       </c>
       <c r="O57" t="s">
         <v>171</v>
@@ -3428,10 +3428,10 @@
         <v>86</v>
       </c>
       <c r="M58" t="s">
-        <v>108</v>
+        <v>128</v>
       </c>
       <c r="N58" t="s">
-        <v>109</v>
+        <v>129</v>
       </c>
       <c r="O58" t="s">
         <v>171</v>
@@ -3442,10 +3442,10 @@
         <v>86</v>
       </c>
       <c r="M59" t="s">
-        <v>106</v>
+        <v>87</v>
       </c>
       <c r="N59" t="s">
-        <v>107</v>
+        <v>88</v>
       </c>
       <c r="O59" t="s">
         <v>171</v>
@@ -3456,10 +3456,10 @@
         <v>86</v>
       </c>
       <c r="M60" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="N60" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="O60" t="s">
         <v>171</v>
@@ -3470,10 +3470,10 @@
         <v>86</v>
       </c>
       <c r="M61" t="s">
-        <v>192</v>
+        <v>108</v>
       </c>
       <c r="N61" t="s">
-        <v>193</v>
+        <v>109</v>
       </c>
       <c r="O61" t="s">
         <v>171</v>
@@ -3484,10 +3484,10 @@
         <v>86</v>
       </c>
       <c r="M62" t="s">
-        <v>116</v>
+        <v>192</v>
       </c>
       <c r="N62" t="s">
-        <v>117</v>
+        <v>193</v>
       </c>
       <c r="O62" t="s">
         <v>171</v>

--- a/VerveStacks_POL_grids_kan50/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_POL_grids_kan50/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCCFC7B7-9496-41ED-9290-9591ED5D9353}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{920B5643-8CDD-40CA-A1AC-DD31EF54B3A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -556,12 +556,48 @@
     <t>e_demand,ev_battery,H2prd_Elc_PEM,H2prd_Elc_ALK</t>
   </si>
   <si>
+    <t>Siedlce_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Siedlce_POL</t>
+  </si>
+  <si>
+    <t>Walbrzych_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Walbrzych_POL</t>
+  </si>
+  <si>
     <t>Pila_POL</t>
   </si>
   <si>
     <t>at grid node - Pila_POL</t>
   </si>
   <si>
+    <t>Legnica_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Legnica_POL</t>
+  </si>
+  <si>
+    <t>Grajewo_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Grajewo_POL</t>
+  </si>
+  <si>
+    <t>Olsztyn_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Olsztyn_POL</t>
+  </si>
+  <si>
+    <t>OstrowiecSwietokrz_POL</t>
+  </si>
+  <si>
+    <t>at grid node - OstrowiecSwietokrz_POL</t>
+  </si>
+  <si>
     <t>Zamosc_POL</t>
   </si>
   <si>
@@ -574,52 +610,16 @@
     <t>at grid node - Elk_POL</t>
   </si>
   <si>
-    <t>Siedlce_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Siedlce_POL</t>
-  </si>
-  <si>
-    <t>Legnica_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Legnica_POL</t>
+    <t>Chelm_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Chelm_POL</t>
   </si>
   <si>
     <t>Kielce_POL</t>
   </si>
   <si>
     <t>at grid node - Kielce_POL</t>
-  </si>
-  <si>
-    <t>Olsztyn_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Olsztyn_POL</t>
-  </si>
-  <si>
-    <t>OstrowiecSwietokrz_POL</t>
-  </si>
-  <si>
-    <t>at grid node - OstrowiecSwietokrz_POL</t>
-  </si>
-  <si>
-    <t>Walbrzych_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Walbrzych_POL</t>
-  </si>
-  <si>
-    <t>Chelm_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Chelm_POL</t>
-  </si>
-  <si>
-    <t>Grajewo_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Grajewo_POL</t>
   </si>
   <si>
     <t>h_demand</t>
@@ -1126,10 +1126,10 @@
         <v>86</v>
       </c>
       <c r="M11" t="s">
-        <v>102</v>
+        <v>163</v>
       </c>
       <c r="N11" t="s">
-        <v>103</v>
+        <v>164</v>
       </c>
       <c r="O11" t="s">
         <v>171</v>
@@ -1188,10 +1188,10 @@
         <v>86</v>
       </c>
       <c r="M12" t="s">
-        <v>122</v>
+        <v>92</v>
       </c>
       <c r="N12" t="s">
-        <v>123</v>
+        <v>93</v>
       </c>
       <c r="O12" t="s">
         <v>171</v>
@@ -1250,10 +1250,10 @@
         <v>86</v>
       </c>
       <c r="M13" t="s">
-        <v>130</v>
+        <v>142</v>
       </c>
       <c r="N13" t="s">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="O13" t="s">
         <v>171</v>
@@ -1312,10 +1312,10 @@
         <v>86</v>
       </c>
       <c r="M14" t="s">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="N14" t="s">
-        <v>101</v>
+        <v>88</v>
       </c>
       <c r="O14" t="s">
         <v>171</v>
@@ -1374,10 +1374,10 @@
         <v>86</v>
       </c>
       <c r="M15" t="s">
-        <v>172</v>
+        <v>114</v>
       </c>
       <c r="N15" t="s">
-        <v>173</v>
+        <v>115</v>
       </c>
       <c r="O15" t="s">
         <v>171</v>
@@ -1436,10 +1436,10 @@
         <v>86</v>
       </c>
       <c r="M16" t="s">
-        <v>104</v>
+        <v>154</v>
       </c>
       <c r="N16" t="s">
-        <v>105</v>
+        <v>155</v>
       </c>
       <c r="O16" t="s">
         <v>171</v>
@@ -1498,10 +1498,10 @@
         <v>86</v>
       </c>
       <c r="M17" t="s">
-        <v>136</v>
+        <v>172</v>
       </c>
       <c r="N17" t="s">
-        <v>137</v>
+        <v>173</v>
       </c>
       <c r="O17" t="s">
         <v>171</v>
@@ -1560,10 +1560,10 @@
         <v>86</v>
       </c>
       <c r="M18" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="N18" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="O18" t="s">
         <v>171</v>
@@ -1622,10 +1622,10 @@
         <v>86</v>
       </c>
       <c r="M19" t="s">
-        <v>174</v>
+        <v>106</v>
       </c>
       <c r="N19" t="s">
-        <v>175</v>
+        <v>107</v>
       </c>
       <c r="O19" t="s">
         <v>171</v>
@@ -1684,10 +1684,10 @@
         <v>86</v>
       </c>
       <c r="M20" t="s">
-        <v>176</v>
+        <v>100</v>
       </c>
       <c r="N20" t="s">
-        <v>177</v>
+        <v>101</v>
       </c>
       <c r="O20" t="s">
         <v>171</v>
@@ -1746,10 +1746,10 @@
         <v>86</v>
       </c>
       <c r="M21" t="s">
-        <v>134</v>
+        <v>174</v>
       </c>
       <c r="N21" t="s">
-        <v>135</v>
+        <v>175</v>
       </c>
       <c r="O21" t="s">
         <v>171</v>
@@ -1808,10 +1808,10 @@
         <v>86</v>
       </c>
       <c r="M22" t="s">
-        <v>178</v>
+        <v>98</v>
       </c>
       <c r="N22" t="s">
-        <v>179</v>
+        <v>99</v>
       </c>
       <c r="O22" t="s">
         <v>171</v>
@@ -1870,10 +1870,10 @@
         <v>86</v>
       </c>
       <c r="M23" t="s">
-        <v>152</v>
+        <v>118</v>
       </c>
       <c r="N23" t="s">
-        <v>153</v>
+        <v>119</v>
       </c>
       <c r="O23" t="s">
         <v>171</v>
@@ -1932,10 +1932,10 @@
         <v>86</v>
       </c>
       <c r="M24" t="s">
-        <v>148</v>
+        <v>130</v>
       </c>
       <c r="N24" t="s">
-        <v>149</v>
+        <v>131</v>
       </c>
       <c r="O24" t="s">
         <v>171</v>
@@ -1994,10 +1994,10 @@
         <v>86</v>
       </c>
       <c r="M25" t="s">
-        <v>106</v>
+        <v>150</v>
       </c>
       <c r="N25" t="s">
-        <v>107</v>
+        <v>151</v>
       </c>
       <c r="O25" t="s">
         <v>171</v>
@@ -2056,10 +2056,10 @@
         <v>86</v>
       </c>
       <c r="M26" t="s">
-        <v>110</v>
+        <v>122</v>
       </c>
       <c r="N26" t="s">
-        <v>111</v>
+        <v>123</v>
       </c>
       <c r="O26" t="s">
         <v>171</v>
@@ -2118,10 +2118,10 @@
         <v>86</v>
       </c>
       <c r="M27" t="s">
-        <v>142</v>
+        <v>152</v>
       </c>
       <c r="N27" t="s">
-        <v>143</v>
+        <v>153</v>
       </c>
       <c r="O27" t="s">
         <v>171</v>
@@ -2180,10 +2180,10 @@
         <v>86</v>
       </c>
       <c r="M28" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="N28" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="O28" t="s">
         <v>171</v>
@@ -2242,10 +2242,10 @@
         <v>86</v>
       </c>
       <c r="M29" t="s">
-        <v>158</v>
+        <v>148</v>
       </c>
       <c r="N29" t="s">
-        <v>159</v>
+        <v>149</v>
       </c>
       <c r="O29" t="s">
         <v>171</v>
@@ -2304,10 +2304,10 @@
         <v>86</v>
       </c>
       <c r="M30" t="s">
-        <v>144</v>
+        <v>176</v>
       </c>
       <c r="N30" t="s">
-        <v>145</v>
+        <v>177</v>
       </c>
       <c r="O30" t="s">
         <v>171</v>
@@ -2366,10 +2366,10 @@
         <v>86</v>
       </c>
       <c r="M31" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="N31" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="O31" t="s">
         <v>171</v>
@@ -2428,10 +2428,10 @@
         <v>86</v>
       </c>
       <c r="M32" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="N32" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="O32" t="s">
         <v>171</v>
@@ -2490,10 +2490,10 @@
         <v>86</v>
       </c>
       <c r="M33" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="N33" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="O33" t="s">
         <v>171</v>
@@ -2552,10 +2552,10 @@
         <v>86</v>
       </c>
       <c r="M34" t="s">
-        <v>156</v>
+        <v>116</v>
       </c>
       <c r="N34" t="s">
-        <v>157</v>
+        <v>117</v>
       </c>
       <c r="O34" t="s">
         <v>171</v>
@@ -2614,10 +2614,10 @@
         <v>86</v>
       </c>
       <c r="M35" t="s">
-        <v>154</v>
+        <v>178</v>
       </c>
       <c r="N35" t="s">
-        <v>155</v>
+        <v>179</v>
       </c>
       <c r="O35" t="s">
         <v>171</v>
@@ -2676,10 +2676,10 @@
         <v>86</v>
       </c>
       <c r="M36" t="s">
-        <v>169</v>
+        <v>158</v>
       </c>
       <c r="N36" t="s">
-        <v>170</v>
+        <v>159</v>
       </c>
       <c r="O36" t="s">
         <v>171</v>
@@ -2738,10 +2738,10 @@
         <v>86</v>
       </c>
       <c r="M37" t="s">
-        <v>90</v>
+        <v>167</v>
       </c>
       <c r="N37" t="s">
-        <v>91</v>
+        <v>168</v>
       </c>
       <c r="O37" t="s">
         <v>171</v>
@@ -2800,10 +2800,10 @@
         <v>86</v>
       </c>
       <c r="M38" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="N38" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="O38" t="s">
         <v>171</v>
@@ -2862,10 +2862,10 @@
         <v>86</v>
       </c>
       <c r="M39" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="N39" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="O39" t="s">
         <v>171</v>
@@ -2924,10 +2924,10 @@
         <v>86</v>
       </c>
       <c r="M40" t="s">
-        <v>180</v>
+        <v>110</v>
       </c>
       <c r="N40" t="s">
-        <v>181</v>
+        <v>111</v>
       </c>
       <c r="O40" t="s">
         <v>171</v>
@@ -2986,10 +2986,10 @@
         <v>86</v>
       </c>
       <c r="M41" t="s">
-        <v>146</v>
+        <v>169</v>
       </c>
       <c r="N41" t="s">
-        <v>147</v>
+        <v>170</v>
       </c>
       <c r="O41" t="s">
         <v>171</v>
@@ -3048,10 +3048,10 @@
         <v>86</v>
       </c>
       <c r="M42" t="s">
-        <v>182</v>
+        <v>120</v>
       </c>
       <c r="N42" t="s">
-        <v>183</v>
+        <v>121</v>
       </c>
       <c r="O42" t="s">
         <v>171</v>
@@ -3086,10 +3086,10 @@
         <v>86</v>
       </c>
       <c r="M43" t="s">
-        <v>138</v>
+        <v>180</v>
       </c>
       <c r="N43" t="s">
-        <v>139</v>
+        <v>181</v>
       </c>
       <c r="O43" t="s">
         <v>171</v>
@@ -3124,10 +3124,10 @@
         <v>86</v>
       </c>
       <c r="M44" t="s">
-        <v>94</v>
+        <v>128</v>
       </c>
       <c r="N44" t="s">
-        <v>95</v>
+        <v>129</v>
       </c>
       <c r="O44" t="s">
         <v>171</v>
@@ -3162,10 +3162,10 @@
         <v>86</v>
       </c>
       <c r="M45" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="N45" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="O45" t="s">
         <v>171</v>
@@ -3200,10 +3200,10 @@
         <v>86</v>
       </c>
       <c r="M46" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="N46" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="O46" t="s">
         <v>171</v>
@@ -3226,10 +3226,10 @@
         <v>86</v>
       </c>
       <c r="M47" t="s">
-        <v>163</v>
+        <v>96</v>
       </c>
       <c r="N47" t="s">
-        <v>164</v>
+        <v>97</v>
       </c>
       <c r="O47" t="s">
         <v>171</v>
@@ -3252,10 +3252,10 @@
         <v>86</v>
       </c>
       <c r="M48" t="s">
-        <v>186</v>
+        <v>146</v>
       </c>
       <c r="N48" t="s">
-        <v>187</v>
+        <v>147</v>
       </c>
       <c r="O48" t="s">
         <v>171</v>
@@ -3278,10 +3278,10 @@
         <v>86</v>
       </c>
       <c r="M49" t="s">
-        <v>96</v>
+        <v>184</v>
       </c>
       <c r="N49" t="s">
-        <v>97</v>
+        <v>185</v>
       </c>
       <c r="O49" t="s">
         <v>171</v>
@@ -3304,10 +3304,10 @@
         <v>86</v>
       </c>
       <c r="M50" t="s">
-        <v>150</v>
+        <v>186</v>
       </c>
       <c r="N50" t="s">
-        <v>151</v>
+        <v>187</v>
       </c>
       <c r="O50" t="s">
         <v>171</v>
@@ -3330,10 +3330,10 @@
         <v>86</v>
       </c>
       <c r="M51" t="s">
-        <v>188</v>
+        <v>156</v>
       </c>
       <c r="N51" t="s">
-        <v>189</v>
+        <v>157</v>
       </c>
       <c r="O51" t="s">
         <v>171</v>
@@ -3344,10 +3344,10 @@
         <v>86</v>
       </c>
       <c r="M52" t="s">
-        <v>118</v>
+        <v>94</v>
       </c>
       <c r="N52" t="s">
-        <v>119</v>
+        <v>95</v>
       </c>
       <c r="O52" t="s">
         <v>171</v>
@@ -3358,10 +3358,10 @@
         <v>86</v>
       </c>
       <c r="M53" t="s">
-        <v>114</v>
+        <v>134</v>
       </c>
       <c r="N53" t="s">
-        <v>115</v>
+        <v>135</v>
       </c>
       <c r="O53" t="s">
         <v>171</v>
@@ -3372,10 +3372,10 @@
         <v>86</v>
       </c>
       <c r="M54" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="N54" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="O54" t="s">
         <v>171</v>
@@ -3386,10 +3386,10 @@
         <v>86</v>
       </c>
       <c r="M55" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="N55" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="O55" t="s">
         <v>171</v>
@@ -3400,10 +3400,10 @@
         <v>86</v>
       </c>
       <c r="M56" t="s">
-        <v>124</v>
+        <v>138</v>
       </c>
       <c r="N56" t="s">
-        <v>125</v>
+        <v>139</v>
       </c>
       <c r="O56" t="s">
         <v>171</v>
@@ -3414,10 +3414,10 @@
         <v>86</v>
       </c>
       <c r="M57" t="s">
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="N57" t="s">
-        <v>121</v>
+        <v>141</v>
       </c>
       <c r="O57" t="s">
         <v>171</v>
@@ -3428,10 +3428,10 @@
         <v>86</v>
       </c>
       <c r="M58" t="s">
-        <v>128</v>
+        <v>190</v>
       </c>
       <c r="N58" t="s">
-        <v>129</v>
+        <v>191</v>
       </c>
       <c r="O58" t="s">
         <v>171</v>
@@ -3442,10 +3442,10 @@
         <v>86</v>
       </c>
       <c r="M59" t="s">
-        <v>87</v>
+        <v>192</v>
       </c>
       <c r="N59" t="s">
-        <v>88</v>
+        <v>193</v>
       </c>
       <c r="O59" t="s">
         <v>171</v>
@@ -3456,10 +3456,10 @@
         <v>86</v>
       </c>
       <c r="M60" t="s">
-        <v>167</v>
+        <v>136</v>
       </c>
       <c r="N60" t="s">
-        <v>168</v>
+        <v>137</v>
       </c>
       <c r="O60" t="s">
         <v>171</v>
@@ -3470,10 +3470,10 @@
         <v>86</v>
       </c>
       <c r="M61" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="N61" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="O61" t="s">
         <v>171</v>
@@ -3484,10 +3484,10 @@
         <v>86</v>
       </c>
       <c r="M62" t="s">
-        <v>192</v>
+        <v>144</v>
       </c>
       <c r="N62" t="s">
-        <v>193</v>
+        <v>145</v>
       </c>
       <c r="O62" t="s">
         <v>171</v>

--- a/VerveStacks_POL_grids_kan50/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_POL_grids_kan50/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{920B5643-8CDD-40CA-A1AC-DD31EF54B3A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DFE0F8A-EC41-4DE1-B85D-C1ADD2E779F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -556,6 +556,36 @@
     <t>e_demand,ev_battery,H2prd_Elc_PEM,H2prd_Elc_ALK</t>
   </si>
   <si>
+    <t>Kielce_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Kielce_POL</t>
+  </si>
+  <si>
+    <t>Olsztyn_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Olsztyn_POL</t>
+  </si>
+  <si>
+    <t>Grajewo_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Grajewo_POL</t>
+  </si>
+  <si>
+    <t>Pila_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Pila_POL</t>
+  </si>
+  <si>
+    <t>Zamosc_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Zamosc_POL</t>
+  </si>
+  <si>
     <t>Siedlce_POL</t>
   </si>
   <si>
@@ -568,10 +598,10 @@
     <t>at grid node - Walbrzych_POL</t>
   </si>
   <si>
-    <t>Pila_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Pila_POL</t>
+    <t>OstrowiecSwietokrz_POL</t>
+  </si>
+  <si>
+    <t>at grid node - OstrowiecSwietokrz_POL</t>
   </si>
   <si>
     <t>Legnica_POL</t>
@@ -580,46 +610,16 @@
     <t>at grid node - Legnica_POL</t>
   </si>
   <si>
-    <t>Grajewo_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Grajewo_POL</t>
-  </si>
-  <si>
-    <t>Olsztyn_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Olsztyn_POL</t>
-  </si>
-  <si>
-    <t>OstrowiecSwietokrz_POL</t>
-  </si>
-  <si>
-    <t>at grid node - OstrowiecSwietokrz_POL</t>
-  </si>
-  <si>
-    <t>Zamosc_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Zamosc_POL</t>
+    <t>Chelm_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Chelm_POL</t>
   </si>
   <si>
     <t>Elk_POL</t>
   </si>
   <si>
     <t>at grid node - Elk_POL</t>
-  </si>
-  <si>
-    <t>Chelm_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Chelm_POL</t>
-  </si>
-  <si>
-    <t>Kielce_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Kielce_POL</t>
   </si>
   <si>
     <t>h_demand</t>
@@ -1126,10 +1126,10 @@
         <v>86</v>
       </c>
       <c r="M11" t="s">
-        <v>163</v>
+        <v>138</v>
       </c>
       <c r="N11" t="s">
-        <v>164</v>
+        <v>139</v>
       </c>
       <c r="O11" t="s">
         <v>171</v>
@@ -1188,10 +1188,10 @@
         <v>86</v>
       </c>
       <c r="M12" t="s">
-        <v>92</v>
+        <v>172</v>
       </c>
       <c r="N12" t="s">
-        <v>93</v>
+        <v>173</v>
       </c>
       <c r="O12" t="s">
         <v>171</v>
@@ -1250,10 +1250,10 @@
         <v>86</v>
       </c>
       <c r="M13" t="s">
-        <v>142</v>
+        <v>174</v>
       </c>
       <c r="N13" t="s">
-        <v>143</v>
+        <v>175</v>
       </c>
       <c r="O13" t="s">
         <v>171</v>
@@ -1312,10 +1312,10 @@
         <v>86</v>
       </c>
       <c r="M14" t="s">
-        <v>87</v>
+        <v>148</v>
       </c>
       <c r="N14" t="s">
-        <v>88</v>
+        <v>149</v>
       </c>
       <c r="O14" t="s">
         <v>171</v>
@@ -1374,10 +1374,10 @@
         <v>86</v>
       </c>
       <c r="M15" t="s">
-        <v>114</v>
+        <v>165</v>
       </c>
       <c r="N15" t="s">
-        <v>115</v>
+        <v>166</v>
       </c>
       <c r="O15" t="s">
         <v>171</v>
@@ -1436,10 +1436,10 @@
         <v>86</v>
       </c>
       <c r="M16" t="s">
-        <v>154</v>
+        <v>126</v>
       </c>
       <c r="N16" t="s">
-        <v>155</v>
+        <v>127</v>
       </c>
       <c r="O16" t="s">
         <v>171</v>
@@ -1498,10 +1498,10 @@
         <v>86</v>
       </c>
       <c r="M17" t="s">
-        <v>172</v>
+        <v>150</v>
       </c>
       <c r="N17" t="s">
-        <v>173</v>
+        <v>151</v>
       </c>
       <c r="O17" t="s">
         <v>171</v>
@@ -1560,10 +1560,10 @@
         <v>86</v>
       </c>
       <c r="M18" t="s">
-        <v>165</v>
+        <v>122</v>
       </c>
       <c r="N18" t="s">
-        <v>166</v>
+        <v>123</v>
       </c>
       <c r="O18" t="s">
         <v>171</v>
@@ -1622,10 +1622,10 @@
         <v>86</v>
       </c>
       <c r="M19" t="s">
-        <v>106</v>
+        <v>176</v>
       </c>
       <c r="N19" t="s">
-        <v>107</v>
+        <v>177</v>
       </c>
       <c r="O19" t="s">
         <v>171</v>
@@ -1684,10 +1684,10 @@
         <v>86</v>
       </c>
       <c r="M20" t="s">
-        <v>100</v>
+        <v>144</v>
       </c>
       <c r="N20" t="s">
-        <v>101</v>
+        <v>145</v>
       </c>
       <c r="O20" t="s">
         <v>171</v>
@@ -1746,10 +1746,10 @@
         <v>86</v>
       </c>
       <c r="M21" t="s">
-        <v>174</v>
+        <v>130</v>
       </c>
       <c r="N21" t="s">
-        <v>175</v>
+        <v>131</v>
       </c>
       <c r="O21" t="s">
         <v>171</v>
@@ -1808,10 +1808,10 @@
         <v>86</v>
       </c>
       <c r="M22" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="N22" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="O22" t="s">
         <v>171</v>
@@ -1870,10 +1870,10 @@
         <v>86</v>
       </c>
       <c r="M23" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="N23" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="O23" t="s">
         <v>171</v>
@@ -1932,10 +1932,10 @@
         <v>86</v>
       </c>
       <c r="M24" t="s">
-        <v>130</v>
+        <v>90</v>
       </c>
       <c r="N24" t="s">
-        <v>131</v>
+        <v>91</v>
       </c>
       <c r="O24" t="s">
         <v>171</v>
@@ -1994,10 +1994,10 @@
         <v>86</v>
       </c>
       <c r="M25" t="s">
-        <v>150</v>
+        <v>178</v>
       </c>
       <c r="N25" t="s">
-        <v>151</v>
+        <v>179</v>
       </c>
       <c r="O25" t="s">
         <v>171</v>
@@ -2056,10 +2056,10 @@
         <v>86</v>
       </c>
       <c r="M26" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="N26" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="O26" t="s">
         <v>171</v>
@@ -2118,10 +2118,10 @@
         <v>86</v>
       </c>
       <c r="M27" t="s">
-        <v>152</v>
+        <v>180</v>
       </c>
       <c r="N27" t="s">
-        <v>153</v>
+        <v>181</v>
       </c>
       <c r="O27" t="s">
         <v>171</v>
@@ -2180,10 +2180,10 @@
         <v>86</v>
       </c>
       <c r="M28" t="s">
-        <v>161</v>
+        <v>182</v>
       </c>
       <c r="N28" t="s">
-        <v>162</v>
+        <v>183</v>
       </c>
       <c r="O28" t="s">
         <v>171</v>
@@ -2242,10 +2242,10 @@
         <v>86</v>
       </c>
       <c r="M29" t="s">
-        <v>148</v>
+        <v>184</v>
       </c>
       <c r="N29" t="s">
-        <v>149</v>
+        <v>185</v>
       </c>
       <c r="O29" t="s">
         <v>171</v>
@@ -2304,10 +2304,10 @@
         <v>86</v>
       </c>
       <c r="M30" t="s">
-        <v>176</v>
+        <v>96</v>
       </c>
       <c r="N30" t="s">
-        <v>177</v>
+        <v>97</v>
       </c>
       <c r="O30" t="s">
         <v>171</v>
@@ -2366,10 +2366,10 @@
         <v>86</v>
       </c>
       <c r="M31" t="s">
-        <v>124</v>
+        <v>87</v>
       </c>
       <c r="N31" t="s">
-        <v>125</v>
+        <v>88</v>
       </c>
       <c r="O31" t="s">
         <v>171</v>
@@ -2428,10 +2428,10 @@
         <v>86</v>
       </c>
       <c r="M32" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="N32" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="O32" t="s">
         <v>171</v>
@@ -2490,10 +2490,10 @@
         <v>86</v>
       </c>
       <c r="M33" t="s">
-        <v>104</v>
+        <v>186</v>
       </c>
       <c r="N33" t="s">
-        <v>105</v>
+        <v>187</v>
       </c>
       <c r="O33" t="s">
         <v>171</v>
@@ -2552,10 +2552,10 @@
         <v>86</v>
       </c>
       <c r="M34" t="s">
-        <v>116</v>
+        <v>136</v>
       </c>
       <c r="N34" t="s">
-        <v>117</v>
+        <v>137</v>
       </c>
       <c r="O34" t="s">
         <v>171</v>
@@ -2614,10 +2614,10 @@
         <v>86</v>
       </c>
       <c r="M35" t="s">
-        <v>178</v>
+        <v>108</v>
       </c>
       <c r="N35" t="s">
-        <v>179</v>
+        <v>109</v>
       </c>
       <c r="O35" t="s">
         <v>171</v>
@@ -2676,10 +2676,10 @@
         <v>86</v>
       </c>
       <c r="M36" t="s">
-        <v>158</v>
+        <v>188</v>
       </c>
       <c r="N36" t="s">
-        <v>159</v>
+        <v>189</v>
       </c>
       <c r="O36" t="s">
         <v>171</v>
@@ -2738,10 +2738,10 @@
         <v>86</v>
       </c>
       <c r="M37" t="s">
-        <v>167</v>
+        <v>190</v>
       </c>
       <c r="N37" t="s">
-        <v>168</v>
+        <v>191</v>
       </c>
       <c r="O37" t="s">
         <v>171</v>
@@ -2800,10 +2800,10 @@
         <v>86</v>
       </c>
       <c r="M38" t="s">
-        <v>90</v>
+        <v>161</v>
       </c>
       <c r="N38" t="s">
-        <v>91</v>
+        <v>162</v>
       </c>
       <c r="O38" t="s">
         <v>171</v>
@@ -2862,10 +2862,10 @@
         <v>86</v>
       </c>
       <c r="M39" t="s">
-        <v>108</v>
+        <v>98</v>
       </c>
       <c r="N39" t="s">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="O39" t="s">
         <v>171</v>
@@ -2924,10 +2924,10 @@
         <v>86</v>
       </c>
       <c r="M40" t="s">
-        <v>110</v>
+        <v>142</v>
       </c>
       <c r="N40" t="s">
-        <v>111</v>
+        <v>143</v>
       </c>
       <c r="O40" t="s">
         <v>171</v>
@@ -2986,10 +2986,10 @@
         <v>86</v>
       </c>
       <c r="M41" t="s">
-        <v>169</v>
+        <v>112</v>
       </c>
       <c r="N41" t="s">
-        <v>170</v>
+        <v>113</v>
       </c>
       <c r="O41" t="s">
         <v>171</v>
@@ -3048,10 +3048,10 @@
         <v>86</v>
       </c>
       <c r="M42" t="s">
-        <v>120</v>
+        <v>104</v>
       </c>
       <c r="N42" t="s">
-        <v>121</v>
+        <v>105</v>
       </c>
       <c r="O42" t="s">
         <v>171</v>
@@ -3086,10 +3086,10 @@
         <v>86</v>
       </c>
       <c r="M43" t="s">
-        <v>180</v>
+        <v>154</v>
       </c>
       <c r="N43" t="s">
-        <v>181</v>
+        <v>155</v>
       </c>
       <c r="O43" t="s">
         <v>171</v>
@@ -3124,10 +3124,10 @@
         <v>86</v>
       </c>
       <c r="M44" t="s">
-        <v>128</v>
+        <v>152</v>
       </c>
       <c r="N44" t="s">
-        <v>129</v>
+        <v>153</v>
       </c>
       <c r="O44" t="s">
         <v>171</v>
@@ -3162,10 +3162,10 @@
         <v>86</v>
       </c>
       <c r="M45" t="s">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="N45" t="s">
-        <v>113</v>
+        <v>95</v>
       </c>
       <c r="O45" t="s">
         <v>171</v>
@@ -3200,10 +3200,10 @@
         <v>86</v>
       </c>
       <c r="M46" t="s">
-        <v>182</v>
+        <v>192</v>
       </c>
       <c r="N46" t="s">
-        <v>183</v>
+        <v>193</v>
       </c>
       <c r="O46" t="s">
         <v>171</v>
@@ -3226,10 +3226,10 @@
         <v>86</v>
       </c>
       <c r="M47" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="N47" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="O47" t="s">
         <v>171</v>
@@ -3252,10 +3252,10 @@
         <v>86</v>
       </c>
       <c r="M48" t="s">
-        <v>146</v>
+        <v>116</v>
       </c>
       <c r="N48" t="s">
-        <v>147</v>
+        <v>117</v>
       </c>
       <c r="O48" t="s">
         <v>171</v>
@@ -3278,10 +3278,10 @@
         <v>86</v>
       </c>
       <c r="M49" t="s">
-        <v>184</v>
+        <v>110</v>
       </c>
       <c r="N49" t="s">
-        <v>185</v>
+        <v>111</v>
       </c>
       <c r="O49" t="s">
         <v>171</v>
@@ -3304,10 +3304,10 @@
         <v>86</v>
       </c>
       <c r="M50" t="s">
-        <v>186</v>
+        <v>163</v>
       </c>
       <c r="N50" t="s">
-        <v>187</v>
+        <v>164</v>
       </c>
       <c r="O50" t="s">
         <v>171</v>
@@ -3344,10 +3344,10 @@
         <v>86</v>
       </c>
       <c r="M52" t="s">
-        <v>94</v>
+        <v>140</v>
       </c>
       <c r="N52" t="s">
-        <v>95</v>
+        <v>141</v>
       </c>
       <c r="O52" t="s">
         <v>171</v>
@@ -3358,10 +3358,10 @@
         <v>86</v>
       </c>
       <c r="M53" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="N53" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="O53" t="s">
         <v>171</v>
@@ -3372,10 +3372,10 @@
         <v>86</v>
       </c>
       <c r="M54" t="s">
-        <v>132</v>
+        <v>167</v>
       </c>
       <c r="N54" t="s">
-        <v>133</v>
+        <v>168</v>
       </c>
       <c r="O54" t="s">
         <v>171</v>
@@ -3386,10 +3386,10 @@
         <v>86</v>
       </c>
       <c r="M55" t="s">
-        <v>188</v>
+        <v>134</v>
       </c>
       <c r="N55" t="s">
-        <v>189</v>
+        <v>135</v>
       </c>
       <c r="O55" t="s">
         <v>171</v>
@@ -3400,10 +3400,10 @@
         <v>86</v>
       </c>
       <c r="M56" t="s">
-        <v>138</v>
+        <v>92</v>
       </c>
       <c r="N56" t="s">
-        <v>139</v>
+        <v>93</v>
       </c>
       <c r="O56" t="s">
         <v>171</v>
@@ -3414,10 +3414,10 @@
         <v>86</v>
       </c>
       <c r="M57" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="N57" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="O57" t="s">
         <v>171</v>
@@ -3428,10 +3428,10 @@
         <v>86</v>
       </c>
       <c r="M58" t="s">
-        <v>190</v>
+        <v>118</v>
       </c>
       <c r="N58" t="s">
-        <v>191</v>
+        <v>119</v>
       </c>
       <c r="O58" t="s">
         <v>171</v>
@@ -3442,10 +3442,10 @@
         <v>86</v>
       </c>
       <c r="M59" t="s">
-        <v>192</v>
+        <v>158</v>
       </c>
       <c r="N59" t="s">
-        <v>193</v>
+        <v>159</v>
       </c>
       <c r="O59" t="s">
         <v>171</v>
@@ -3456,10 +3456,10 @@
         <v>86</v>
       </c>
       <c r="M60" t="s">
-        <v>136</v>
+        <v>146</v>
       </c>
       <c r="N60" t="s">
-        <v>137</v>
+        <v>147</v>
       </c>
       <c r="O60" t="s">
         <v>171</v>
@@ -3470,10 +3470,10 @@
         <v>86</v>
       </c>
       <c r="M61" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="N61" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="O61" t="s">
         <v>171</v>
@@ -3484,10 +3484,10 @@
         <v>86</v>
       </c>
       <c r="M62" t="s">
-        <v>144</v>
+        <v>169</v>
       </c>
       <c r="N62" t="s">
-        <v>145</v>
+        <v>170</v>
       </c>
       <c r="O62" t="s">
         <v>171</v>

--- a/VerveStacks_POL_grids_kan50/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_POL_grids_kan50/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DFE0F8A-EC41-4DE1-B85D-C1ADD2E779F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CB99746-9592-4CAC-A69B-07CE79B2B126}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -556,70 +556,70 @@
     <t>e_demand,ev_battery,H2prd_Elc_PEM,H2prd_Elc_ALK</t>
   </si>
   <si>
+    <t>Chelm_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Chelm_POL</t>
+  </si>
+  <si>
+    <t>Siedlce_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Siedlce_POL</t>
+  </si>
+  <si>
+    <t>Elk_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Elk_POL</t>
+  </si>
+  <si>
+    <t>Zamosc_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Zamosc_POL</t>
+  </si>
+  <si>
+    <t>Legnica_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Legnica_POL</t>
+  </si>
+  <si>
     <t>Kielce_POL</t>
   </si>
   <si>
     <t>at grid node - Kielce_POL</t>
   </si>
   <si>
+    <t>Pila_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Pila_POL</t>
+  </si>
+  <si>
     <t>Olsztyn_POL</t>
   </si>
   <si>
     <t>at grid node - Olsztyn_POL</t>
   </si>
   <si>
+    <t>Walbrzych_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Walbrzych_POL</t>
+  </si>
+  <si>
+    <t>OstrowiecSwietokrz_POL</t>
+  </si>
+  <si>
+    <t>at grid node - OstrowiecSwietokrz_POL</t>
+  </si>
+  <si>
     <t>Grajewo_POL</t>
   </si>
   <si>
     <t>at grid node - Grajewo_POL</t>
-  </si>
-  <si>
-    <t>Pila_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Pila_POL</t>
-  </si>
-  <si>
-    <t>Zamosc_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Zamosc_POL</t>
-  </si>
-  <si>
-    <t>Siedlce_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Siedlce_POL</t>
-  </si>
-  <si>
-    <t>Walbrzych_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Walbrzych_POL</t>
-  </si>
-  <si>
-    <t>OstrowiecSwietokrz_POL</t>
-  </si>
-  <si>
-    <t>at grid node - OstrowiecSwietokrz_POL</t>
-  </si>
-  <si>
-    <t>Legnica_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Legnica_POL</t>
-  </si>
-  <si>
-    <t>Chelm_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Chelm_POL</t>
-  </si>
-  <si>
-    <t>Elk_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Elk_POL</t>
   </si>
   <si>
     <t>h_demand</t>
@@ -1126,10 +1126,10 @@
         <v>86</v>
       </c>
       <c r="M11" t="s">
-        <v>138</v>
+        <v>163</v>
       </c>
       <c r="N11" t="s">
-        <v>139</v>
+        <v>164</v>
       </c>
       <c r="O11" t="s">
         <v>171</v>
@@ -1250,10 +1250,10 @@
         <v>86</v>
       </c>
       <c r="M13" t="s">
-        <v>174</v>
+        <v>140</v>
       </c>
       <c r="N13" t="s">
-        <v>175</v>
+        <v>141</v>
       </c>
       <c r="O13" t="s">
         <v>171</v>
@@ -1312,10 +1312,10 @@
         <v>86</v>
       </c>
       <c r="M14" t="s">
-        <v>148</v>
+        <v>120</v>
       </c>
       <c r="N14" t="s">
-        <v>149</v>
+        <v>121</v>
       </c>
       <c r="O14" t="s">
         <v>171</v>
@@ -1374,10 +1374,10 @@
         <v>86</v>
       </c>
       <c r="M15" t="s">
-        <v>165</v>
+        <v>126</v>
       </c>
       <c r="N15" t="s">
-        <v>166</v>
+        <v>127</v>
       </c>
       <c r="O15" t="s">
         <v>171</v>
@@ -1436,10 +1436,10 @@
         <v>86</v>
       </c>
       <c r="M16" t="s">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="N16" t="s">
-        <v>127</v>
+        <v>137</v>
       </c>
       <c r="O16" t="s">
         <v>171</v>
@@ -1498,10 +1498,10 @@
         <v>86</v>
       </c>
       <c r="M17" t="s">
-        <v>150</v>
+        <v>122</v>
       </c>
       <c r="N17" t="s">
-        <v>151</v>
+        <v>123</v>
       </c>
       <c r="O17" t="s">
         <v>171</v>
@@ -1560,10 +1560,10 @@
         <v>86</v>
       </c>
       <c r="M18" t="s">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="N18" t="s">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="O18" t="s">
         <v>171</v>
@@ -1622,10 +1622,10 @@
         <v>86</v>
       </c>
       <c r="M19" t="s">
-        <v>176</v>
+        <v>142</v>
       </c>
       <c r="N19" t="s">
-        <v>177</v>
+        <v>143</v>
       </c>
       <c r="O19" t="s">
         <v>171</v>
@@ -1684,10 +1684,10 @@
         <v>86</v>
       </c>
       <c r="M20" t="s">
-        <v>144</v>
+        <v>174</v>
       </c>
       <c r="N20" t="s">
-        <v>145</v>
+        <v>175</v>
       </c>
       <c r="O20" t="s">
         <v>171</v>
@@ -1746,10 +1746,10 @@
         <v>86</v>
       </c>
       <c r="M21" t="s">
-        <v>130</v>
+        <v>148</v>
       </c>
       <c r="N21" t="s">
-        <v>131</v>
+        <v>149</v>
       </c>
       <c r="O21" t="s">
         <v>171</v>
@@ -1808,10 +1808,10 @@
         <v>86</v>
       </c>
       <c r="M22" t="s">
-        <v>102</v>
+        <v>154</v>
       </c>
       <c r="N22" t="s">
-        <v>103</v>
+        <v>155</v>
       </c>
       <c r="O22" t="s">
         <v>171</v>
@@ -1870,10 +1870,10 @@
         <v>86</v>
       </c>
       <c r="M23" t="s">
-        <v>120</v>
+        <v>176</v>
       </c>
       <c r="N23" t="s">
-        <v>121</v>
+        <v>177</v>
       </c>
       <c r="O23" t="s">
         <v>171</v>
@@ -1932,10 +1932,10 @@
         <v>86</v>
       </c>
       <c r="M24" t="s">
-        <v>90</v>
+        <v>156</v>
       </c>
       <c r="N24" t="s">
-        <v>91</v>
+        <v>157</v>
       </c>
       <c r="O24" t="s">
         <v>171</v>
@@ -1994,10 +1994,10 @@
         <v>86</v>
       </c>
       <c r="M25" t="s">
-        <v>178</v>
+        <v>112</v>
       </c>
       <c r="N25" t="s">
-        <v>179</v>
+        <v>113</v>
       </c>
       <c r="O25" t="s">
         <v>171</v>
@@ -2056,10 +2056,10 @@
         <v>86</v>
       </c>
       <c r="M26" t="s">
-        <v>114</v>
+        <v>94</v>
       </c>
       <c r="N26" t="s">
-        <v>115</v>
+        <v>95</v>
       </c>
       <c r="O26" t="s">
         <v>171</v>
@@ -2118,10 +2118,10 @@
         <v>86</v>
       </c>
       <c r="M27" t="s">
-        <v>180</v>
+        <v>161</v>
       </c>
       <c r="N27" t="s">
-        <v>181</v>
+        <v>162</v>
       </c>
       <c r="O27" t="s">
         <v>171</v>
@@ -2180,10 +2180,10 @@
         <v>86</v>
       </c>
       <c r="M28" t="s">
-        <v>182</v>
+        <v>146</v>
       </c>
       <c r="N28" t="s">
-        <v>183</v>
+        <v>147</v>
       </c>
       <c r="O28" t="s">
         <v>171</v>
@@ -2242,10 +2242,10 @@
         <v>86</v>
       </c>
       <c r="M29" t="s">
-        <v>184</v>
+        <v>138</v>
       </c>
       <c r="N29" t="s">
-        <v>185</v>
+        <v>139</v>
       </c>
       <c r="O29" t="s">
         <v>171</v>
@@ -2304,10 +2304,10 @@
         <v>86</v>
       </c>
       <c r="M30" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="N30" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="O30" t="s">
         <v>171</v>
@@ -2366,10 +2366,10 @@
         <v>86</v>
       </c>
       <c r="M31" t="s">
-        <v>87</v>
+        <v>158</v>
       </c>
       <c r="N31" t="s">
-        <v>88</v>
+        <v>159</v>
       </c>
       <c r="O31" t="s">
         <v>171</v>
@@ -2428,10 +2428,10 @@
         <v>86</v>
       </c>
       <c r="M32" t="s">
-        <v>124</v>
+        <v>178</v>
       </c>
       <c r="N32" t="s">
-        <v>125</v>
+        <v>179</v>
       </c>
       <c r="O32" t="s">
         <v>171</v>
@@ -2490,10 +2490,10 @@
         <v>86</v>
       </c>
       <c r="M33" t="s">
-        <v>186</v>
+        <v>108</v>
       </c>
       <c r="N33" t="s">
-        <v>187</v>
+        <v>109</v>
       </c>
       <c r="O33" t="s">
         <v>171</v>
@@ -2552,10 +2552,10 @@
         <v>86</v>
       </c>
       <c r="M34" t="s">
-        <v>136</v>
+        <v>98</v>
       </c>
       <c r="N34" t="s">
-        <v>137</v>
+        <v>99</v>
       </c>
       <c r="O34" t="s">
         <v>171</v>
@@ -2614,10 +2614,10 @@
         <v>86</v>
       </c>
       <c r="M35" t="s">
-        <v>108</v>
+        <v>180</v>
       </c>
       <c r="N35" t="s">
-        <v>109</v>
+        <v>181</v>
       </c>
       <c r="O35" t="s">
         <v>171</v>
@@ -2676,10 +2676,10 @@
         <v>86</v>
       </c>
       <c r="M36" t="s">
-        <v>188</v>
+        <v>152</v>
       </c>
       <c r="N36" t="s">
-        <v>189</v>
+        <v>153</v>
       </c>
       <c r="O36" t="s">
         <v>171</v>
@@ -2738,10 +2738,10 @@
         <v>86</v>
       </c>
       <c r="M37" t="s">
-        <v>190</v>
+        <v>118</v>
       </c>
       <c r="N37" t="s">
-        <v>191</v>
+        <v>119</v>
       </c>
       <c r="O37" t="s">
         <v>171</v>
@@ -2800,10 +2800,10 @@
         <v>86</v>
       </c>
       <c r="M38" t="s">
-        <v>161</v>
+        <v>116</v>
       </c>
       <c r="N38" t="s">
-        <v>162</v>
+        <v>117</v>
       </c>
       <c r="O38" t="s">
         <v>171</v>
@@ -2862,10 +2862,10 @@
         <v>86</v>
       </c>
       <c r="M39" t="s">
-        <v>98</v>
+        <v>182</v>
       </c>
       <c r="N39" t="s">
-        <v>99</v>
+        <v>183</v>
       </c>
       <c r="O39" t="s">
         <v>171</v>
@@ -2924,10 +2924,10 @@
         <v>86</v>
       </c>
       <c r="M40" t="s">
-        <v>142</v>
+        <v>184</v>
       </c>
       <c r="N40" t="s">
-        <v>143</v>
+        <v>185</v>
       </c>
       <c r="O40" t="s">
         <v>171</v>
@@ -2986,10 +2986,10 @@
         <v>86</v>
       </c>
       <c r="M41" t="s">
-        <v>112</v>
+        <v>144</v>
       </c>
       <c r="N41" t="s">
-        <v>113</v>
+        <v>145</v>
       </c>
       <c r="O41" t="s">
         <v>171</v>
@@ -3048,10 +3048,10 @@
         <v>86</v>
       </c>
       <c r="M42" t="s">
-        <v>104</v>
+        <v>150</v>
       </c>
       <c r="N42" t="s">
-        <v>105</v>
+        <v>151</v>
       </c>
       <c r="O42" t="s">
         <v>171</v>
@@ -3086,10 +3086,10 @@
         <v>86</v>
       </c>
       <c r="M43" t="s">
-        <v>154</v>
+        <v>102</v>
       </c>
       <c r="N43" t="s">
-        <v>155</v>
+        <v>103</v>
       </c>
       <c r="O43" t="s">
         <v>171</v>
@@ -3124,10 +3124,10 @@
         <v>86</v>
       </c>
       <c r="M44" t="s">
-        <v>152</v>
+        <v>186</v>
       </c>
       <c r="N44" t="s">
-        <v>153</v>
+        <v>187</v>
       </c>
       <c r="O44" t="s">
         <v>171</v>
@@ -3162,10 +3162,10 @@
         <v>86</v>
       </c>
       <c r="M45" t="s">
-        <v>94</v>
+        <v>167</v>
       </c>
       <c r="N45" t="s">
-        <v>95</v>
+        <v>168</v>
       </c>
       <c r="O45" t="s">
         <v>171</v>
@@ -3200,10 +3200,10 @@
         <v>86</v>
       </c>
       <c r="M46" t="s">
-        <v>192</v>
+        <v>130</v>
       </c>
       <c r="N46" t="s">
-        <v>193</v>
+        <v>131</v>
       </c>
       <c r="O46" t="s">
         <v>171</v>
@@ -3226,10 +3226,10 @@
         <v>86</v>
       </c>
       <c r="M47" t="s">
-        <v>100</v>
+        <v>124</v>
       </c>
       <c r="N47" t="s">
-        <v>101</v>
+        <v>125</v>
       </c>
       <c r="O47" t="s">
         <v>171</v>
@@ -3252,10 +3252,10 @@
         <v>86</v>
       </c>
       <c r="M48" t="s">
-        <v>116</v>
+        <v>128</v>
       </c>
       <c r="N48" t="s">
-        <v>117</v>
+        <v>129</v>
       </c>
       <c r="O48" t="s">
         <v>171</v>
@@ -3278,10 +3278,10 @@
         <v>86</v>
       </c>
       <c r="M49" t="s">
-        <v>110</v>
+        <v>188</v>
       </c>
       <c r="N49" t="s">
-        <v>111</v>
+        <v>189</v>
       </c>
       <c r="O49" t="s">
         <v>171</v>
@@ -3304,10 +3304,10 @@
         <v>86</v>
       </c>
       <c r="M50" t="s">
-        <v>163</v>
+        <v>106</v>
       </c>
       <c r="N50" t="s">
-        <v>164</v>
+        <v>107</v>
       </c>
       <c r="O50" t="s">
         <v>171</v>
@@ -3330,10 +3330,10 @@
         <v>86</v>
       </c>
       <c r="M51" t="s">
-        <v>156</v>
+        <v>100</v>
       </c>
       <c r="N51" t="s">
-        <v>157</v>
+        <v>101</v>
       </c>
       <c r="O51" t="s">
         <v>171</v>
@@ -3344,10 +3344,10 @@
         <v>86</v>
       </c>
       <c r="M52" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="N52" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="O52" t="s">
         <v>171</v>
@@ -3358,10 +3358,10 @@
         <v>86</v>
       </c>
       <c r="M53" t="s">
-        <v>128</v>
+        <v>90</v>
       </c>
       <c r="N53" t="s">
-        <v>129</v>
+        <v>91</v>
       </c>
       <c r="O53" t="s">
         <v>171</v>
@@ -3372,10 +3372,10 @@
         <v>86</v>
       </c>
       <c r="M54" t="s">
-        <v>167</v>
+        <v>87</v>
       </c>
       <c r="N54" t="s">
-        <v>168</v>
+        <v>88</v>
       </c>
       <c r="O54" t="s">
         <v>171</v>
@@ -3386,10 +3386,10 @@
         <v>86</v>
       </c>
       <c r="M55" t="s">
-        <v>134</v>
+        <v>96</v>
       </c>
       <c r="N55" t="s">
-        <v>135</v>
+        <v>97</v>
       </c>
       <c r="O55" t="s">
         <v>171</v>
@@ -3400,10 +3400,10 @@
         <v>86</v>
       </c>
       <c r="M56" t="s">
-        <v>92</v>
+        <v>190</v>
       </c>
       <c r="N56" t="s">
-        <v>93</v>
+        <v>191</v>
       </c>
       <c r="O56" t="s">
         <v>171</v>
@@ -3414,10 +3414,10 @@
         <v>86</v>
       </c>
       <c r="M57" t="s">
-        <v>132</v>
+        <v>114</v>
       </c>
       <c r="N57" t="s">
-        <v>133</v>
+        <v>115</v>
       </c>
       <c r="O57" t="s">
         <v>171</v>
@@ -3428,10 +3428,10 @@
         <v>86</v>
       </c>
       <c r="M58" t="s">
-        <v>118</v>
+        <v>104</v>
       </c>
       <c r="N58" t="s">
-        <v>119</v>
+        <v>105</v>
       </c>
       <c r="O58" t="s">
         <v>171</v>
@@ -3442,10 +3442,10 @@
         <v>86</v>
       </c>
       <c r="M59" t="s">
-        <v>158</v>
+        <v>169</v>
       </c>
       <c r="N59" t="s">
-        <v>159</v>
+        <v>170</v>
       </c>
       <c r="O59" t="s">
         <v>171</v>
@@ -3456,10 +3456,10 @@
         <v>86</v>
       </c>
       <c r="M60" t="s">
-        <v>146</v>
+        <v>110</v>
       </c>
       <c r="N60" t="s">
-        <v>147</v>
+        <v>111</v>
       </c>
       <c r="O60" t="s">
         <v>171</v>
@@ -3470,10 +3470,10 @@
         <v>86</v>
       </c>
       <c r="M61" t="s">
-        <v>106</v>
+        <v>192</v>
       </c>
       <c r="N61" t="s">
-        <v>107</v>
+        <v>193</v>
       </c>
       <c r="O61" t="s">
         <v>171</v>
@@ -3484,10 +3484,10 @@
         <v>86</v>
       </c>
       <c r="M62" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="N62" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="O62" t="s">
         <v>171</v>

--- a/VerveStacks_POL_grids_kan50/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_POL_grids_kan50/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CB99746-9592-4CAC-A69B-07CE79B2B126}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FCACDF4-9DB8-4336-BBE2-E4F96C8F8A4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -556,70 +556,70 @@
     <t>e_demand,ev_battery,H2prd_Elc_PEM,H2prd_Elc_ALK</t>
   </si>
   <si>
+    <t>Grajewo_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Grajewo_POL</t>
+  </si>
+  <si>
+    <t>Elk_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Elk_POL</t>
+  </si>
+  <si>
+    <t>Pila_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Pila_POL</t>
+  </si>
+  <si>
+    <t>Walbrzych_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Walbrzych_POL</t>
+  </si>
+  <si>
+    <t>Olsztyn_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Olsztyn_POL</t>
+  </si>
+  <si>
+    <t>Legnica_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Legnica_POL</t>
+  </si>
+  <si>
+    <t>Zamosc_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Zamosc_POL</t>
+  </si>
+  <si>
+    <t>Siedlce_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Siedlce_POL</t>
+  </si>
+  <si>
     <t>Chelm_POL</t>
   </si>
   <si>
     <t>at grid node - Chelm_POL</t>
   </si>
   <si>
-    <t>Siedlce_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Siedlce_POL</t>
-  </si>
-  <si>
-    <t>Elk_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Elk_POL</t>
-  </si>
-  <si>
-    <t>Zamosc_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Zamosc_POL</t>
-  </si>
-  <si>
-    <t>Legnica_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Legnica_POL</t>
-  </si>
-  <si>
     <t>Kielce_POL</t>
   </si>
   <si>
     <t>at grid node - Kielce_POL</t>
   </si>
   <si>
-    <t>Pila_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Pila_POL</t>
-  </si>
-  <si>
-    <t>Olsztyn_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Olsztyn_POL</t>
-  </si>
-  <si>
-    <t>Walbrzych_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Walbrzych_POL</t>
-  </si>
-  <si>
     <t>OstrowiecSwietokrz_POL</t>
   </si>
   <si>
     <t>at grid node - OstrowiecSwietokrz_POL</t>
-  </si>
-  <si>
-    <t>Grajewo_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Grajewo_POL</t>
   </si>
   <si>
     <t>h_demand</t>
@@ -1126,10 +1126,10 @@
         <v>86</v>
       </c>
       <c r="M11" t="s">
-        <v>163</v>
+        <v>120</v>
       </c>
       <c r="N11" t="s">
-        <v>164</v>
+        <v>121</v>
       </c>
       <c r="O11" t="s">
         <v>171</v>
@@ -1188,10 +1188,10 @@
         <v>86</v>
       </c>
       <c r="M12" t="s">
-        <v>172</v>
+        <v>122</v>
       </c>
       <c r="N12" t="s">
-        <v>173</v>
+        <v>123</v>
       </c>
       <c r="O12" t="s">
         <v>171</v>
@@ -1250,10 +1250,10 @@
         <v>86</v>
       </c>
       <c r="M13" t="s">
-        <v>140</v>
+        <v>110</v>
       </c>
       <c r="N13" t="s">
-        <v>141</v>
+        <v>111</v>
       </c>
       <c r="O13" t="s">
         <v>171</v>
@@ -1312,10 +1312,10 @@
         <v>86</v>
       </c>
       <c r="M14" t="s">
-        <v>120</v>
+        <v>154</v>
       </c>
       <c r="N14" t="s">
-        <v>121</v>
+        <v>155</v>
       </c>
       <c r="O14" t="s">
         <v>171</v>
@@ -1374,10 +1374,10 @@
         <v>86</v>
       </c>
       <c r="M15" t="s">
-        <v>126</v>
+        <v>146</v>
       </c>
       <c r="N15" t="s">
-        <v>127</v>
+        <v>147</v>
       </c>
       <c r="O15" t="s">
         <v>171</v>
@@ -1436,10 +1436,10 @@
         <v>86</v>
       </c>
       <c r="M16" t="s">
-        <v>136</v>
+        <v>172</v>
       </c>
       <c r="N16" t="s">
-        <v>137</v>
+        <v>173</v>
       </c>
       <c r="O16" t="s">
         <v>171</v>
@@ -1498,10 +1498,10 @@
         <v>86</v>
       </c>
       <c r="M17" t="s">
-        <v>122</v>
+        <v>98</v>
       </c>
       <c r="N17" t="s">
-        <v>123</v>
+        <v>99</v>
       </c>
       <c r="O17" t="s">
         <v>171</v>
@@ -1560,10 +1560,10 @@
         <v>86</v>
       </c>
       <c r="M18" t="s">
-        <v>132</v>
+        <v>165</v>
       </c>
       <c r="N18" t="s">
-        <v>133</v>
+        <v>166</v>
       </c>
       <c r="O18" t="s">
         <v>171</v>
@@ -1622,10 +1622,10 @@
         <v>86</v>
       </c>
       <c r="M19" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="N19" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="O19" t="s">
         <v>171</v>
@@ -1746,10 +1746,10 @@
         <v>86</v>
       </c>
       <c r="M21" t="s">
-        <v>148</v>
+        <v>163</v>
       </c>
       <c r="N21" t="s">
-        <v>149</v>
+        <v>164</v>
       </c>
       <c r="O21" t="s">
         <v>171</v>
@@ -1808,10 +1808,10 @@
         <v>86</v>
       </c>
       <c r="M22" t="s">
-        <v>154</v>
+        <v>96</v>
       </c>
       <c r="N22" t="s">
-        <v>155</v>
+        <v>97</v>
       </c>
       <c r="O22" t="s">
         <v>171</v>
@@ -1932,10 +1932,10 @@
         <v>86</v>
       </c>
       <c r="M24" t="s">
-        <v>156</v>
+        <v>104</v>
       </c>
       <c r="N24" t="s">
-        <v>157</v>
+        <v>105</v>
       </c>
       <c r="O24" t="s">
         <v>171</v>
@@ -1994,10 +1994,10 @@
         <v>86</v>
       </c>
       <c r="M25" t="s">
-        <v>112</v>
+        <v>152</v>
       </c>
       <c r="N25" t="s">
-        <v>113</v>
+        <v>153</v>
       </c>
       <c r="O25" t="s">
         <v>171</v>
@@ -2056,10 +2056,10 @@
         <v>86</v>
       </c>
       <c r="M26" t="s">
-        <v>94</v>
+        <v>148</v>
       </c>
       <c r="N26" t="s">
-        <v>95</v>
+        <v>149</v>
       </c>
       <c r="O26" t="s">
         <v>171</v>
@@ -2118,10 +2118,10 @@
         <v>86</v>
       </c>
       <c r="M27" t="s">
-        <v>161</v>
+        <v>114</v>
       </c>
       <c r="N27" t="s">
-        <v>162</v>
+        <v>115</v>
       </c>
       <c r="O27" t="s">
         <v>171</v>
@@ -2180,10 +2180,10 @@
         <v>86</v>
       </c>
       <c r="M28" t="s">
-        <v>146</v>
+        <v>108</v>
       </c>
       <c r="N28" t="s">
-        <v>147</v>
+        <v>109</v>
       </c>
       <c r="O28" t="s">
         <v>171</v>
@@ -2242,10 +2242,10 @@
         <v>86</v>
       </c>
       <c r="M29" t="s">
-        <v>138</v>
+        <v>178</v>
       </c>
       <c r="N29" t="s">
-        <v>139</v>
+        <v>179</v>
       </c>
       <c r="O29" t="s">
         <v>171</v>
@@ -2304,10 +2304,10 @@
         <v>86</v>
       </c>
       <c r="M30" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="N30" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="O30" t="s">
         <v>171</v>
@@ -2366,10 +2366,10 @@
         <v>86</v>
       </c>
       <c r="M31" t="s">
-        <v>158</v>
+        <v>112</v>
       </c>
       <c r="N31" t="s">
-        <v>159</v>
+        <v>113</v>
       </c>
       <c r="O31" t="s">
         <v>171</v>
@@ -2428,10 +2428,10 @@
         <v>86</v>
       </c>
       <c r="M32" t="s">
-        <v>178</v>
+        <v>169</v>
       </c>
       <c r="N32" t="s">
-        <v>179</v>
+        <v>170</v>
       </c>
       <c r="O32" t="s">
         <v>171</v>
@@ -2490,10 +2490,10 @@
         <v>86</v>
       </c>
       <c r="M33" t="s">
-        <v>108</v>
+        <v>158</v>
       </c>
       <c r="N33" t="s">
-        <v>109</v>
+        <v>159</v>
       </c>
       <c r="O33" t="s">
         <v>171</v>
@@ -2552,10 +2552,10 @@
         <v>86</v>
       </c>
       <c r="M34" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="N34" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="O34" t="s">
         <v>171</v>
@@ -2614,10 +2614,10 @@
         <v>86</v>
       </c>
       <c r="M35" t="s">
-        <v>180</v>
+        <v>142</v>
       </c>
       <c r="N35" t="s">
-        <v>181</v>
+        <v>143</v>
       </c>
       <c r="O35" t="s">
         <v>171</v>
@@ -2676,10 +2676,10 @@
         <v>86</v>
       </c>
       <c r="M36" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="N36" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="O36" t="s">
         <v>171</v>
@@ -2738,10 +2738,10 @@
         <v>86</v>
       </c>
       <c r="M37" t="s">
-        <v>118</v>
+        <v>150</v>
       </c>
       <c r="N37" t="s">
-        <v>119</v>
+        <v>151</v>
       </c>
       <c r="O37" t="s">
         <v>171</v>
@@ -2800,10 +2800,10 @@
         <v>86</v>
       </c>
       <c r="M38" t="s">
-        <v>116</v>
+        <v>132</v>
       </c>
       <c r="N38" t="s">
-        <v>117</v>
+        <v>133</v>
       </c>
       <c r="O38" t="s">
         <v>171</v>
@@ -2862,10 +2862,10 @@
         <v>86</v>
       </c>
       <c r="M39" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="N39" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="O39" t="s">
         <v>171</v>
@@ -2924,10 +2924,10 @@
         <v>86</v>
       </c>
       <c r="M40" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="N40" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="O40" t="s">
         <v>171</v>
@@ -2986,10 +2986,10 @@
         <v>86</v>
       </c>
       <c r="M41" t="s">
-        <v>144</v>
+        <v>128</v>
       </c>
       <c r="N41" t="s">
-        <v>145</v>
+        <v>129</v>
       </c>
       <c r="O41" t="s">
         <v>171</v>
@@ -3048,10 +3048,10 @@
         <v>86</v>
       </c>
       <c r="M42" t="s">
-        <v>150</v>
+        <v>184</v>
       </c>
       <c r="N42" t="s">
-        <v>151</v>
+        <v>185</v>
       </c>
       <c r="O42" t="s">
         <v>171</v>
@@ -3086,10 +3086,10 @@
         <v>86</v>
       </c>
       <c r="M43" t="s">
-        <v>102</v>
+        <v>136</v>
       </c>
       <c r="N43" t="s">
-        <v>103</v>
+        <v>137</v>
       </c>
       <c r="O43" t="s">
         <v>171</v>
@@ -3124,10 +3124,10 @@
         <v>86</v>
       </c>
       <c r="M44" t="s">
-        <v>186</v>
+        <v>106</v>
       </c>
       <c r="N44" t="s">
-        <v>187</v>
+        <v>107</v>
       </c>
       <c r="O44" t="s">
         <v>171</v>
@@ -3162,10 +3162,10 @@
         <v>86</v>
       </c>
       <c r="M45" t="s">
-        <v>167</v>
+        <v>102</v>
       </c>
       <c r="N45" t="s">
-        <v>168</v>
+        <v>103</v>
       </c>
       <c r="O45" t="s">
         <v>171</v>
@@ -3200,10 +3200,10 @@
         <v>86</v>
       </c>
       <c r="M46" t="s">
-        <v>130</v>
+        <v>116</v>
       </c>
       <c r="N46" t="s">
-        <v>131</v>
+        <v>117</v>
       </c>
       <c r="O46" t="s">
         <v>171</v>
@@ -3226,10 +3226,10 @@
         <v>86</v>
       </c>
       <c r="M47" t="s">
-        <v>124</v>
+        <v>186</v>
       </c>
       <c r="N47" t="s">
-        <v>125</v>
+        <v>187</v>
       </c>
       <c r="O47" t="s">
         <v>171</v>
@@ -3252,10 +3252,10 @@
         <v>86</v>
       </c>
       <c r="M48" t="s">
-        <v>128</v>
+        <v>140</v>
       </c>
       <c r="N48" t="s">
-        <v>129</v>
+        <v>141</v>
       </c>
       <c r="O48" t="s">
         <v>171</v>
@@ -3278,10 +3278,10 @@
         <v>86</v>
       </c>
       <c r="M49" t="s">
-        <v>188</v>
+        <v>100</v>
       </c>
       <c r="N49" t="s">
-        <v>189</v>
+        <v>101</v>
       </c>
       <c r="O49" t="s">
         <v>171</v>
@@ -3304,10 +3304,10 @@
         <v>86</v>
       </c>
       <c r="M50" t="s">
-        <v>106</v>
+        <v>126</v>
       </c>
       <c r="N50" t="s">
-        <v>107</v>
+        <v>127</v>
       </c>
       <c r="O50" t="s">
         <v>171</v>
@@ -3330,10 +3330,10 @@
         <v>86</v>
       </c>
       <c r="M51" t="s">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="N51" t="s">
-        <v>101</v>
+        <v>131</v>
       </c>
       <c r="O51" t="s">
         <v>171</v>
@@ -3344,10 +3344,10 @@
         <v>86</v>
       </c>
       <c r="M52" t="s">
-        <v>134</v>
+        <v>167</v>
       </c>
       <c r="N52" t="s">
-        <v>135</v>
+        <v>168</v>
       </c>
       <c r="O52" t="s">
         <v>171</v>
@@ -3358,10 +3358,10 @@
         <v>86</v>
       </c>
       <c r="M53" t="s">
-        <v>90</v>
+        <v>118</v>
       </c>
       <c r="N53" t="s">
-        <v>91</v>
+        <v>119</v>
       </c>
       <c r="O53" t="s">
         <v>171</v>
@@ -3372,10 +3372,10 @@
         <v>86</v>
       </c>
       <c r="M54" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="N54" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="O54" t="s">
         <v>171</v>
@@ -3386,10 +3386,10 @@
         <v>86</v>
       </c>
       <c r="M55" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="N55" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="O55" t="s">
         <v>171</v>
@@ -3400,10 +3400,10 @@
         <v>86</v>
       </c>
       <c r="M56" t="s">
-        <v>190</v>
+        <v>161</v>
       </c>
       <c r="N56" t="s">
-        <v>191</v>
+        <v>162</v>
       </c>
       <c r="O56" t="s">
         <v>171</v>
@@ -3414,10 +3414,10 @@
         <v>86</v>
       </c>
       <c r="M57" t="s">
-        <v>114</v>
+        <v>188</v>
       </c>
       <c r="N57" t="s">
-        <v>115</v>
+        <v>189</v>
       </c>
       <c r="O57" t="s">
         <v>171</v>
@@ -3428,10 +3428,10 @@
         <v>86</v>
       </c>
       <c r="M58" t="s">
-        <v>104</v>
+        <v>190</v>
       </c>
       <c r="N58" t="s">
-        <v>105</v>
+        <v>191</v>
       </c>
       <c r="O58" t="s">
         <v>171</v>
@@ -3442,10 +3442,10 @@
         <v>86</v>
       </c>
       <c r="M59" t="s">
-        <v>169</v>
+        <v>144</v>
       </c>
       <c r="N59" t="s">
-        <v>170</v>
+        <v>145</v>
       </c>
       <c r="O59" t="s">
         <v>171</v>
@@ -3456,10 +3456,10 @@
         <v>86</v>
       </c>
       <c r="M60" t="s">
-        <v>110</v>
+        <v>134</v>
       </c>
       <c r="N60" t="s">
-        <v>111</v>
+        <v>135</v>
       </c>
       <c r="O60" t="s">
         <v>171</v>
@@ -3484,10 +3484,10 @@
         <v>86</v>
       </c>
       <c r="M62" t="s">
-        <v>165</v>
+        <v>124</v>
       </c>
       <c r="N62" t="s">
-        <v>166</v>
+        <v>125</v>
       </c>
       <c r="O62" t="s">
         <v>171</v>

--- a/VerveStacks_POL_grids_kan50/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_POL_grids_kan50/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FCACDF4-9DB8-4336-BBE2-E4F96C8F8A4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C7AD0BA-BF96-46F5-8C9C-9E3EEB8CDFA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -556,70 +556,70 @@
     <t>e_demand,ev_battery,H2prd_Elc_PEM,H2prd_Elc_ALK</t>
   </si>
   <si>
+    <t>Pila_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Pila_POL</t>
+  </si>
+  <si>
+    <t>Chelm_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Chelm_POL</t>
+  </si>
+  <si>
+    <t>Kielce_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Kielce_POL</t>
+  </si>
+  <si>
+    <t>Legnica_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Legnica_POL</t>
+  </si>
+  <si>
+    <t>OstrowiecSwietokrz_POL</t>
+  </si>
+  <si>
+    <t>at grid node - OstrowiecSwietokrz_POL</t>
+  </si>
+  <si>
+    <t>Elk_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Elk_POL</t>
+  </si>
+  <si>
+    <t>Zamosc_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Zamosc_POL</t>
+  </si>
+  <si>
+    <t>Olsztyn_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Olsztyn_POL</t>
+  </si>
+  <si>
     <t>Grajewo_POL</t>
   </si>
   <si>
     <t>at grid node - Grajewo_POL</t>
   </si>
   <si>
-    <t>Elk_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Elk_POL</t>
-  </si>
-  <si>
-    <t>Pila_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Pila_POL</t>
+    <t>Siedlce_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Siedlce_POL</t>
   </si>
   <si>
     <t>Walbrzych_POL</t>
   </si>
   <si>
     <t>at grid node - Walbrzych_POL</t>
-  </si>
-  <si>
-    <t>Olsztyn_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Olsztyn_POL</t>
-  </si>
-  <si>
-    <t>Legnica_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Legnica_POL</t>
-  </si>
-  <si>
-    <t>Zamosc_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Zamosc_POL</t>
-  </si>
-  <si>
-    <t>Siedlce_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Siedlce_POL</t>
-  </si>
-  <si>
-    <t>Chelm_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Chelm_POL</t>
-  </si>
-  <si>
-    <t>Kielce_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Kielce_POL</t>
-  </si>
-  <si>
-    <t>OstrowiecSwietokrz_POL</t>
-  </si>
-  <si>
-    <t>at grid node - OstrowiecSwietokrz_POL</t>
   </si>
   <si>
     <t>h_demand</t>
@@ -1126,10 +1126,10 @@
         <v>86</v>
       </c>
       <c r="M11" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="N11" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="O11" t="s">
         <v>171</v>
@@ -1188,10 +1188,10 @@
         <v>86</v>
       </c>
       <c r="M12" t="s">
-        <v>122</v>
+        <v>158</v>
       </c>
       <c r="N12" t="s">
-        <v>123</v>
+        <v>159</v>
       </c>
       <c r="O12" t="s">
         <v>171</v>
@@ -1250,10 +1250,10 @@
         <v>86</v>
       </c>
       <c r="M13" t="s">
-        <v>110</v>
+        <v>87</v>
       </c>
       <c r="N13" t="s">
-        <v>111</v>
+        <v>88</v>
       </c>
       <c r="O13" t="s">
         <v>171</v>
@@ -1312,10 +1312,10 @@
         <v>86</v>
       </c>
       <c r="M14" t="s">
-        <v>154</v>
+        <v>172</v>
       </c>
       <c r="N14" t="s">
-        <v>155</v>
+        <v>173</v>
       </c>
       <c r="O14" t="s">
         <v>171</v>
@@ -1374,10 +1374,10 @@
         <v>86</v>
       </c>
       <c r="M15" t="s">
-        <v>146</v>
+        <v>96</v>
       </c>
       <c r="N15" t="s">
-        <v>147</v>
+        <v>97</v>
       </c>
       <c r="O15" t="s">
         <v>171</v>
@@ -1436,10 +1436,10 @@
         <v>86</v>
       </c>
       <c r="M16" t="s">
-        <v>172</v>
+        <v>104</v>
       </c>
       <c r="N16" t="s">
-        <v>173</v>
+        <v>105</v>
       </c>
       <c r="O16" t="s">
         <v>171</v>
@@ -1498,10 +1498,10 @@
         <v>86</v>
       </c>
       <c r="M17" t="s">
-        <v>98</v>
+        <v>156</v>
       </c>
       <c r="N17" t="s">
-        <v>99</v>
+        <v>157</v>
       </c>
       <c r="O17" t="s">
         <v>171</v>
@@ -1560,10 +1560,10 @@
         <v>86</v>
       </c>
       <c r="M18" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="N18" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="O18" t="s">
         <v>171</v>
@@ -1622,10 +1622,10 @@
         <v>86</v>
       </c>
       <c r="M19" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="N19" t="s">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="O19" t="s">
         <v>171</v>
@@ -1684,10 +1684,10 @@
         <v>86</v>
       </c>
       <c r="M20" t="s">
-        <v>174</v>
+        <v>94</v>
       </c>
       <c r="N20" t="s">
-        <v>175</v>
+        <v>95</v>
       </c>
       <c r="O20" t="s">
         <v>171</v>
@@ -1746,10 +1746,10 @@
         <v>86</v>
       </c>
       <c r="M21" t="s">
-        <v>163</v>
+        <v>114</v>
       </c>
       <c r="N21" t="s">
-        <v>164</v>
+        <v>115</v>
       </c>
       <c r="O21" t="s">
         <v>171</v>
@@ -1808,10 +1808,10 @@
         <v>86</v>
       </c>
       <c r="M22" t="s">
-        <v>96</v>
+        <v>167</v>
       </c>
       <c r="N22" t="s">
-        <v>97</v>
+        <v>168</v>
       </c>
       <c r="O22" t="s">
         <v>171</v>
@@ -1870,10 +1870,10 @@
         <v>86</v>
       </c>
       <c r="M23" t="s">
-        <v>176</v>
+        <v>140</v>
       </c>
       <c r="N23" t="s">
-        <v>177</v>
+        <v>141</v>
       </c>
       <c r="O23" t="s">
         <v>171</v>
@@ -1932,10 +1932,10 @@
         <v>86</v>
       </c>
       <c r="M24" t="s">
-        <v>104</v>
+        <v>174</v>
       </c>
       <c r="N24" t="s">
-        <v>105</v>
+        <v>175</v>
       </c>
       <c r="O24" t="s">
         <v>171</v>
@@ -1994,10 +1994,10 @@
         <v>86</v>
       </c>
       <c r="M25" t="s">
-        <v>152</v>
+        <v>116</v>
       </c>
       <c r="N25" t="s">
-        <v>153</v>
+        <v>117</v>
       </c>
       <c r="O25" t="s">
         <v>171</v>
@@ -2056,10 +2056,10 @@
         <v>86</v>
       </c>
       <c r="M26" t="s">
-        <v>148</v>
+        <v>120</v>
       </c>
       <c r="N26" t="s">
-        <v>149</v>
+        <v>121</v>
       </c>
       <c r="O26" t="s">
         <v>171</v>
@@ -2118,10 +2118,10 @@
         <v>86</v>
       </c>
       <c r="M27" t="s">
-        <v>114</v>
+        <v>98</v>
       </c>
       <c r="N27" t="s">
-        <v>115</v>
+        <v>99</v>
       </c>
       <c r="O27" t="s">
         <v>171</v>
@@ -2180,10 +2180,10 @@
         <v>86</v>
       </c>
       <c r="M28" t="s">
-        <v>108</v>
+        <v>142</v>
       </c>
       <c r="N28" t="s">
-        <v>109</v>
+        <v>143</v>
       </c>
       <c r="O28" t="s">
         <v>171</v>
@@ -2242,10 +2242,10 @@
         <v>86</v>
       </c>
       <c r="M29" t="s">
-        <v>178</v>
+        <v>128</v>
       </c>
       <c r="N29" t="s">
-        <v>179</v>
+        <v>129</v>
       </c>
       <c r="O29" t="s">
         <v>171</v>
@@ -2304,10 +2304,10 @@
         <v>86</v>
       </c>
       <c r="M30" t="s">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="N30" t="s">
-        <v>91</v>
+        <v>111</v>
       </c>
       <c r="O30" t="s">
         <v>171</v>
@@ -2366,10 +2366,10 @@
         <v>86</v>
       </c>
       <c r="M31" t="s">
-        <v>112</v>
+        <v>176</v>
       </c>
       <c r="N31" t="s">
-        <v>113</v>
+        <v>177</v>
       </c>
       <c r="O31" t="s">
         <v>171</v>
@@ -2428,10 +2428,10 @@
         <v>86</v>
       </c>
       <c r="M32" t="s">
-        <v>169</v>
+        <v>148</v>
       </c>
       <c r="N32" t="s">
-        <v>170</v>
+        <v>149</v>
       </c>
       <c r="O32" t="s">
         <v>171</v>
@@ -2490,10 +2490,10 @@
         <v>86</v>
       </c>
       <c r="M33" t="s">
-        <v>158</v>
+        <v>144</v>
       </c>
       <c r="N33" t="s">
-        <v>159</v>
+        <v>145</v>
       </c>
       <c r="O33" t="s">
         <v>171</v>
@@ -2552,10 +2552,10 @@
         <v>86</v>
       </c>
       <c r="M34" t="s">
-        <v>92</v>
+        <v>136</v>
       </c>
       <c r="N34" t="s">
-        <v>93</v>
+        <v>137</v>
       </c>
       <c r="O34" t="s">
         <v>171</v>
@@ -2614,10 +2614,10 @@
         <v>86</v>
       </c>
       <c r="M35" t="s">
-        <v>142</v>
+        <v>178</v>
       </c>
       <c r="N35" t="s">
-        <v>143</v>
+        <v>179</v>
       </c>
       <c r="O35" t="s">
         <v>171</v>
@@ -2676,10 +2676,10 @@
         <v>86</v>
       </c>
       <c r="M36" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="N36" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="O36" t="s">
         <v>171</v>
@@ -2738,10 +2738,10 @@
         <v>86</v>
       </c>
       <c r="M37" t="s">
-        <v>150</v>
+        <v>118</v>
       </c>
       <c r="N37" t="s">
-        <v>151</v>
+        <v>119</v>
       </c>
       <c r="O37" t="s">
         <v>171</v>
@@ -2800,10 +2800,10 @@
         <v>86</v>
       </c>
       <c r="M38" t="s">
-        <v>132</v>
+        <v>154</v>
       </c>
       <c r="N38" t="s">
-        <v>133</v>
+        <v>155</v>
       </c>
       <c r="O38" t="s">
         <v>171</v>
@@ -2862,10 +2862,10 @@
         <v>86</v>
       </c>
       <c r="M39" t="s">
-        <v>180</v>
+        <v>122</v>
       </c>
       <c r="N39" t="s">
-        <v>181</v>
+        <v>123</v>
       </c>
       <c r="O39" t="s">
         <v>171</v>
@@ -2924,10 +2924,10 @@
         <v>86</v>
       </c>
       <c r="M40" t="s">
-        <v>182</v>
+        <v>134</v>
       </c>
       <c r="N40" t="s">
-        <v>183</v>
+        <v>135</v>
       </c>
       <c r="O40" t="s">
         <v>171</v>
@@ -2986,10 +2986,10 @@
         <v>86</v>
       </c>
       <c r="M41" t="s">
-        <v>128</v>
+        <v>90</v>
       </c>
       <c r="N41" t="s">
-        <v>129</v>
+        <v>91</v>
       </c>
       <c r="O41" t="s">
         <v>171</v>
@@ -3048,10 +3048,10 @@
         <v>86</v>
       </c>
       <c r="M42" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="N42" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="O42" t="s">
         <v>171</v>
@@ -3086,10 +3086,10 @@
         <v>86</v>
       </c>
       <c r="M43" t="s">
-        <v>136</v>
+        <v>124</v>
       </c>
       <c r="N43" t="s">
-        <v>137</v>
+        <v>125</v>
       </c>
       <c r="O43" t="s">
         <v>171</v>
@@ -3124,10 +3124,10 @@
         <v>86</v>
       </c>
       <c r="M44" t="s">
-        <v>106</v>
+        <v>126</v>
       </c>
       <c r="N44" t="s">
-        <v>107</v>
+        <v>127</v>
       </c>
       <c r="O44" t="s">
         <v>171</v>
@@ -3162,10 +3162,10 @@
         <v>86</v>
       </c>
       <c r="M45" t="s">
-        <v>102</v>
+        <v>182</v>
       </c>
       <c r="N45" t="s">
-        <v>103</v>
+        <v>183</v>
       </c>
       <c r="O45" t="s">
         <v>171</v>
@@ -3200,10 +3200,10 @@
         <v>86</v>
       </c>
       <c r="M46" t="s">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="N46" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
       <c r="O46" t="s">
         <v>171</v>
@@ -3226,10 +3226,10 @@
         <v>86</v>
       </c>
       <c r="M47" t="s">
-        <v>186</v>
+        <v>102</v>
       </c>
       <c r="N47" t="s">
-        <v>187</v>
+        <v>103</v>
       </c>
       <c r="O47" t="s">
         <v>171</v>
@@ -3252,10 +3252,10 @@
         <v>86</v>
       </c>
       <c r="M48" t="s">
-        <v>140</v>
+        <v>161</v>
       </c>
       <c r="N48" t="s">
-        <v>141</v>
+        <v>162</v>
       </c>
       <c r="O48" t="s">
         <v>171</v>
@@ -3278,10 +3278,10 @@
         <v>86</v>
       </c>
       <c r="M49" t="s">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="N49" t="s">
-        <v>101</v>
+        <v>151</v>
       </c>
       <c r="O49" t="s">
         <v>171</v>
@@ -3304,10 +3304,10 @@
         <v>86</v>
       </c>
       <c r="M50" t="s">
-        <v>126</v>
+        <v>184</v>
       </c>
       <c r="N50" t="s">
-        <v>127</v>
+        <v>185</v>
       </c>
       <c r="O50" t="s">
         <v>171</v>
@@ -3330,10 +3330,10 @@
         <v>86</v>
       </c>
       <c r="M51" t="s">
-        <v>130</v>
+        <v>169</v>
       </c>
       <c r="N51" t="s">
-        <v>131</v>
+        <v>170</v>
       </c>
       <c r="O51" t="s">
         <v>171</v>
@@ -3344,10 +3344,10 @@
         <v>86</v>
       </c>
       <c r="M52" t="s">
-        <v>167</v>
+        <v>186</v>
       </c>
       <c r="N52" t="s">
-        <v>168</v>
+        <v>187</v>
       </c>
       <c r="O52" t="s">
         <v>171</v>
@@ -3358,10 +3358,10 @@
         <v>86</v>
       </c>
       <c r="M53" t="s">
-        <v>118</v>
+        <v>188</v>
       </c>
       <c r="N53" t="s">
-        <v>119</v>
+        <v>189</v>
       </c>
       <c r="O53" t="s">
         <v>171</v>
@@ -3372,10 +3372,10 @@
         <v>86</v>
       </c>
       <c r="M54" t="s">
-        <v>94</v>
+        <v>138</v>
       </c>
       <c r="N54" t="s">
-        <v>95</v>
+        <v>139</v>
       </c>
       <c r="O54" t="s">
         <v>171</v>
@@ -3386,10 +3386,10 @@
         <v>86</v>
       </c>
       <c r="M55" t="s">
-        <v>87</v>
+        <v>112</v>
       </c>
       <c r="N55" t="s">
-        <v>88</v>
+        <v>113</v>
       </c>
       <c r="O55" t="s">
         <v>171</v>
@@ -3400,10 +3400,10 @@
         <v>86</v>
       </c>
       <c r="M56" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="N56" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="O56" t="s">
         <v>171</v>
@@ -3414,10 +3414,10 @@
         <v>86</v>
       </c>
       <c r="M57" t="s">
-        <v>188</v>
+        <v>100</v>
       </c>
       <c r="N57" t="s">
-        <v>189</v>
+        <v>101</v>
       </c>
       <c r="O57" t="s">
         <v>171</v>
@@ -3428,10 +3428,10 @@
         <v>86</v>
       </c>
       <c r="M58" t="s">
-        <v>190</v>
+        <v>130</v>
       </c>
       <c r="N58" t="s">
-        <v>191</v>
+        <v>131</v>
       </c>
       <c r="O58" t="s">
         <v>171</v>
@@ -3442,10 +3442,10 @@
         <v>86</v>
       </c>
       <c r="M59" t="s">
-        <v>144</v>
+        <v>190</v>
       </c>
       <c r="N59" t="s">
-        <v>145</v>
+        <v>191</v>
       </c>
       <c r="O59" t="s">
         <v>171</v>
@@ -3456,10 +3456,10 @@
         <v>86</v>
       </c>
       <c r="M60" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="N60" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="O60" t="s">
         <v>171</v>
@@ -3484,10 +3484,10 @@
         <v>86</v>
       </c>
       <c r="M62" t="s">
-        <v>124</v>
+        <v>92</v>
       </c>
       <c r="N62" t="s">
-        <v>125</v>
+        <v>93</v>
       </c>
       <c r="O62" t="s">
         <v>171</v>
